--- a/Test Data/Regression/4689052/UK_ImportMapping.xlsx
+++ b/Test Data/Regression/4689052/UK_ImportMapping.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="5" rupBuild="29530"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="5" rupBuild="29822"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Playwright self\Test Data\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Playwright_self\playwright-OCT-Automation2\Test Data\Regression\4689052\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{349B98F9-C049-48E4-A7D8-96077D76A5DE}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C619C4F5-9977-41C0-AB70-498B22580BFA}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="11500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -16,14 +16,14 @@
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">Sheet1!$A$1:$F$854</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">Sheet1!$A$1:$F$852</definedName>
   </definedNames>
   <calcPr calcId="0"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1841" uniqueCount="922">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1831" uniqueCount="918">
   <si>
     <t>Account Code(Single)</t>
   </si>
@@ -125,18 +125,6 @@
   </si>
   <si>
     <t>Purchases</t>
-  </si>
-  <si>
-    <t>Trial balance__Income statement__Profit/loss__Tax on profit (+) / loss (-)</t>
-  </si>
-  <si>
-    <t>Printing, postage and stationery</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Tax on profit (+) / loss (-) </t>
-  </si>
-  <si>
-    <t>Rent and rates</t>
   </si>
   <si>
     <t>Trial balance__Income statement__Profit/loss before tax__Finance costs</t>
@@ -3131,7 +3119,7 @@
   <sheetPr>
     <outlinePr summaryBelow="0"/>
   </sheetPr>
-  <dimension ref="A1:F854"/>
+  <dimension ref="A1:F852"/>
   <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
     <col min="1" max="1" width="18.54296875" bestFit="1" customWidth="1"/>
@@ -3523,7 +3511,7 @@
     </row>
     <row r="20" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A20">
-        <v>276</v>
+        <v>405</v>
       </c>
       <c r="B20" t="s">
         <v>34</v>
@@ -3543,7 +3531,7 @@
     </row>
     <row r="21" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A21">
-        <v>250</v>
+        <v>374</v>
       </c>
       <c r="B21" t="s">
         <v>34</v>
@@ -3563,7 +3551,7 @@
     </row>
     <row r="22" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A22">
-        <v>405</v>
+        <v>244</v>
       </c>
       <c r="B22" t="s">
         <v>38</v>
@@ -3583,7 +3571,7 @@
     </row>
     <row r="23" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A23">
-        <v>374</v>
+        <v>243</v>
       </c>
       <c r="B23" t="s">
         <v>38</v>
@@ -3603,19 +3591,19 @@
     </row>
     <row r="24" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A24">
-        <v>244</v>
+        <v>294</v>
       </c>
       <c r="B24" t="s">
-        <v>42</v>
+        <v>38</v>
       </c>
       <c r="C24" t="s">
         <v>7</v>
       </c>
       <c r="D24" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="E24" t="s">
-        <v>44</v>
+        <v>40</v>
       </c>
       <c r="F24" t="s">
         <v>10</v>
@@ -3623,19 +3611,19 @@
     </row>
     <row r="25" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A25">
-        <v>243</v>
+        <v>1</v>
       </c>
       <c r="B25" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="C25" t="s">
         <v>7</v>
       </c>
       <c r="D25" t="s">
+        <v>44</v>
+      </c>
+      <c r="E25" t="s">
         <v>45</v>
-      </c>
-      <c r="E25" t="s">
-        <v>44</v>
       </c>
       <c r="F25" t="s">
         <v>10</v>
@@ -3643,10 +3631,10 @@
     </row>
     <row r="26" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A26">
-        <v>294</v>
+        <v>248</v>
       </c>
       <c r="B26" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="C26" t="s">
         <v>7</v>
@@ -3655,7 +3643,7 @@
         <v>46</v>
       </c>
       <c r="E26" t="s">
-        <v>44</v>
+        <v>47</v>
       </c>
       <c r="F26" t="s">
         <v>10</v>
@@ -3663,19 +3651,19 @@
     </row>
     <row r="27" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A27">
-        <v>1</v>
+        <v>360</v>
       </c>
       <c r="B27" t="s">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="C27" t="s">
         <v>7</v>
       </c>
       <c r="D27" t="s">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="E27" t="s">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="F27" t="s">
         <v>10</v>
@@ -3683,19 +3671,19 @@
     </row>
     <row r="28" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A28">
-        <v>248</v>
+        <v>335</v>
       </c>
       <c r="B28" t="s">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="C28" t="s">
         <v>7</v>
       </c>
       <c r="D28" t="s">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="E28" t="s">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="F28" t="s">
         <v>10</v>
@@ -3703,19 +3691,19 @@
     </row>
     <row r="29" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A29">
-        <v>360</v>
+        <v>234</v>
       </c>
       <c r="B29" t="s">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="C29" t="s">
         <v>7</v>
       </c>
       <c r="D29" t="s">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="E29" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="F29" t="s">
         <v>10</v>
@@ -3723,19 +3711,19 @@
     </row>
     <row r="30" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A30">
-        <v>335</v>
+        <v>231</v>
       </c>
       <c r="B30" t="s">
-        <v>52</v>
+        <v>56</v>
       </c>
       <c r="C30" t="s">
         <v>7</v>
       </c>
       <c r="D30" t="s">
-        <v>55</v>
+        <v>30</v>
       </c>
       <c r="E30" t="s">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="F30" t="s">
         <v>10</v>
@@ -3743,19 +3731,19 @@
     </row>
     <row r="31" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A31">
-        <v>234</v>
+        <v>254</v>
       </c>
       <c r="B31" t="s">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="C31" t="s">
         <v>7</v>
       </c>
       <c r="D31" t="s">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="E31" t="s">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="F31" t="s">
         <v>10</v>
@@ -3763,16 +3751,16 @@
     </row>
     <row r="32" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A32">
-        <v>231</v>
+        <v>74</v>
       </c>
       <c r="B32" t="s">
-        <v>60</v>
+        <v>48</v>
       </c>
       <c r="C32" t="s">
         <v>7</v>
       </c>
       <c r="D32" t="s">
-        <v>30</v>
+        <v>54</v>
       </c>
       <c r="E32" t="s">
         <v>61</v>
@@ -3783,7 +3771,7 @@
     </row>
     <row r="33" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A33">
-        <v>254</v>
+        <v>310</v>
       </c>
       <c r="B33" t="s">
         <v>62</v>
@@ -3803,16 +3791,16 @@
     </row>
     <row r="34" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A34">
-        <v>74</v>
+        <v>230</v>
       </c>
       <c r="B34" t="s">
-        <v>52</v>
+        <v>48</v>
       </c>
       <c r="C34" t="s">
         <v>7</v>
       </c>
       <c r="D34" t="s">
-        <v>58</v>
+        <v>32</v>
       </c>
       <c r="E34" t="s">
         <v>65</v>
@@ -3823,7 +3811,7 @@
     </row>
     <row r="35" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A35">
-        <v>310</v>
+        <v>341</v>
       </c>
       <c r="B35" t="s">
         <v>66</v>
@@ -3835,7 +3823,7 @@
         <v>67</v>
       </c>
       <c r="E35" t="s">
-        <v>68</v>
+        <v>64</v>
       </c>
       <c r="F35" t="s">
         <v>10</v>
@@ -3843,19 +3831,19 @@
     </row>
     <row r="36" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A36">
-        <v>230</v>
+        <v>280</v>
       </c>
       <c r="B36" t="s">
-        <v>52</v>
+        <v>68</v>
       </c>
       <c r="C36" t="s">
         <v>7</v>
       </c>
       <c r="D36" t="s">
-        <v>32</v>
+        <v>69</v>
       </c>
       <c r="E36" t="s">
-        <v>69</v>
+        <v>45</v>
       </c>
       <c r="F36" t="s">
         <v>10</v>
@@ -3863,7 +3851,7 @@
     </row>
     <row r="37" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A37">
-        <v>341</v>
+        <v>330</v>
       </c>
       <c r="B37" t="s">
         <v>70</v>
@@ -3875,7 +3863,7 @@
         <v>71</v>
       </c>
       <c r="E37" t="s">
-        <v>68</v>
+        <v>64</v>
       </c>
       <c r="F37" t="s">
         <v>10</v>
@@ -3883,7 +3871,7 @@
     </row>
     <row r="38" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A38">
-        <v>280</v>
+        <v>348</v>
       </c>
       <c r="B38" t="s">
         <v>72</v>
@@ -3895,7 +3883,7 @@
         <v>73</v>
       </c>
       <c r="E38" t="s">
-        <v>49</v>
+        <v>74</v>
       </c>
       <c r="F38" t="s">
         <v>10</v>
@@ -3903,10 +3891,10 @@
     </row>
     <row r="39" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A39">
-        <v>330</v>
+        <v>431</v>
       </c>
       <c r="B39" t="s">
-        <v>74</v>
+        <v>48</v>
       </c>
       <c r="C39" t="s">
         <v>7</v>
@@ -3915,7 +3903,7 @@
         <v>75</v>
       </c>
       <c r="E39" t="s">
-        <v>68</v>
+        <v>76</v>
       </c>
       <c r="F39" t="s">
         <v>10</v>
@@ -3923,19 +3911,19 @@
     </row>
     <row r="40" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A40">
-        <v>348</v>
+        <v>354</v>
       </c>
       <c r="B40" t="s">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="C40" t="s">
         <v>7</v>
       </c>
       <c r="D40" t="s">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="E40" t="s">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="F40" t="s">
         <v>10</v>
@@ -3943,19 +3931,19 @@
     </row>
     <row r="41" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A41">
-        <v>431</v>
+        <v>260</v>
       </c>
       <c r="B41" t="s">
-        <v>52</v>
+        <v>77</v>
       </c>
       <c r="C41" t="s">
         <v>7</v>
       </c>
       <c r="D41" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="E41" t="s">
-        <v>80</v>
+        <v>61</v>
       </c>
       <c r="F41" t="s">
         <v>10</v>
@@ -3963,110 +3951,86 @@
     </row>
     <row r="42" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A42">
-        <v>354</v>
+        <v>301</v>
       </c>
       <c r="B42" t="s">
-        <v>81</v>
+        <v>77</v>
       </c>
       <c r="C42" t="s">
         <v>7</v>
       </c>
       <c r="D42" t="s">
+        <v>81</v>
+      </c>
+      <c r="E42" t="s">
         <v>82</v>
-      </c>
-      <c r="E42" t="s">
-        <v>83</v>
       </c>
       <c r="F42" t="s">
         <v>10</v>
       </c>
     </row>
     <row r="43" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="A43">
-        <v>260</v>
-      </c>
       <c r="B43" t="s">
-        <v>81</v>
-      </c>
-      <c r="C43" t="s">
-        <v>7</v>
-      </c>
-      <c r="D43" t="s">
+        <v>83</v>
+      </c>
+      <c r="E43" t="s">
         <v>84</v>
       </c>
-      <c r="E43" t="s">
-        <v>65</v>
-      </c>
-      <c r="F43" t="s">
-        <v>10</v>
-      </c>
     </row>
     <row r="44" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="A44">
-        <v>301</v>
-      </c>
       <c r="B44" t="s">
-        <v>81</v>
-      </c>
-      <c r="C44" t="s">
-        <v>7</v>
-      </c>
-      <c r="D44" t="s">
         <v>85</v>
       </c>
       <c r="E44" t="s">
-        <v>86</v>
-      </c>
-      <c r="F44" t="s">
-        <v>10</v>
+        <v>60</v>
       </c>
     </row>
     <row r="45" spans="1:6" x14ac:dyDescent="0.35">
       <c r="B45" t="s">
+        <v>86</v>
+      </c>
+      <c r="E45" t="s">
         <v>87</v>
-      </c>
-      <c r="E45" t="s">
-        <v>88</v>
       </c>
     </row>
     <row r="46" spans="1:6" x14ac:dyDescent="0.35">
       <c r="B46" t="s">
-        <v>89</v>
+        <v>88</v>
       </c>
       <c r="E46" t="s">
-        <v>64</v>
+        <v>82</v>
       </c>
     </row>
     <row r="47" spans="1:6" x14ac:dyDescent="0.35">
       <c r="B47" t="s">
+        <v>89</v>
+      </c>
+      <c r="E47" t="s">
         <v>90</v>
-      </c>
-      <c r="E47" t="s">
-        <v>91</v>
       </c>
     </row>
     <row r="48" spans="1:6" x14ac:dyDescent="0.35">
       <c r="B48" t="s">
-        <v>92</v>
+        <v>91</v>
       </c>
       <c r="E48" t="s">
-        <v>86</v>
+        <v>74</v>
       </c>
     </row>
     <row r="49" spans="2:5" x14ac:dyDescent="0.35">
       <c r="B49" t="s">
+        <v>92</v>
+      </c>
+      <c r="E49" t="s">
         <v>93</v>
-      </c>
-      <c r="E49" t="s">
-        <v>94</v>
       </c>
     </row>
     <row r="50" spans="2:5" x14ac:dyDescent="0.35">
       <c r="B50" t="s">
+        <v>94</v>
+      </c>
+      <c r="E50" t="s">
         <v>95</v>
-      </c>
-      <c r="E50" t="s">
-        <v>78</v>
       </c>
     </row>
     <row r="51" spans="2:5" x14ac:dyDescent="0.35">
@@ -4090,23 +4054,23 @@
         <v>100</v>
       </c>
       <c r="E53" t="s">
-        <v>101</v>
+        <v>79</v>
       </c>
     </row>
     <row r="54" spans="2:5" x14ac:dyDescent="0.35">
       <c r="B54" t="s">
+        <v>101</v>
+      </c>
+      <c r="E54" t="s">
         <v>102</v>
-      </c>
-      <c r="E54" t="s">
-        <v>103</v>
       </c>
     </row>
     <row r="55" spans="2:5" x14ac:dyDescent="0.35">
       <c r="B55" t="s">
+        <v>103</v>
+      </c>
+      <c r="E55" t="s">
         <v>104</v>
-      </c>
-      <c r="E55" t="s">
-        <v>83</v>
       </c>
     </row>
     <row r="56" spans="2:5" x14ac:dyDescent="0.35">
@@ -4130,52 +4094,52 @@
         <v>109</v>
       </c>
       <c r="E58" t="s">
-        <v>110</v>
+        <v>45</v>
       </c>
     </row>
     <row r="59" spans="2:5" x14ac:dyDescent="0.35">
       <c r="B59" t="s">
-        <v>111</v>
+        <v>110</v>
       </c>
       <c r="E59" t="s">
-        <v>112</v>
+        <v>57</v>
       </c>
     </row>
     <row r="60" spans="2:5" x14ac:dyDescent="0.35">
       <c r="B60" t="s">
-        <v>113</v>
+        <v>111</v>
       </c>
       <c r="E60" t="s">
-        <v>49</v>
+        <v>55</v>
       </c>
     </row>
     <row r="61" spans="2:5" x14ac:dyDescent="0.35">
       <c r="B61" t="s">
-        <v>114</v>
+        <v>112</v>
       </c>
       <c r="E61" t="s">
-        <v>61</v>
+        <v>50</v>
       </c>
     </row>
     <row r="62" spans="2:5" x14ac:dyDescent="0.35">
       <c r="B62" t="s">
-        <v>115</v>
+        <v>113</v>
       </c>
       <c r="E62" t="s">
-        <v>59</v>
+        <v>60</v>
       </c>
     </row>
     <row r="63" spans="2:5" x14ac:dyDescent="0.35">
       <c r="B63" t="s">
-        <v>116</v>
+        <v>114</v>
       </c>
       <c r="E63" t="s">
-        <v>54</v>
+        <v>87</v>
       </c>
     </row>
     <row r="64" spans="2:5" x14ac:dyDescent="0.35">
       <c r="B64" t="s">
-        <v>117</v>
+        <v>115</v>
       </c>
       <c r="E64" t="s">
         <v>64</v>
@@ -4183,47 +4147,47 @@
     </row>
     <row r="65" spans="2:5" x14ac:dyDescent="0.35">
       <c r="B65" t="s">
-        <v>118</v>
+        <v>116</v>
       </c>
       <c r="E65" t="s">
-        <v>91</v>
+        <v>82</v>
       </c>
     </row>
     <row r="66" spans="2:5" x14ac:dyDescent="0.35">
       <c r="B66" t="s">
-        <v>119</v>
+        <v>117</v>
       </c>
       <c r="E66" t="s">
-        <v>68</v>
+        <v>90</v>
       </c>
     </row>
     <row r="67" spans="2:5" x14ac:dyDescent="0.35">
       <c r="B67" t="s">
-        <v>120</v>
+        <v>118</v>
       </c>
       <c r="E67" t="s">
-        <v>86</v>
+        <v>74</v>
       </c>
     </row>
     <row r="68" spans="2:5" x14ac:dyDescent="0.35">
       <c r="B68" t="s">
-        <v>121</v>
+        <v>119</v>
       </c>
       <c r="E68" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
     </row>
     <row r="69" spans="2:5" x14ac:dyDescent="0.35">
       <c r="B69" t="s">
-        <v>122</v>
+        <v>120</v>
       </c>
       <c r="E69" t="s">
-        <v>78</v>
+        <v>95</v>
       </c>
     </row>
     <row r="70" spans="2:5" x14ac:dyDescent="0.35">
       <c r="B70" t="s">
-        <v>123</v>
+        <v>121</v>
       </c>
       <c r="E70" t="s">
         <v>97</v>
@@ -4231,7 +4195,7 @@
     </row>
     <row r="71" spans="2:5" x14ac:dyDescent="0.35">
       <c r="B71" t="s">
-        <v>124</v>
+        <v>122</v>
       </c>
       <c r="E71" t="s">
         <v>99</v>
@@ -4239,31 +4203,31 @@
     </row>
     <row r="72" spans="2:5" x14ac:dyDescent="0.35">
       <c r="B72" t="s">
-        <v>125</v>
+        <v>123</v>
       </c>
       <c r="E72" t="s">
-        <v>101</v>
+        <v>79</v>
       </c>
     </row>
     <row r="73" spans="2:5" x14ac:dyDescent="0.35">
       <c r="B73" t="s">
-        <v>126</v>
+        <v>124</v>
       </c>
       <c r="E73" t="s">
-        <v>103</v>
+        <v>102</v>
       </c>
     </row>
     <row r="74" spans="2:5" x14ac:dyDescent="0.35">
       <c r="B74" t="s">
-        <v>127</v>
+        <v>125</v>
       </c>
       <c r="E74" t="s">
-        <v>83</v>
+        <v>104</v>
       </c>
     </row>
     <row r="75" spans="2:5" x14ac:dyDescent="0.35">
       <c r="B75" t="s">
-        <v>128</v>
+        <v>126</v>
       </c>
       <c r="E75" t="s">
         <v>106</v>
@@ -4271,7 +4235,7 @@
     </row>
     <row r="76" spans="2:5" x14ac:dyDescent="0.35">
       <c r="B76" t="s">
-        <v>129</v>
+        <v>127</v>
       </c>
       <c r="E76" t="s">
         <v>108</v>
@@ -4279,55 +4243,55 @@
     </row>
     <row r="77" spans="2:5" x14ac:dyDescent="0.35">
       <c r="B77" t="s">
-        <v>130</v>
+        <v>128</v>
       </c>
       <c r="E77" t="s">
-        <v>110</v>
+        <v>45</v>
       </c>
     </row>
     <row r="78" spans="2:5" x14ac:dyDescent="0.35">
       <c r="B78" t="s">
-        <v>131</v>
+        <v>129</v>
       </c>
       <c r="E78" t="s">
-        <v>112</v>
+        <v>57</v>
       </c>
     </row>
     <row r="79" spans="2:5" x14ac:dyDescent="0.35">
       <c r="B79" t="s">
-        <v>132</v>
+        <v>130</v>
       </c>
       <c r="E79" t="s">
-        <v>49</v>
+        <v>55</v>
       </c>
     </row>
     <row r="80" spans="2:5" x14ac:dyDescent="0.35">
       <c r="B80" t="s">
-        <v>133</v>
+        <v>131</v>
       </c>
       <c r="E80" t="s">
-        <v>61</v>
+        <v>50</v>
       </c>
     </row>
     <row r="81" spans="2:5" x14ac:dyDescent="0.35">
       <c r="B81" t="s">
-        <v>134</v>
+        <v>132</v>
       </c>
       <c r="E81" t="s">
-        <v>59</v>
+        <v>60</v>
       </c>
     </row>
     <row r="82" spans="2:5" x14ac:dyDescent="0.35">
       <c r="B82" t="s">
-        <v>135</v>
+        <v>133</v>
       </c>
       <c r="E82" t="s">
-        <v>54</v>
+        <v>87</v>
       </c>
     </row>
     <row r="83" spans="2:5" x14ac:dyDescent="0.35">
       <c r="B83" t="s">
-        <v>136</v>
+        <v>134</v>
       </c>
       <c r="E83" t="s">
         <v>64</v>
@@ -4335,47 +4299,47 @@
     </row>
     <row r="84" spans="2:5" x14ac:dyDescent="0.35">
       <c r="B84" t="s">
-        <v>137</v>
+        <v>135</v>
       </c>
       <c r="E84" t="s">
-        <v>91</v>
+        <v>82</v>
       </c>
     </row>
     <row r="85" spans="2:5" x14ac:dyDescent="0.35">
       <c r="B85" t="s">
-        <v>138</v>
+        <v>136</v>
       </c>
       <c r="E85" t="s">
-        <v>68</v>
+        <v>90</v>
       </c>
     </row>
     <row r="86" spans="2:5" x14ac:dyDescent="0.35">
       <c r="B86" t="s">
-        <v>139</v>
+        <v>137</v>
       </c>
       <c r="E86" t="s">
-        <v>86</v>
+        <v>74</v>
       </c>
     </row>
     <row r="87" spans="2:5" x14ac:dyDescent="0.35">
       <c r="B87" t="s">
-        <v>140</v>
+        <v>138</v>
       </c>
       <c r="E87" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
     </row>
     <row r="88" spans="2:5" x14ac:dyDescent="0.35">
       <c r="B88" t="s">
-        <v>141</v>
+        <v>139</v>
       </c>
       <c r="E88" t="s">
-        <v>78</v>
+        <v>95</v>
       </c>
     </row>
     <row r="89" spans="2:5" x14ac:dyDescent="0.35">
       <c r="B89" t="s">
-        <v>142</v>
+        <v>140</v>
       </c>
       <c r="E89" t="s">
         <v>97</v>
@@ -4383,7 +4347,7 @@
     </row>
     <row r="90" spans="2:5" x14ac:dyDescent="0.35">
       <c r="B90" t="s">
-        <v>143</v>
+        <v>141</v>
       </c>
       <c r="E90" t="s">
         <v>99</v>
@@ -4391,31 +4355,31 @@
     </row>
     <row r="91" spans="2:5" x14ac:dyDescent="0.35">
       <c r="B91" t="s">
-        <v>144</v>
+        <v>142</v>
       </c>
       <c r="E91" t="s">
-        <v>101</v>
+        <v>79</v>
       </c>
     </row>
     <row r="92" spans="2:5" x14ac:dyDescent="0.35">
       <c r="B92" t="s">
-        <v>145</v>
+        <v>143</v>
       </c>
       <c r="E92" t="s">
-        <v>103</v>
+        <v>102</v>
       </c>
     </row>
     <row r="93" spans="2:5" x14ac:dyDescent="0.35">
       <c r="B93" t="s">
-        <v>146</v>
+        <v>144</v>
       </c>
       <c r="E93" t="s">
-        <v>83</v>
+        <v>104</v>
       </c>
     </row>
     <row r="94" spans="2:5" x14ac:dyDescent="0.35">
       <c r="B94" t="s">
-        <v>147</v>
+        <v>145</v>
       </c>
       <c r="E94" t="s">
         <v>106</v>
@@ -4423,7 +4387,7 @@
     </row>
     <row r="95" spans="2:5" x14ac:dyDescent="0.35">
       <c r="B95" t="s">
-        <v>148</v>
+        <v>146</v>
       </c>
       <c r="E95" t="s">
         <v>108</v>
@@ -4431,55 +4395,55 @@
     </row>
     <row r="96" spans="2:5" x14ac:dyDescent="0.35">
       <c r="B96" t="s">
-        <v>149</v>
+        <v>147</v>
       </c>
       <c r="E96" t="s">
-        <v>110</v>
+        <v>45</v>
       </c>
     </row>
     <row r="97" spans="2:5" x14ac:dyDescent="0.35">
       <c r="B97" t="s">
-        <v>150</v>
+        <v>148</v>
       </c>
       <c r="E97" t="s">
-        <v>112</v>
+        <v>57</v>
       </c>
     </row>
     <row r="98" spans="2:5" x14ac:dyDescent="0.35">
       <c r="B98" t="s">
-        <v>151</v>
+        <v>149</v>
       </c>
       <c r="E98" t="s">
-        <v>49</v>
+        <v>55</v>
       </c>
     </row>
     <row r="99" spans="2:5" x14ac:dyDescent="0.35">
       <c r="B99" t="s">
-        <v>152</v>
+        <v>150</v>
       </c>
       <c r="E99" t="s">
-        <v>61</v>
+        <v>50</v>
       </c>
     </row>
     <row r="100" spans="2:5" x14ac:dyDescent="0.35">
       <c r="B100" t="s">
-        <v>153</v>
+        <v>151</v>
       </c>
       <c r="E100" t="s">
-        <v>59</v>
+        <v>60</v>
       </c>
     </row>
     <row r="101" spans="2:5" x14ac:dyDescent="0.35">
       <c r="B101" t="s">
-        <v>154</v>
+        <v>152</v>
       </c>
       <c r="E101" t="s">
-        <v>54</v>
+        <v>87</v>
       </c>
     </row>
     <row r="102" spans="2:5" x14ac:dyDescent="0.35">
       <c r="B102" t="s">
-        <v>155</v>
+        <v>153</v>
       </c>
       <c r="E102" t="s">
         <v>64</v>
@@ -4487,47 +4451,47 @@
     </row>
     <row r="103" spans="2:5" x14ac:dyDescent="0.35">
       <c r="B103" t="s">
-        <v>156</v>
+        <v>154</v>
       </c>
       <c r="E103" t="s">
-        <v>91</v>
+        <v>82</v>
       </c>
     </row>
     <row r="104" spans="2:5" x14ac:dyDescent="0.35">
       <c r="B104" t="s">
-        <v>157</v>
+        <v>155</v>
       </c>
       <c r="E104" t="s">
-        <v>68</v>
+        <v>90</v>
       </c>
     </row>
     <row r="105" spans="2:5" x14ac:dyDescent="0.35">
       <c r="B105" t="s">
-        <v>158</v>
+        <v>156</v>
       </c>
       <c r="E105" t="s">
-        <v>86</v>
+        <v>74</v>
       </c>
     </row>
     <row r="106" spans="2:5" x14ac:dyDescent="0.35">
       <c r="B106" t="s">
-        <v>159</v>
+        <v>157</v>
       </c>
       <c r="E106" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
     </row>
     <row r="107" spans="2:5" x14ac:dyDescent="0.35">
       <c r="B107" t="s">
-        <v>160</v>
+        <v>158</v>
       </c>
       <c r="E107" t="s">
-        <v>78</v>
+        <v>95</v>
       </c>
     </row>
     <row r="108" spans="2:5" x14ac:dyDescent="0.35">
       <c r="B108" t="s">
-        <v>161</v>
+        <v>159</v>
       </c>
       <c r="E108" t="s">
         <v>97</v>
@@ -4535,7 +4499,7 @@
     </row>
     <row r="109" spans="2:5" x14ac:dyDescent="0.35">
       <c r="B109" t="s">
-        <v>162</v>
+        <v>160</v>
       </c>
       <c r="E109" t="s">
         <v>99</v>
@@ -4543,31 +4507,31 @@
     </row>
     <row r="110" spans="2:5" x14ac:dyDescent="0.35">
       <c r="B110" t="s">
-        <v>163</v>
+        <v>161</v>
       </c>
       <c r="E110" t="s">
-        <v>101</v>
+        <v>79</v>
       </c>
     </row>
     <row r="111" spans="2:5" x14ac:dyDescent="0.35">
       <c r="B111" t="s">
-        <v>164</v>
+        <v>162</v>
       </c>
       <c r="E111" t="s">
-        <v>103</v>
+        <v>102</v>
       </c>
     </row>
     <row r="112" spans="2:5" x14ac:dyDescent="0.35">
       <c r="B112" t="s">
-        <v>165</v>
+        <v>163</v>
       </c>
       <c r="E112" t="s">
-        <v>83</v>
+        <v>104</v>
       </c>
     </row>
     <row r="113" spans="2:5" x14ac:dyDescent="0.35">
       <c r="B113" t="s">
-        <v>166</v>
+        <v>164</v>
       </c>
       <c r="E113" t="s">
         <v>106</v>
@@ -4575,7 +4539,7 @@
     </row>
     <row r="114" spans="2:5" x14ac:dyDescent="0.35">
       <c r="B114" t="s">
-        <v>167</v>
+        <v>165</v>
       </c>
       <c r="E114" t="s">
         <v>108</v>
@@ -4583,55 +4547,55 @@
     </row>
     <row r="115" spans="2:5" x14ac:dyDescent="0.35">
       <c r="B115" t="s">
-        <v>168</v>
+        <v>166</v>
       </c>
       <c r="E115" t="s">
-        <v>110</v>
+        <v>45</v>
       </c>
     </row>
     <row r="116" spans="2:5" x14ac:dyDescent="0.35">
       <c r="B116" t="s">
-        <v>169</v>
+        <v>167</v>
       </c>
       <c r="E116" t="s">
-        <v>112</v>
+        <v>57</v>
       </c>
     </row>
     <row r="117" spans="2:5" x14ac:dyDescent="0.35">
       <c r="B117" t="s">
-        <v>170</v>
+        <v>168</v>
       </c>
       <c r="E117" t="s">
-        <v>49</v>
+        <v>55</v>
       </c>
     </row>
     <row r="118" spans="2:5" x14ac:dyDescent="0.35">
       <c r="B118" t="s">
-        <v>171</v>
+        <v>169</v>
       </c>
       <c r="E118" t="s">
-        <v>61</v>
+        <v>50</v>
       </c>
     </row>
     <row r="119" spans="2:5" x14ac:dyDescent="0.35">
       <c r="B119" t="s">
-        <v>172</v>
+        <v>170</v>
       </c>
       <c r="E119" t="s">
-        <v>59</v>
+        <v>60</v>
       </c>
     </row>
     <row r="120" spans="2:5" x14ac:dyDescent="0.35">
       <c r="B120" t="s">
-        <v>173</v>
+        <v>171</v>
       </c>
       <c r="E120" t="s">
-        <v>54</v>
+        <v>87</v>
       </c>
     </row>
     <row r="121" spans="2:5" x14ac:dyDescent="0.35">
       <c r="B121" t="s">
-        <v>174</v>
+        <v>172</v>
       </c>
       <c r="E121" t="s">
         <v>64</v>
@@ -4639,47 +4603,47 @@
     </row>
     <row r="122" spans="2:5" x14ac:dyDescent="0.35">
       <c r="B122" t="s">
-        <v>175</v>
+        <v>173</v>
       </c>
       <c r="E122" t="s">
-        <v>91</v>
+        <v>82</v>
       </c>
     </row>
     <row r="123" spans="2:5" x14ac:dyDescent="0.35">
       <c r="B123" t="s">
-        <v>176</v>
+        <v>174</v>
       </c>
       <c r="E123" t="s">
-        <v>68</v>
+        <v>90</v>
       </c>
     </row>
     <row r="124" spans="2:5" x14ac:dyDescent="0.35">
       <c r="B124" t="s">
-        <v>177</v>
+        <v>175</v>
       </c>
       <c r="E124" t="s">
-        <v>86</v>
+        <v>74</v>
       </c>
     </row>
     <row r="125" spans="2:5" x14ac:dyDescent="0.35">
       <c r="B125" t="s">
-        <v>178</v>
+        <v>176</v>
       </c>
       <c r="E125" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
     </row>
     <row r="126" spans="2:5" x14ac:dyDescent="0.35">
       <c r="B126" t="s">
-        <v>179</v>
+        <v>177</v>
       </c>
       <c r="E126" t="s">
-        <v>78</v>
+        <v>95</v>
       </c>
     </row>
     <row r="127" spans="2:5" x14ac:dyDescent="0.35">
       <c r="B127" t="s">
-        <v>180</v>
+        <v>178</v>
       </c>
       <c r="E127" t="s">
         <v>97</v>
@@ -4687,7 +4651,7 @@
     </row>
     <row r="128" spans="2:5" x14ac:dyDescent="0.35">
       <c r="B128" t="s">
-        <v>181</v>
+        <v>179</v>
       </c>
       <c r="E128" t="s">
         <v>99</v>
@@ -4695,31 +4659,31 @@
     </row>
     <row r="129" spans="2:5" x14ac:dyDescent="0.35">
       <c r="B129" t="s">
-        <v>182</v>
+        <v>180</v>
       </c>
       <c r="E129" t="s">
-        <v>101</v>
+        <v>79</v>
       </c>
     </row>
     <row r="130" spans="2:5" x14ac:dyDescent="0.35">
       <c r="B130" t="s">
-        <v>183</v>
+        <v>181</v>
       </c>
       <c r="E130" t="s">
-        <v>103</v>
+        <v>102</v>
       </c>
     </row>
     <row r="131" spans="2:5" x14ac:dyDescent="0.35">
       <c r="B131" t="s">
-        <v>184</v>
+        <v>182</v>
       </c>
       <c r="E131" t="s">
-        <v>83</v>
+        <v>104</v>
       </c>
     </row>
     <row r="132" spans="2:5" x14ac:dyDescent="0.35">
       <c r="B132" t="s">
-        <v>185</v>
+        <v>183</v>
       </c>
       <c r="E132" t="s">
         <v>106</v>
@@ -4727,7 +4691,7 @@
     </row>
     <row r="133" spans="2:5" x14ac:dyDescent="0.35">
       <c r="B133" t="s">
-        <v>186</v>
+        <v>184</v>
       </c>
       <c r="E133" t="s">
         <v>108</v>
@@ -4735,55 +4699,55 @@
     </row>
     <row r="134" spans="2:5" x14ac:dyDescent="0.35">
       <c r="B134" t="s">
-        <v>187</v>
+        <v>185</v>
       </c>
       <c r="E134" t="s">
-        <v>110</v>
+        <v>45</v>
       </c>
     </row>
     <row r="135" spans="2:5" x14ac:dyDescent="0.35">
       <c r="B135" t="s">
-        <v>188</v>
+        <v>186</v>
       </c>
       <c r="E135" t="s">
-        <v>112</v>
+        <v>57</v>
       </c>
     </row>
     <row r="136" spans="2:5" x14ac:dyDescent="0.35">
       <c r="B136" t="s">
-        <v>189</v>
+        <v>187</v>
       </c>
       <c r="E136" t="s">
-        <v>49</v>
+        <v>55</v>
       </c>
     </row>
     <row r="137" spans="2:5" x14ac:dyDescent="0.35">
       <c r="B137" t="s">
-        <v>190</v>
+        <v>188</v>
       </c>
       <c r="E137" t="s">
-        <v>61</v>
+        <v>50</v>
       </c>
     </row>
     <row r="138" spans="2:5" x14ac:dyDescent="0.35">
       <c r="B138" t="s">
-        <v>191</v>
+        <v>189</v>
       </c>
       <c r="E138" t="s">
-        <v>59</v>
+        <v>60</v>
       </c>
     </row>
     <row r="139" spans="2:5" x14ac:dyDescent="0.35">
       <c r="B139" t="s">
-        <v>192</v>
+        <v>190</v>
       </c>
       <c r="E139" t="s">
-        <v>54</v>
+        <v>87</v>
       </c>
     </row>
     <row r="140" spans="2:5" x14ac:dyDescent="0.35">
       <c r="B140" t="s">
-        <v>193</v>
+        <v>191</v>
       </c>
       <c r="E140" t="s">
         <v>64</v>
@@ -4791,47 +4755,47 @@
     </row>
     <row r="141" spans="2:5" x14ac:dyDescent="0.35">
       <c r="B141" t="s">
-        <v>194</v>
+        <v>192</v>
       </c>
       <c r="E141" t="s">
-        <v>91</v>
+        <v>82</v>
       </c>
     </row>
     <row r="142" spans="2:5" x14ac:dyDescent="0.35">
       <c r="B142" t="s">
-        <v>195</v>
+        <v>193</v>
       </c>
       <c r="E142" t="s">
-        <v>68</v>
+        <v>90</v>
       </c>
     </row>
     <row r="143" spans="2:5" x14ac:dyDescent="0.35">
       <c r="B143" t="s">
-        <v>196</v>
+        <v>194</v>
       </c>
       <c r="E143" t="s">
-        <v>86</v>
+        <v>74</v>
       </c>
     </row>
     <row r="144" spans="2:5" x14ac:dyDescent="0.35">
       <c r="B144" t="s">
-        <v>197</v>
+        <v>195</v>
       </c>
       <c r="E144" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
     </row>
     <row r="145" spans="2:5" x14ac:dyDescent="0.35">
       <c r="B145" t="s">
-        <v>198</v>
+        <v>196</v>
       </c>
       <c r="E145" t="s">
-        <v>78</v>
+        <v>95</v>
       </c>
     </row>
     <row r="146" spans="2:5" x14ac:dyDescent="0.35">
       <c r="B146" t="s">
-        <v>199</v>
+        <v>197</v>
       </c>
       <c r="E146" t="s">
         <v>97</v>
@@ -4839,7 +4803,7 @@
     </row>
     <row r="147" spans="2:5" x14ac:dyDescent="0.35">
       <c r="B147" t="s">
-        <v>200</v>
+        <v>198</v>
       </c>
       <c r="E147" t="s">
         <v>99</v>
@@ -4847,31 +4811,31 @@
     </row>
     <row r="148" spans="2:5" x14ac:dyDescent="0.35">
       <c r="B148" t="s">
-        <v>201</v>
+        <v>199</v>
       </c>
       <c r="E148" t="s">
-        <v>101</v>
+        <v>79</v>
       </c>
     </row>
     <row r="149" spans="2:5" x14ac:dyDescent="0.35">
       <c r="B149" t="s">
-        <v>202</v>
+        <v>200</v>
       </c>
       <c r="E149" t="s">
-        <v>103</v>
+        <v>102</v>
       </c>
     </row>
     <row r="150" spans="2:5" x14ac:dyDescent="0.35">
       <c r="B150" t="s">
-        <v>203</v>
+        <v>201</v>
       </c>
       <c r="E150" t="s">
-        <v>83</v>
+        <v>104</v>
       </c>
     </row>
     <row r="151" spans="2:5" x14ac:dyDescent="0.35">
       <c r="B151" t="s">
-        <v>204</v>
+        <v>202</v>
       </c>
       <c r="E151" t="s">
         <v>106</v>
@@ -4879,7 +4843,7 @@
     </row>
     <row r="152" spans="2:5" x14ac:dyDescent="0.35">
       <c r="B152" t="s">
-        <v>205</v>
+        <v>203</v>
       </c>
       <c r="E152" t="s">
         <v>108</v>
@@ -4887,55 +4851,55 @@
     </row>
     <row r="153" spans="2:5" x14ac:dyDescent="0.35">
       <c r="B153" t="s">
-        <v>206</v>
+        <v>204</v>
       </c>
       <c r="E153" t="s">
-        <v>110</v>
+        <v>45</v>
       </c>
     </row>
     <row r="154" spans="2:5" x14ac:dyDescent="0.35">
       <c r="B154" t="s">
-        <v>207</v>
+        <v>205</v>
       </c>
       <c r="E154" t="s">
-        <v>112</v>
+        <v>57</v>
       </c>
     </row>
     <row r="155" spans="2:5" x14ac:dyDescent="0.35">
       <c r="B155" t="s">
-        <v>208</v>
+        <v>206</v>
       </c>
       <c r="E155" t="s">
-        <v>49</v>
+        <v>55</v>
       </c>
     </row>
     <row r="156" spans="2:5" x14ac:dyDescent="0.35">
       <c r="B156" t="s">
-        <v>209</v>
+        <v>207</v>
       </c>
       <c r="E156" t="s">
-        <v>61</v>
+        <v>50</v>
       </c>
     </row>
     <row r="157" spans="2:5" x14ac:dyDescent="0.35">
       <c r="B157" t="s">
-        <v>210</v>
+        <v>208</v>
       </c>
       <c r="E157" t="s">
-        <v>59</v>
+        <v>60</v>
       </c>
     </row>
     <row r="158" spans="2:5" x14ac:dyDescent="0.35">
       <c r="B158" t="s">
-        <v>211</v>
+        <v>209</v>
       </c>
       <c r="E158" t="s">
-        <v>54</v>
+        <v>87</v>
       </c>
     </row>
     <row r="159" spans="2:5" x14ac:dyDescent="0.35">
       <c r="B159" t="s">
-        <v>212</v>
+        <v>210</v>
       </c>
       <c r="E159" t="s">
         <v>64</v>
@@ -4943,47 +4907,47 @@
     </row>
     <row r="160" spans="2:5" x14ac:dyDescent="0.35">
       <c r="B160" t="s">
-        <v>213</v>
+        <v>211</v>
       </c>
       <c r="E160" t="s">
-        <v>91</v>
+        <v>82</v>
       </c>
     </row>
     <row r="161" spans="2:5" x14ac:dyDescent="0.35">
       <c r="B161" t="s">
-        <v>214</v>
+        <v>212</v>
       </c>
       <c r="E161" t="s">
-        <v>68</v>
+        <v>90</v>
       </c>
     </row>
     <row r="162" spans="2:5" x14ac:dyDescent="0.35">
       <c r="B162" t="s">
-        <v>215</v>
+        <v>213</v>
       </c>
       <c r="E162" t="s">
-        <v>86</v>
+        <v>74</v>
       </c>
     </row>
     <row r="163" spans="2:5" x14ac:dyDescent="0.35">
       <c r="B163" t="s">
-        <v>216</v>
+        <v>214</v>
       </c>
       <c r="E163" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
     </row>
     <row r="164" spans="2:5" x14ac:dyDescent="0.35">
       <c r="B164" t="s">
-        <v>217</v>
+        <v>215</v>
       </c>
       <c r="E164" t="s">
-        <v>78</v>
+        <v>95</v>
       </c>
     </row>
     <row r="165" spans="2:5" x14ac:dyDescent="0.35">
       <c r="B165" t="s">
-        <v>218</v>
+        <v>216</v>
       </c>
       <c r="E165" t="s">
         <v>97</v>
@@ -4991,7 +4955,7 @@
     </row>
     <row r="166" spans="2:5" x14ac:dyDescent="0.35">
       <c r="B166" t="s">
-        <v>219</v>
+        <v>217</v>
       </c>
       <c r="E166" t="s">
         <v>99</v>
@@ -4999,31 +4963,31 @@
     </row>
     <row r="167" spans="2:5" x14ac:dyDescent="0.35">
       <c r="B167" t="s">
-        <v>220</v>
+        <v>218</v>
       </c>
       <c r="E167" t="s">
-        <v>101</v>
+        <v>79</v>
       </c>
     </row>
     <row r="168" spans="2:5" x14ac:dyDescent="0.35">
       <c r="B168" t="s">
-        <v>221</v>
+        <v>219</v>
       </c>
       <c r="E168" t="s">
-        <v>103</v>
+        <v>102</v>
       </c>
     </row>
     <row r="169" spans="2:5" x14ac:dyDescent="0.35">
       <c r="B169" t="s">
-        <v>222</v>
+        <v>220</v>
       </c>
       <c r="E169" t="s">
-        <v>83</v>
+        <v>104</v>
       </c>
     </row>
     <row r="170" spans="2:5" x14ac:dyDescent="0.35">
       <c r="B170" t="s">
-        <v>223</v>
+        <v>221</v>
       </c>
       <c r="E170" t="s">
         <v>106</v>
@@ -5031,7 +4995,7 @@
     </row>
     <row r="171" spans="2:5" x14ac:dyDescent="0.35">
       <c r="B171" t="s">
-        <v>224</v>
+        <v>222</v>
       </c>
       <c r="E171" t="s">
         <v>108</v>
@@ -5039,55 +5003,55 @@
     </row>
     <row r="172" spans="2:5" x14ac:dyDescent="0.35">
       <c r="B172" t="s">
-        <v>225</v>
+        <v>223</v>
       </c>
       <c r="E172" t="s">
-        <v>110</v>
+        <v>45</v>
       </c>
     </row>
     <row r="173" spans="2:5" x14ac:dyDescent="0.35">
       <c r="B173" t="s">
-        <v>226</v>
+        <v>224</v>
       </c>
       <c r="E173" t="s">
-        <v>112</v>
+        <v>57</v>
       </c>
     </row>
     <row r="174" spans="2:5" x14ac:dyDescent="0.35">
       <c r="B174" t="s">
-        <v>227</v>
+        <v>225</v>
       </c>
       <c r="E174" t="s">
-        <v>49</v>
+        <v>55</v>
       </c>
     </row>
     <row r="175" spans="2:5" x14ac:dyDescent="0.35">
       <c r="B175" t="s">
-        <v>228</v>
+        <v>226</v>
       </c>
       <c r="E175" t="s">
-        <v>61</v>
+        <v>50</v>
       </c>
     </row>
     <row r="176" spans="2:5" x14ac:dyDescent="0.35">
       <c r="B176" t="s">
-        <v>229</v>
+        <v>227</v>
       </c>
       <c r="E176" t="s">
-        <v>59</v>
+        <v>60</v>
       </c>
     </row>
     <row r="177" spans="2:5" x14ac:dyDescent="0.35">
       <c r="B177" t="s">
-        <v>230</v>
+        <v>228</v>
       </c>
       <c r="E177" t="s">
-        <v>54</v>
+        <v>87</v>
       </c>
     </row>
     <row r="178" spans="2:5" x14ac:dyDescent="0.35">
       <c r="B178" t="s">
-        <v>231</v>
+        <v>229</v>
       </c>
       <c r="E178" t="s">
         <v>64</v>
@@ -5095,47 +5059,47 @@
     </row>
     <row r="179" spans="2:5" x14ac:dyDescent="0.35">
       <c r="B179" t="s">
-        <v>232</v>
+        <v>230</v>
       </c>
       <c r="E179" t="s">
-        <v>91</v>
+        <v>82</v>
       </c>
     </row>
     <row r="180" spans="2:5" x14ac:dyDescent="0.35">
       <c r="B180" t="s">
-        <v>233</v>
+        <v>231</v>
       </c>
       <c r="E180" t="s">
-        <v>68</v>
+        <v>90</v>
       </c>
     </row>
     <row r="181" spans="2:5" x14ac:dyDescent="0.35">
       <c r="B181" t="s">
-        <v>234</v>
+        <v>232</v>
       </c>
       <c r="E181" t="s">
-        <v>86</v>
+        <v>74</v>
       </c>
     </row>
     <row r="182" spans="2:5" x14ac:dyDescent="0.35">
       <c r="B182" t="s">
-        <v>235</v>
+        <v>233</v>
       </c>
       <c r="E182" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
     </row>
     <row r="183" spans="2:5" x14ac:dyDescent="0.35">
       <c r="B183" t="s">
-        <v>236</v>
+        <v>234</v>
       </c>
       <c r="E183" t="s">
-        <v>78</v>
+        <v>95</v>
       </c>
     </row>
     <row r="184" spans="2:5" x14ac:dyDescent="0.35">
       <c r="B184" t="s">
-        <v>237</v>
+        <v>235</v>
       </c>
       <c r="E184" t="s">
         <v>97</v>
@@ -5143,7 +5107,7 @@
     </row>
     <row r="185" spans="2:5" x14ac:dyDescent="0.35">
       <c r="B185" t="s">
-        <v>238</v>
+        <v>236</v>
       </c>
       <c r="E185" t="s">
         <v>99</v>
@@ -5151,31 +5115,31 @@
     </row>
     <row r="186" spans="2:5" x14ac:dyDescent="0.35">
       <c r="B186" t="s">
-        <v>239</v>
+        <v>237</v>
       </c>
       <c r="E186" t="s">
-        <v>101</v>
+        <v>79</v>
       </c>
     </row>
     <row r="187" spans="2:5" x14ac:dyDescent="0.35">
       <c r="B187" t="s">
-        <v>240</v>
+        <v>238</v>
       </c>
       <c r="E187" t="s">
-        <v>103</v>
+        <v>102</v>
       </c>
     </row>
     <row r="188" spans="2:5" x14ac:dyDescent="0.35">
       <c r="B188" t="s">
-        <v>241</v>
+        <v>239</v>
       </c>
       <c r="E188" t="s">
-        <v>83</v>
+        <v>104</v>
       </c>
     </row>
     <row r="189" spans="2:5" x14ac:dyDescent="0.35">
       <c r="B189" t="s">
-        <v>242</v>
+        <v>240</v>
       </c>
       <c r="E189" t="s">
         <v>106</v>
@@ -5183,7 +5147,7 @@
     </row>
     <row r="190" spans="2:5" x14ac:dyDescent="0.35">
       <c r="B190" t="s">
-        <v>243</v>
+        <v>241</v>
       </c>
       <c r="E190" t="s">
         <v>108</v>
@@ -5191,79 +5155,79 @@
     </row>
     <row r="191" spans="2:5" x14ac:dyDescent="0.35">
       <c r="B191" t="s">
-        <v>244</v>
+        <v>242</v>
       </c>
       <c r="E191" t="s">
-        <v>110</v>
+        <v>57</v>
       </c>
     </row>
     <row r="192" spans="2:5" x14ac:dyDescent="0.35">
       <c r="B192" t="s">
-        <v>245</v>
+        <v>243</v>
       </c>
       <c r="E192" t="s">
-        <v>112</v>
+        <v>55</v>
       </c>
     </row>
     <row r="193" spans="2:5" x14ac:dyDescent="0.35">
       <c r="B193" t="s">
-        <v>246</v>
+        <v>244</v>
       </c>
       <c r="E193" t="s">
-        <v>61</v>
+        <v>50</v>
       </c>
     </row>
     <row r="194" spans="2:5" x14ac:dyDescent="0.35">
       <c r="B194" t="s">
-        <v>247</v>
+        <v>245</v>
       </c>
       <c r="E194" t="s">
-        <v>59</v>
+        <v>60</v>
       </c>
     </row>
     <row r="195" spans="2:5" x14ac:dyDescent="0.35">
       <c r="B195" t="s">
-        <v>248</v>
+        <v>246</v>
       </c>
       <c r="E195" t="s">
-        <v>54</v>
+        <v>87</v>
       </c>
     </row>
     <row r="196" spans="2:5" x14ac:dyDescent="0.35">
       <c r="B196" t="s">
-        <v>249</v>
+        <v>247</v>
       </c>
       <c r="E196" t="s">
-        <v>64</v>
+        <v>82</v>
       </c>
     </row>
     <row r="197" spans="2:5" x14ac:dyDescent="0.35">
       <c r="B197" t="s">
-        <v>250</v>
+        <v>248</v>
       </c>
       <c r="E197" t="s">
-        <v>91</v>
+        <v>90</v>
       </c>
     </row>
     <row r="198" spans="2:5" x14ac:dyDescent="0.35">
       <c r="B198" t="s">
-        <v>251</v>
+        <v>249</v>
       </c>
       <c r="E198" t="s">
-        <v>86</v>
+        <v>93</v>
       </c>
     </row>
     <row r="199" spans="2:5" x14ac:dyDescent="0.35">
       <c r="B199" t="s">
-        <v>252</v>
+        <v>250</v>
       </c>
       <c r="E199" t="s">
-        <v>94</v>
+        <v>95</v>
       </c>
     </row>
     <row r="200" spans="2:5" x14ac:dyDescent="0.35">
       <c r="B200" t="s">
-        <v>253</v>
+        <v>251</v>
       </c>
       <c r="E200" t="s">
         <v>97</v>
@@ -5271,7 +5235,7 @@
     </row>
     <row r="201" spans="2:5" x14ac:dyDescent="0.35">
       <c r="B201" t="s">
-        <v>254</v>
+        <v>252</v>
       </c>
       <c r="E201" t="s">
         <v>99</v>
@@ -5279,23 +5243,23 @@
     </row>
     <row r="202" spans="2:5" x14ac:dyDescent="0.35">
       <c r="B202" t="s">
-        <v>255</v>
+        <v>253</v>
       </c>
       <c r="E202" t="s">
-        <v>101</v>
+        <v>102</v>
       </c>
     </row>
     <row r="203" spans="2:5" x14ac:dyDescent="0.35">
       <c r="B203" t="s">
-        <v>256</v>
+        <v>254</v>
       </c>
       <c r="E203" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
     </row>
     <row r="204" spans="2:5" x14ac:dyDescent="0.35">
       <c r="B204" t="s">
-        <v>257</v>
+        <v>255</v>
       </c>
       <c r="E204" t="s">
         <v>106</v>
@@ -5303,7 +5267,7 @@
     </row>
     <row r="205" spans="2:5" x14ac:dyDescent="0.35">
       <c r="B205" t="s">
-        <v>258</v>
+        <v>256</v>
       </c>
       <c r="E205" t="s">
         <v>108</v>
@@ -5311,55 +5275,55 @@
     </row>
     <row r="206" spans="2:5" x14ac:dyDescent="0.35">
       <c r="B206" t="s">
-        <v>259</v>
+        <v>257</v>
       </c>
       <c r="E206" t="s">
-        <v>110</v>
+        <v>45</v>
       </c>
     </row>
     <row r="207" spans="2:5" x14ac:dyDescent="0.35">
       <c r="B207" t="s">
-        <v>260</v>
+        <v>258</v>
       </c>
       <c r="E207" t="s">
-        <v>112</v>
+        <v>57</v>
       </c>
     </row>
     <row r="208" spans="2:5" x14ac:dyDescent="0.35">
       <c r="B208" t="s">
-        <v>261</v>
+        <v>259</v>
       </c>
       <c r="E208" t="s">
-        <v>49</v>
+        <v>55</v>
       </c>
     </row>
     <row r="209" spans="2:5" x14ac:dyDescent="0.35">
       <c r="B209" t="s">
-        <v>262</v>
+        <v>260</v>
       </c>
       <c r="E209" t="s">
-        <v>61</v>
+        <v>50</v>
       </c>
     </row>
     <row r="210" spans="2:5" x14ac:dyDescent="0.35">
       <c r="B210" t="s">
-        <v>263</v>
+        <v>261</v>
       </c>
       <c r="E210" t="s">
-        <v>59</v>
+        <v>60</v>
       </c>
     </row>
     <row r="211" spans="2:5" x14ac:dyDescent="0.35">
       <c r="B211" t="s">
-        <v>264</v>
+        <v>262</v>
       </c>
       <c r="E211" t="s">
-        <v>54</v>
+        <v>87</v>
       </c>
     </row>
     <row r="212" spans="2:5" x14ac:dyDescent="0.35">
       <c r="B212" t="s">
-        <v>265</v>
+        <v>263</v>
       </c>
       <c r="E212" t="s">
         <v>64</v>
@@ -5367,47 +5331,47 @@
     </row>
     <row r="213" spans="2:5" x14ac:dyDescent="0.35">
       <c r="B213" t="s">
-        <v>266</v>
+        <v>264</v>
       </c>
       <c r="E213" t="s">
-        <v>91</v>
+        <v>82</v>
       </c>
     </row>
     <row r="214" spans="2:5" x14ac:dyDescent="0.35">
       <c r="B214" t="s">
-        <v>267</v>
+        <v>265</v>
       </c>
       <c r="E214" t="s">
-        <v>68</v>
+        <v>90</v>
       </c>
     </row>
     <row r="215" spans="2:5" x14ac:dyDescent="0.35">
       <c r="B215" t="s">
-        <v>268</v>
+        <v>266</v>
       </c>
       <c r="E215" t="s">
-        <v>86</v>
+        <v>74</v>
       </c>
     </row>
     <row r="216" spans="2:5" x14ac:dyDescent="0.35">
       <c r="B216" t="s">
-        <v>269</v>
+        <v>267</v>
       </c>
       <c r="E216" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
     </row>
     <row r="217" spans="2:5" x14ac:dyDescent="0.35">
       <c r="B217" t="s">
-        <v>270</v>
+        <v>268</v>
       </c>
       <c r="E217" t="s">
-        <v>78</v>
+        <v>95</v>
       </c>
     </row>
     <row r="218" spans="2:5" x14ac:dyDescent="0.35">
       <c r="B218" t="s">
-        <v>271</v>
+        <v>269</v>
       </c>
       <c r="E218" t="s">
         <v>97</v>
@@ -5415,7 +5379,7 @@
     </row>
     <row r="219" spans="2:5" x14ac:dyDescent="0.35">
       <c r="B219" t="s">
-        <v>272</v>
+        <v>270</v>
       </c>
       <c r="E219" t="s">
         <v>99</v>
@@ -5423,31 +5387,31 @@
     </row>
     <row r="220" spans="2:5" x14ac:dyDescent="0.35">
       <c r="B220" t="s">
-        <v>273</v>
+        <v>271</v>
       </c>
       <c r="E220" t="s">
-        <v>101</v>
+        <v>79</v>
       </c>
     </row>
     <row r="221" spans="2:5" x14ac:dyDescent="0.35">
       <c r="B221" t="s">
-        <v>274</v>
+        <v>272</v>
       </c>
       <c r="E221" t="s">
-        <v>103</v>
+        <v>102</v>
       </c>
     </row>
     <row r="222" spans="2:5" x14ac:dyDescent="0.35">
       <c r="B222" t="s">
-        <v>275</v>
+        <v>273</v>
       </c>
       <c r="E222" t="s">
-        <v>83</v>
+        <v>104</v>
       </c>
     </row>
     <row r="223" spans="2:5" x14ac:dyDescent="0.35">
       <c r="B223" t="s">
-        <v>276</v>
+        <v>274</v>
       </c>
       <c r="E223" t="s">
         <v>106</v>
@@ -5455,7 +5419,7 @@
     </row>
     <row r="224" spans="2:5" x14ac:dyDescent="0.35">
       <c r="B224" t="s">
-        <v>277</v>
+        <v>275</v>
       </c>
       <c r="E224" t="s">
         <v>108</v>
@@ -5463,55 +5427,55 @@
     </row>
     <row r="225" spans="2:5" x14ac:dyDescent="0.35">
       <c r="B225" t="s">
-        <v>278</v>
+        <v>276</v>
       </c>
       <c r="E225" t="s">
-        <v>110</v>
+        <v>45</v>
       </c>
     </row>
     <row r="226" spans="2:5" x14ac:dyDescent="0.35">
       <c r="B226" t="s">
-        <v>279</v>
+        <v>277</v>
       </c>
       <c r="E226" t="s">
-        <v>112</v>
+        <v>57</v>
       </c>
     </row>
     <row r="227" spans="2:5" x14ac:dyDescent="0.35">
       <c r="B227" t="s">
-        <v>280</v>
+        <v>278</v>
       </c>
       <c r="E227" t="s">
-        <v>49</v>
+        <v>55</v>
       </c>
     </row>
     <row r="228" spans="2:5" x14ac:dyDescent="0.35">
       <c r="B228" t="s">
-        <v>281</v>
+        <v>279</v>
       </c>
       <c r="E228" t="s">
-        <v>61</v>
+        <v>50</v>
       </c>
     </row>
     <row r="229" spans="2:5" x14ac:dyDescent="0.35">
       <c r="B229" t="s">
-        <v>282</v>
+        <v>280</v>
       </c>
       <c r="E229" t="s">
-        <v>59</v>
+        <v>60</v>
       </c>
     </row>
     <row r="230" spans="2:5" x14ac:dyDescent="0.35">
       <c r="B230" t="s">
-        <v>283</v>
+        <v>281</v>
       </c>
       <c r="E230" t="s">
-        <v>54</v>
+        <v>87</v>
       </c>
     </row>
     <row r="231" spans="2:5" x14ac:dyDescent="0.35">
       <c r="B231" t="s">
-        <v>284</v>
+        <v>282</v>
       </c>
       <c r="E231" t="s">
         <v>64</v>
@@ -5519,47 +5483,47 @@
     </row>
     <row r="232" spans="2:5" x14ac:dyDescent="0.35">
       <c r="B232" t="s">
-        <v>285</v>
+        <v>283</v>
       </c>
       <c r="E232" t="s">
-        <v>91</v>
+        <v>82</v>
       </c>
     </row>
     <row r="233" spans="2:5" x14ac:dyDescent="0.35">
       <c r="B233" t="s">
-        <v>286</v>
+        <v>284</v>
       </c>
       <c r="E233" t="s">
-        <v>68</v>
+        <v>90</v>
       </c>
     </row>
     <row r="234" spans="2:5" x14ac:dyDescent="0.35">
       <c r="B234" t="s">
-        <v>287</v>
+        <v>285</v>
       </c>
       <c r="E234" t="s">
-        <v>86</v>
+        <v>74</v>
       </c>
     </row>
     <row r="235" spans="2:5" x14ac:dyDescent="0.35">
       <c r="B235" t="s">
-        <v>288</v>
+        <v>286</v>
       </c>
       <c r="E235" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
     </row>
     <row r="236" spans="2:5" x14ac:dyDescent="0.35">
       <c r="B236" t="s">
-        <v>289</v>
+        <v>287</v>
       </c>
       <c r="E236" t="s">
-        <v>78</v>
+        <v>95</v>
       </c>
     </row>
     <row r="237" spans="2:5" x14ac:dyDescent="0.35">
       <c r="B237" t="s">
-        <v>290</v>
+        <v>288</v>
       </c>
       <c r="E237" t="s">
         <v>97</v>
@@ -5567,7 +5531,7 @@
     </row>
     <row r="238" spans="2:5" x14ac:dyDescent="0.35">
       <c r="B238" t="s">
-        <v>291</v>
+        <v>289</v>
       </c>
       <c r="E238" t="s">
         <v>99</v>
@@ -5575,31 +5539,31 @@
     </row>
     <row r="239" spans="2:5" x14ac:dyDescent="0.35">
       <c r="B239" t="s">
-        <v>292</v>
+        <v>290</v>
       </c>
       <c r="E239" t="s">
-        <v>101</v>
+        <v>79</v>
       </c>
     </row>
     <row r="240" spans="2:5" x14ac:dyDescent="0.35">
       <c r="B240" t="s">
-        <v>293</v>
+        <v>291</v>
       </c>
       <c r="E240" t="s">
-        <v>103</v>
+        <v>102</v>
       </c>
     </row>
     <row r="241" spans="2:5" x14ac:dyDescent="0.35">
       <c r="B241" t="s">
-        <v>294</v>
+        <v>292</v>
       </c>
       <c r="E241" t="s">
-        <v>83</v>
+        <v>104</v>
       </c>
     </row>
     <row r="242" spans="2:5" x14ac:dyDescent="0.35">
       <c r="B242" t="s">
-        <v>295</v>
+        <v>293</v>
       </c>
       <c r="E242" t="s">
         <v>106</v>
@@ -5607,7 +5571,7 @@
     </row>
     <row r="243" spans="2:5" x14ac:dyDescent="0.35">
       <c r="B243" t="s">
-        <v>296</v>
+        <v>294</v>
       </c>
       <c r="E243" t="s">
         <v>108</v>
@@ -5615,55 +5579,55 @@
     </row>
     <row r="244" spans="2:5" x14ac:dyDescent="0.35">
       <c r="B244" t="s">
-        <v>297</v>
+        <v>295</v>
       </c>
       <c r="E244" t="s">
-        <v>110</v>
+        <v>45</v>
       </c>
     </row>
     <row r="245" spans="2:5" x14ac:dyDescent="0.35">
       <c r="B245" t="s">
-        <v>298</v>
+        <v>296</v>
       </c>
       <c r="E245" t="s">
-        <v>112</v>
+        <v>57</v>
       </c>
     </row>
     <row r="246" spans="2:5" x14ac:dyDescent="0.35">
       <c r="B246" t="s">
-        <v>299</v>
+        <v>297</v>
       </c>
       <c r="E246" t="s">
-        <v>49</v>
+        <v>55</v>
       </c>
     </row>
     <row r="247" spans="2:5" x14ac:dyDescent="0.35">
       <c r="B247" t="s">
-        <v>300</v>
+        <v>298</v>
       </c>
       <c r="E247" t="s">
-        <v>61</v>
+        <v>50</v>
       </c>
     </row>
     <row r="248" spans="2:5" x14ac:dyDescent="0.35">
       <c r="B248" t="s">
-        <v>301</v>
+        <v>299</v>
       </c>
       <c r="E248" t="s">
-        <v>59</v>
+        <v>60</v>
       </c>
     </row>
     <row r="249" spans="2:5" x14ac:dyDescent="0.35">
       <c r="B249" t="s">
-        <v>302</v>
+        <v>300</v>
       </c>
       <c r="E249" t="s">
-        <v>54</v>
+        <v>87</v>
       </c>
     </row>
     <row r="250" spans="2:5" x14ac:dyDescent="0.35">
       <c r="B250" t="s">
-        <v>303</v>
+        <v>301</v>
       </c>
       <c r="E250" t="s">
         <v>64</v>
@@ -5671,47 +5635,47 @@
     </row>
     <row r="251" spans="2:5" x14ac:dyDescent="0.35">
       <c r="B251" t="s">
-        <v>304</v>
+        <v>302</v>
       </c>
       <c r="E251" t="s">
-        <v>91</v>
+        <v>82</v>
       </c>
     </row>
     <row r="252" spans="2:5" x14ac:dyDescent="0.35">
       <c r="B252" t="s">
-        <v>305</v>
+        <v>303</v>
       </c>
       <c r="E252" t="s">
-        <v>68</v>
+        <v>90</v>
       </c>
     </row>
     <row r="253" spans="2:5" x14ac:dyDescent="0.35">
       <c r="B253" t="s">
-        <v>306</v>
+        <v>304</v>
       </c>
       <c r="E253" t="s">
-        <v>86</v>
+        <v>74</v>
       </c>
     </row>
     <row r="254" spans="2:5" x14ac:dyDescent="0.35">
       <c r="B254" t="s">
-        <v>307</v>
+        <v>305</v>
       </c>
       <c r="E254" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
     </row>
     <row r="255" spans="2:5" x14ac:dyDescent="0.35">
       <c r="B255" t="s">
-        <v>308</v>
+        <v>306</v>
       </c>
       <c r="E255" t="s">
-        <v>78</v>
+        <v>95</v>
       </c>
     </row>
     <row r="256" spans="2:5" x14ac:dyDescent="0.35">
       <c r="B256" t="s">
-        <v>309</v>
+        <v>307</v>
       </c>
       <c r="E256" t="s">
         <v>97</v>
@@ -5719,7 +5683,7 @@
     </row>
     <row r="257" spans="2:5" x14ac:dyDescent="0.35">
       <c r="B257" t="s">
-        <v>310</v>
+        <v>308</v>
       </c>
       <c r="E257" t="s">
         <v>99</v>
@@ -5727,31 +5691,31 @@
     </row>
     <row r="258" spans="2:5" x14ac:dyDescent="0.35">
       <c r="B258" t="s">
-        <v>311</v>
+        <v>309</v>
       </c>
       <c r="E258" t="s">
-        <v>101</v>
+        <v>79</v>
       </c>
     </row>
     <row r="259" spans="2:5" x14ac:dyDescent="0.35">
       <c r="B259" t="s">
-        <v>312</v>
+        <v>310</v>
       </c>
       <c r="E259" t="s">
-        <v>103</v>
+        <v>102</v>
       </c>
     </row>
     <row r="260" spans="2:5" x14ac:dyDescent="0.35">
       <c r="B260" t="s">
-        <v>313</v>
+        <v>311</v>
       </c>
       <c r="E260" t="s">
-        <v>83</v>
+        <v>104</v>
       </c>
     </row>
     <row r="261" spans="2:5" x14ac:dyDescent="0.35">
       <c r="B261" t="s">
-        <v>314</v>
+        <v>312</v>
       </c>
       <c r="E261" t="s">
         <v>106</v>
@@ -5759,7 +5723,7 @@
     </row>
     <row r="262" spans="2:5" x14ac:dyDescent="0.35">
       <c r="B262" t="s">
-        <v>315</v>
+        <v>313</v>
       </c>
       <c r="E262" t="s">
         <v>108</v>
@@ -5767,55 +5731,55 @@
     </row>
     <row r="263" spans="2:5" x14ac:dyDescent="0.35">
       <c r="B263" t="s">
-        <v>316</v>
+        <v>314</v>
       </c>
       <c r="E263" t="s">
-        <v>110</v>
+        <v>45</v>
       </c>
     </row>
     <row r="264" spans="2:5" x14ac:dyDescent="0.35">
       <c r="B264" t="s">
-        <v>317</v>
+        <v>315</v>
       </c>
       <c r="E264" t="s">
-        <v>112</v>
+        <v>57</v>
       </c>
     </row>
     <row r="265" spans="2:5" x14ac:dyDescent="0.35">
       <c r="B265" t="s">
-        <v>318</v>
+        <v>316</v>
       </c>
       <c r="E265" t="s">
-        <v>49</v>
+        <v>55</v>
       </c>
     </row>
     <row r="266" spans="2:5" x14ac:dyDescent="0.35">
       <c r="B266" t="s">
-        <v>319</v>
+        <v>317</v>
       </c>
       <c r="E266" t="s">
-        <v>61</v>
+        <v>50</v>
       </c>
     </row>
     <row r="267" spans="2:5" x14ac:dyDescent="0.35">
       <c r="B267" t="s">
-        <v>320</v>
+        <v>318</v>
       </c>
       <c r="E267" t="s">
-        <v>59</v>
+        <v>60</v>
       </c>
     </row>
     <row r="268" spans="2:5" x14ac:dyDescent="0.35">
       <c r="B268" t="s">
-        <v>321</v>
+        <v>319</v>
       </c>
       <c r="E268" t="s">
-        <v>54</v>
+        <v>87</v>
       </c>
     </row>
     <row r="269" spans="2:5" x14ac:dyDescent="0.35">
       <c r="B269" t="s">
-        <v>322</v>
+        <v>320</v>
       </c>
       <c r="E269" t="s">
         <v>64</v>
@@ -5823,47 +5787,47 @@
     </row>
     <row r="270" spans="2:5" x14ac:dyDescent="0.35">
       <c r="B270" t="s">
-        <v>323</v>
+        <v>321</v>
       </c>
       <c r="E270" t="s">
-        <v>91</v>
+        <v>82</v>
       </c>
     </row>
     <row r="271" spans="2:5" x14ac:dyDescent="0.35">
       <c r="B271" t="s">
-        <v>324</v>
+        <v>322</v>
       </c>
       <c r="E271" t="s">
-        <v>68</v>
+        <v>90</v>
       </c>
     </row>
     <row r="272" spans="2:5" x14ac:dyDescent="0.35">
       <c r="B272" t="s">
-        <v>325</v>
+        <v>323</v>
       </c>
       <c r="E272" t="s">
-        <v>86</v>
+        <v>74</v>
       </c>
     </row>
     <row r="273" spans="2:5" x14ac:dyDescent="0.35">
       <c r="B273" t="s">
-        <v>326</v>
+        <v>324</v>
       </c>
       <c r="E273" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
     </row>
     <row r="274" spans="2:5" x14ac:dyDescent="0.35">
       <c r="B274" t="s">
-        <v>327</v>
+        <v>325</v>
       </c>
       <c r="E274" t="s">
-        <v>78</v>
+        <v>95</v>
       </c>
     </row>
     <row r="275" spans="2:5" x14ac:dyDescent="0.35">
       <c r="B275" t="s">
-        <v>328</v>
+        <v>326</v>
       </c>
       <c r="E275" t="s">
         <v>97</v>
@@ -5871,7 +5835,7 @@
     </row>
     <row r="276" spans="2:5" x14ac:dyDescent="0.35">
       <c r="B276" t="s">
-        <v>329</v>
+        <v>327</v>
       </c>
       <c r="E276" t="s">
         <v>99</v>
@@ -5879,31 +5843,31 @@
     </row>
     <row r="277" spans="2:5" x14ac:dyDescent="0.35">
       <c r="B277" t="s">
-        <v>330</v>
+        <v>328</v>
       </c>
       <c r="E277" t="s">
-        <v>101</v>
+        <v>79</v>
       </c>
     </row>
     <row r="278" spans="2:5" x14ac:dyDescent="0.35">
       <c r="B278" t="s">
-        <v>331</v>
+        <v>329</v>
       </c>
       <c r="E278" t="s">
-        <v>103</v>
+        <v>102</v>
       </c>
     </row>
     <row r="279" spans="2:5" x14ac:dyDescent="0.35">
       <c r="B279" t="s">
-        <v>332</v>
+        <v>330</v>
       </c>
       <c r="E279" t="s">
-        <v>83</v>
+        <v>104</v>
       </c>
     </row>
     <row r="280" spans="2:5" x14ac:dyDescent="0.35">
       <c r="B280" t="s">
-        <v>333</v>
+        <v>331</v>
       </c>
       <c r="E280" t="s">
         <v>106</v>
@@ -5911,7 +5875,7 @@
     </row>
     <row r="281" spans="2:5" x14ac:dyDescent="0.35">
       <c r="B281" t="s">
-        <v>334</v>
+        <v>332</v>
       </c>
       <c r="E281" t="s">
         <v>108</v>
@@ -5919,55 +5883,55 @@
     </row>
     <row r="282" spans="2:5" x14ac:dyDescent="0.35">
       <c r="B282" t="s">
-        <v>335</v>
+        <v>333</v>
       </c>
       <c r="E282" t="s">
-        <v>110</v>
+        <v>45</v>
       </c>
     </row>
     <row r="283" spans="2:5" x14ac:dyDescent="0.35">
       <c r="B283" t="s">
-        <v>336</v>
+        <v>334</v>
       </c>
       <c r="E283" t="s">
-        <v>112</v>
+        <v>57</v>
       </c>
     </row>
     <row r="284" spans="2:5" x14ac:dyDescent="0.35">
       <c r="B284" t="s">
-        <v>337</v>
+        <v>335</v>
       </c>
       <c r="E284" t="s">
-        <v>49</v>
+        <v>55</v>
       </c>
     </row>
     <row r="285" spans="2:5" x14ac:dyDescent="0.35">
       <c r="B285" t="s">
-        <v>338</v>
+        <v>336</v>
       </c>
       <c r="E285" t="s">
-        <v>61</v>
+        <v>50</v>
       </c>
     </row>
     <row r="286" spans="2:5" x14ac:dyDescent="0.35">
       <c r="B286" t="s">
-        <v>339</v>
+        <v>337</v>
       </c>
       <c r="E286" t="s">
-        <v>59</v>
+        <v>60</v>
       </c>
     </row>
     <row r="287" spans="2:5" x14ac:dyDescent="0.35">
       <c r="B287" t="s">
-        <v>340</v>
+        <v>338</v>
       </c>
       <c r="E287" t="s">
-        <v>54</v>
+        <v>87</v>
       </c>
     </row>
     <row r="288" spans="2:5" x14ac:dyDescent="0.35">
       <c r="B288" t="s">
-        <v>341</v>
+        <v>339</v>
       </c>
       <c r="E288" t="s">
         <v>64</v>
@@ -5975,47 +5939,47 @@
     </row>
     <row r="289" spans="2:5" x14ac:dyDescent="0.35">
       <c r="B289" t="s">
-        <v>342</v>
+        <v>340</v>
       </c>
       <c r="E289" t="s">
-        <v>91</v>
+        <v>82</v>
       </c>
     </row>
     <row r="290" spans="2:5" x14ac:dyDescent="0.35">
       <c r="B290" t="s">
-        <v>343</v>
+        <v>341</v>
       </c>
       <c r="E290" t="s">
-        <v>68</v>
+        <v>90</v>
       </c>
     </row>
     <row r="291" spans="2:5" x14ac:dyDescent="0.35">
       <c r="B291" t="s">
-        <v>344</v>
+        <v>342</v>
       </c>
       <c r="E291" t="s">
-        <v>86</v>
+        <v>74</v>
       </c>
     </row>
     <row r="292" spans="2:5" x14ac:dyDescent="0.35">
       <c r="B292" t="s">
-        <v>345</v>
+        <v>343</v>
       </c>
       <c r="E292" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
     </row>
     <row r="293" spans="2:5" x14ac:dyDescent="0.35">
       <c r="B293" t="s">
-        <v>346</v>
+        <v>344</v>
       </c>
       <c r="E293" t="s">
-        <v>78</v>
+        <v>95</v>
       </c>
     </row>
     <row r="294" spans="2:5" x14ac:dyDescent="0.35">
       <c r="B294" t="s">
-        <v>347</v>
+        <v>345</v>
       </c>
       <c r="E294" t="s">
         <v>97</v>
@@ -6023,7 +5987,7 @@
     </row>
     <row r="295" spans="2:5" x14ac:dyDescent="0.35">
       <c r="B295" t="s">
-        <v>348</v>
+        <v>346</v>
       </c>
       <c r="E295" t="s">
         <v>99</v>
@@ -6031,31 +5995,31 @@
     </row>
     <row r="296" spans="2:5" x14ac:dyDescent="0.35">
       <c r="B296" t="s">
-        <v>349</v>
+        <v>347</v>
       </c>
       <c r="E296" t="s">
-        <v>101</v>
+        <v>79</v>
       </c>
     </row>
     <row r="297" spans="2:5" x14ac:dyDescent="0.35">
       <c r="B297" t="s">
-        <v>350</v>
+        <v>348</v>
       </c>
       <c r="E297" t="s">
-        <v>103</v>
+        <v>102</v>
       </c>
     </row>
     <row r="298" spans="2:5" x14ac:dyDescent="0.35">
       <c r="B298" t="s">
-        <v>351</v>
+        <v>349</v>
       </c>
       <c r="E298" t="s">
-        <v>83</v>
+        <v>104</v>
       </c>
     </row>
     <row r="299" spans="2:5" x14ac:dyDescent="0.35">
       <c r="B299" t="s">
-        <v>352</v>
+        <v>350</v>
       </c>
       <c r="E299" t="s">
         <v>106</v>
@@ -6063,7 +6027,7 @@
     </row>
     <row r="300" spans="2:5" x14ac:dyDescent="0.35">
       <c r="B300" t="s">
-        <v>353</v>
+        <v>351</v>
       </c>
       <c r="E300" t="s">
         <v>108</v>
@@ -6071,55 +6035,55 @@
     </row>
     <row r="301" spans="2:5" x14ac:dyDescent="0.35">
       <c r="B301" t="s">
-        <v>354</v>
+        <v>352</v>
       </c>
       <c r="E301" t="s">
-        <v>110</v>
+        <v>45</v>
       </c>
     </row>
     <row r="302" spans="2:5" x14ac:dyDescent="0.35">
       <c r="B302" t="s">
-        <v>355</v>
+        <v>353</v>
       </c>
       <c r="E302" t="s">
-        <v>112</v>
+        <v>57</v>
       </c>
     </row>
     <row r="303" spans="2:5" x14ac:dyDescent="0.35">
       <c r="B303" t="s">
-        <v>356</v>
+        <v>354</v>
       </c>
       <c r="E303" t="s">
-        <v>49</v>
+        <v>55</v>
       </c>
     </row>
     <row r="304" spans="2:5" x14ac:dyDescent="0.35">
       <c r="B304" t="s">
-        <v>357</v>
+        <v>355</v>
       </c>
       <c r="E304" t="s">
-        <v>61</v>
+        <v>50</v>
       </c>
     </row>
     <row r="305" spans="2:5" x14ac:dyDescent="0.35">
       <c r="B305" t="s">
-        <v>358</v>
+        <v>356</v>
       </c>
       <c r="E305" t="s">
-        <v>59</v>
+        <v>60</v>
       </c>
     </row>
     <row r="306" spans="2:5" x14ac:dyDescent="0.35">
       <c r="B306" t="s">
-        <v>359</v>
+        <v>357</v>
       </c>
       <c r="E306" t="s">
-        <v>54</v>
+        <v>87</v>
       </c>
     </row>
     <row r="307" spans="2:5" x14ac:dyDescent="0.35">
       <c r="B307" t="s">
-        <v>360</v>
+        <v>358</v>
       </c>
       <c r="E307" t="s">
         <v>64</v>
@@ -6127,47 +6091,47 @@
     </row>
     <row r="308" spans="2:5" x14ac:dyDescent="0.35">
       <c r="B308" t="s">
-        <v>361</v>
+        <v>359</v>
       </c>
       <c r="E308" t="s">
-        <v>91</v>
+        <v>82</v>
       </c>
     </row>
     <row r="309" spans="2:5" x14ac:dyDescent="0.35">
       <c r="B309" t="s">
-        <v>362</v>
+        <v>360</v>
       </c>
       <c r="E309" t="s">
-        <v>68</v>
+        <v>90</v>
       </c>
     </row>
     <row r="310" spans="2:5" x14ac:dyDescent="0.35">
       <c r="B310" t="s">
-        <v>363</v>
+        <v>361</v>
       </c>
       <c r="E310" t="s">
-        <v>86</v>
+        <v>74</v>
       </c>
     </row>
     <row r="311" spans="2:5" x14ac:dyDescent="0.35">
       <c r="B311" t="s">
-        <v>364</v>
+        <v>362</v>
       </c>
       <c r="E311" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
     </row>
     <row r="312" spans="2:5" x14ac:dyDescent="0.35">
       <c r="B312" t="s">
-        <v>365</v>
+        <v>363</v>
       </c>
       <c r="E312" t="s">
-        <v>78</v>
+        <v>95</v>
       </c>
     </row>
     <row r="313" spans="2:5" x14ac:dyDescent="0.35">
       <c r="B313" t="s">
-        <v>366</v>
+        <v>364</v>
       </c>
       <c r="E313" t="s">
         <v>97</v>
@@ -6175,7 +6139,7 @@
     </row>
     <row r="314" spans="2:5" x14ac:dyDescent="0.35">
       <c r="B314" t="s">
-        <v>367</v>
+        <v>365</v>
       </c>
       <c r="E314" t="s">
         <v>99</v>
@@ -6183,31 +6147,31 @@
     </row>
     <row r="315" spans="2:5" x14ac:dyDescent="0.35">
       <c r="B315" t="s">
-        <v>368</v>
+        <v>366</v>
       </c>
       <c r="E315" t="s">
-        <v>101</v>
+        <v>79</v>
       </c>
     </row>
     <row r="316" spans="2:5" x14ac:dyDescent="0.35">
       <c r="B316" t="s">
-        <v>369</v>
+        <v>367</v>
       </c>
       <c r="E316" t="s">
-        <v>103</v>
+        <v>102</v>
       </c>
     </row>
     <row r="317" spans="2:5" x14ac:dyDescent="0.35">
       <c r="B317" t="s">
-        <v>370</v>
+        <v>368</v>
       </c>
       <c r="E317" t="s">
-        <v>83</v>
+        <v>104</v>
       </c>
     </row>
     <row r="318" spans="2:5" x14ac:dyDescent="0.35">
       <c r="B318" t="s">
-        <v>371</v>
+        <v>369</v>
       </c>
       <c r="E318" t="s">
         <v>106</v>
@@ -6215,7 +6179,7 @@
     </row>
     <row r="319" spans="2:5" x14ac:dyDescent="0.35">
       <c r="B319" t="s">
-        <v>372</v>
+        <v>370</v>
       </c>
       <c r="E319" t="s">
         <v>108</v>
@@ -6223,55 +6187,55 @@
     </row>
     <row r="320" spans="2:5" x14ac:dyDescent="0.35">
       <c r="B320" t="s">
-        <v>373</v>
+        <v>371</v>
       </c>
       <c r="E320" t="s">
-        <v>110</v>
+        <v>45</v>
       </c>
     </row>
     <row r="321" spans="2:5" x14ac:dyDescent="0.35">
       <c r="B321" t="s">
-        <v>374</v>
+        <v>372</v>
       </c>
       <c r="E321" t="s">
-        <v>112</v>
+        <v>57</v>
       </c>
     </row>
     <row r="322" spans="2:5" x14ac:dyDescent="0.35">
       <c r="B322" t="s">
-        <v>375</v>
+        <v>373</v>
       </c>
       <c r="E322" t="s">
-        <v>49</v>
+        <v>55</v>
       </c>
     </row>
     <row r="323" spans="2:5" x14ac:dyDescent="0.35">
       <c r="B323" t="s">
-        <v>376</v>
+        <v>374</v>
       </c>
       <c r="E323" t="s">
-        <v>61</v>
+        <v>50</v>
       </c>
     </row>
     <row r="324" spans="2:5" x14ac:dyDescent="0.35">
       <c r="B324" t="s">
-        <v>377</v>
+        <v>375</v>
       </c>
       <c r="E324" t="s">
-        <v>59</v>
+        <v>60</v>
       </c>
     </row>
     <row r="325" spans="2:5" x14ac:dyDescent="0.35">
       <c r="B325" t="s">
-        <v>378</v>
+        <v>376</v>
       </c>
       <c r="E325" t="s">
-        <v>54</v>
+        <v>87</v>
       </c>
     </row>
     <row r="326" spans="2:5" x14ac:dyDescent="0.35">
       <c r="B326" t="s">
-        <v>379</v>
+        <v>377</v>
       </c>
       <c r="E326" t="s">
         <v>64</v>
@@ -6279,47 +6243,47 @@
     </row>
     <row r="327" spans="2:5" x14ac:dyDescent="0.35">
       <c r="B327" t="s">
-        <v>380</v>
+        <v>378</v>
       </c>
       <c r="E327" t="s">
-        <v>91</v>
+        <v>82</v>
       </c>
     </row>
     <row r="328" spans="2:5" x14ac:dyDescent="0.35">
       <c r="B328" t="s">
-        <v>381</v>
+        <v>379</v>
       </c>
       <c r="E328" t="s">
-        <v>68</v>
+        <v>90</v>
       </c>
     </row>
     <row r="329" spans="2:5" x14ac:dyDescent="0.35">
       <c r="B329" t="s">
-        <v>382</v>
+        <v>380</v>
       </c>
       <c r="E329" t="s">
-        <v>86</v>
+        <v>74</v>
       </c>
     </row>
     <row r="330" spans="2:5" x14ac:dyDescent="0.35">
       <c r="B330" t="s">
-        <v>383</v>
+        <v>381</v>
       </c>
       <c r="E330" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
     </row>
     <row r="331" spans="2:5" x14ac:dyDescent="0.35">
       <c r="B331" t="s">
-        <v>384</v>
+        <v>382</v>
       </c>
       <c r="E331" t="s">
-        <v>78</v>
+        <v>95</v>
       </c>
     </row>
     <row r="332" spans="2:5" x14ac:dyDescent="0.35">
       <c r="B332" t="s">
-        <v>385</v>
+        <v>383</v>
       </c>
       <c r="E332" t="s">
         <v>97</v>
@@ -6327,7 +6291,7 @@
     </row>
     <row r="333" spans="2:5" x14ac:dyDescent="0.35">
       <c r="B333" t="s">
-        <v>386</v>
+        <v>384</v>
       </c>
       <c r="E333" t="s">
         <v>99</v>
@@ -6335,31 +6299,31 @@
     </row>
     <row r="334" spans="2:5" x14ac:dyDescent="0.35">
       <c r="B334" t="s">
-        <v>387</v>
+        <v>385</v>
       </c>
       <c r="E334" t="s">
-        <v>101</v>
+        <v>79</v>
       </c>
     </row>
     <row r="335" spans="2:5" x14ac:dyDescent="0.35">
       <c r="B335" t="s">
-        <v>388</v>
+        <v>386</v>
       </c>
       <c r="E335" t="s">
-        <v>103</v>
+        <v>102</v>
       </c>
     </row>
     <row r="336" spans="2:5" x14ac:dyDescent="0.35">
       <c r="B336" t="s">
-        <v>389</v>
+        <v>387</v>
       </c>
       <c r="E336" t="s">
-        <v>83</v>
+        <v>104</v>
       </c>
     </row>
     <row r="337" spans="2:5" x14ac:dyDescent="0.35">
       <c r="B337" t="s">
-        <v>390</v>
+        <v>388</v>
       </c>
       <c r="E337" t="s">
         <v>106</v>
@@ -6367,7 +6331,7 @@
     </row>
     <row r="338" spans="2:5" x14ac:dyDescent="0.35">
       <c r="B338" t="s">
-        <v>391</v>
+        <v>389</v>
       </c>
       <c r="E338" t="s">
         <v>108</v>
@@ -6375,55 +6339,55 @@
     </row>
     <row r="339" spans="2:5" x14ac:dyDescent="0.35">
       <c r="B339" t="s">
-        <v>392</v>
+        <v>390</v>
       </c>
       <c r="E339" t="s">
-        <v>110</v>
+        <v>45</v>
       </c>
     </row>
     <row r="340" spans="2:5" x14ac:dyDescent="0.35">
       <c r="B340" t="s">
-        <v>393</v>
+        <v>391</v>
       </c>
       <c r="E340" t="s">
-        <v>112</v>
+        <v>57</v>
       </c>
     </row>
     <row r="341" spans="2:5" x14ac:dyDescent="0.35">
       <c r="B341" t="s">
-        <v>394</v>
+        <v>392</v>
       </c>
       <c r="E341" t="s">
-        <v>49</v>
+        <v>55</v>
       </c>
     </row>
     <row r="342" spans="2:5" x14ac:dyDescent="0.35">
       <c r="B342" t="s">
-        <v>395</v>
+        <v>393</v>
       </c>
       <c r="E342" t="s">
-        <v>61</v>
+        <v>50</v>
       </c>
     </row>
     <row r="343" spans="2:5" x14ac:dyDescent="0.35">
       <c r="B343" t="s">
-        <v>396</v>
+        <v>394</v>
       </c>
       <c r="E343" t="s">
-        <v>59</v>
+        <v>60</v>
       </c>
     </row>
     <row r="344" spans="2:5" x14ac:dyDescent="0.35">
       <c r="B344" t="s">
-        <v>397</v>
+        <v>395</v>
       </c>
       <c r="E344" t="s">
-        <v>54</v>
+        <v>87</v>
       </c>
     </row>
     <row r="345" spans="2:5" x14ac:dyDescent="0.35">
       <c r="B345" t="s">
-        <v>398</v>
+        <v>396</v>
       </c>
       <c r="E345" t="s">
         <v>64</v>
@@ -6431,47 +6395,47 @@
     </row>
     <row r="346" spans="2:5" x14ac:dyDescent="0.35">
       <c r="B346" t="s">
-        <v>399</v>
+        <v>397</v>
       </c>
       <c r="E346" t="s">
-        <v>91</v>
+        <v>82</v>
       </c>
     </row>
     <row r="347" spans="2:5" x14ac:dyDescent="0.35">
       <c r="B347" t="s">
-        <v>400</v>
+        <v>398</v>
       </c>
       <c r="E347" t="s">
-        <v>68</v>
+        <v>90</v>
       </c>
     </row>
     <row r="348" spans="2:5" x14ac:dyDescent="0.35">
       <c r="B348" t="s">
-        <v>401</v>
+        <v>399</v>
       </c>
       <c r="E348" t="s">
-        <v>86</v>
+        <v>74</v>
       </c>
     </row>
     <row r="349" spans="2:5" x14ac:dyDescent="0.35">
       <c r="B349" t="s">
-        <v>402</v>
+        <v>400</v>
       </c>
       <c r="E349" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
     </row>
     <row r="350" spans="2:5" x14ac:dyDescent="0.35">
       <c r="B350" t="s">
-        <v>403</v>
+        <v>401</v>
       </c>
       <c r="E350" t="s">
-        <v>78</v>
+        <v>95</v>
       </c>
     </row>
     <row r="351" spans="2:5" x14ac:dyDescent="0.35">
       <c r="B351" t="s">
-        <v>404</v>
+        <v>402</v>
       </c>
       <c r="E351" t="s">
         <v>97</v>
@@ -6479,7 +6443,7 @@
     </row>
     <row r="352" spans="2:5" x14ac:dyDescent="0.35">
       <c r="B352" t="s">
-        <v>405</v>
+        <v>403</v>
       </c>
       <c r="E352" t="s">
         <v>99</v>
@@ -6487,31 +6451,31 @@
     </row>
     <row r="353" spans="2:5" x14ac:dyDescent="0.35">
       <c r="B353" t="s">
-        <v>406</v>
+        <v>404</v>
       </c>
       <c r="E353" t="s">
-        <v>101</v>
+        <v>79</v>
       </c>
     </row>
     <row r="354" spans="2:5" x14ac:dyDescent="0.35">
       <c r="B354" t="s">
-        <v>407</v>
+        <v>405</v>
       </c>
       <c r="E354" t="s">
-        <v>103</v>
+        <v>102</v>
       </c>
     </row>
     <row r="355" spans="2:5" x14ac:dyDescent="0.35">
       <c r="B355" t="s">
-        <v>408</v>
+        <v>406</v>
       </c>
       <c r="E355" t="s">
-        <v>83</v>
+        <v>104</v>
       </c>
     </row>
     <row r="356" spans="2:5" x14ac:dyDescent="0.35">
       <c r="B356" t="s">
-        <v>409</v>
+        <v>407</v>
       </c>
       <c r="E356" t="s">
         <v>106</v>
@@ -6519,7 +6483,7 @@
     </row>
     <row r="357" spans="2:5" x14ac:dyDescent="0.35">
       <c r="B357" t="s">
-        <v>410</v>
+        <v>408</v>
       </c>
       <c r="E357" t="s">
         <v>108</v>
@@ -6527,55 +6491,55 @@
     </row>
     <row r="358" spans="2:5" x14ac:dyDescent="0.35">
       <c r="B358" t="s">
-        <v>411</v>
+        <v>409</v>
       </c>
       <c r="E358" t="s">
-        <v>110</v>
+        <v>45</v>
       </c>
     </row>
     <row r="359" spans="2:5" x14ac:dyDescent="0.35">
       <c r="B359" t="s">
-        <v>412</v>
+        <v>410</v>
       </c>
       <c r="E359" t="s">
-        <v>112</v>
+        <v>57</v>
       </c>
     </row>
     <row r="360" spans="2:5" x14ac:dyDescent="0.35">
       <c r="B360" t="s">
-        <v>413</v>
+        <v>411</v>
       </c>
       <c r="E360" t="s">
-        <v>49</v>
+        <v>55</v>
       </c>
     </row>
     <row r="361" spans="2:5" x14ac:dyDescent="0.35">
       <c r="B361" t="s">
-        <v>414</v>
+        <v>412</v>
       </c>
       <c r="E361" t="s">
-        <v>61</v>
+        <v>50</v>
       </c>
     </row>
     <row r="362" spans="2:5" x14ac:dyDescent="0.35">
       <c r="B362" t="s">
-        <v>415</v>
+        <v>413</v>
       </c>
       <c r="E362" t="s">
-        <v>59</v>
+        <v>60</v>
       </c>
     </row>
     <row r="363" spans="2:5" x14ac:dyDescent="0.35">
       <c r="B363" t="s">
-        <v>416</v>
+        <v>414</v>
       </c>
       <c r="E363" t="s">
-        <v>54</v>
+        <v>87</v>
       </c>
     </row>
     <row r="364" spans="2:5" x14ac:dyDescent="0.35">
       <c r="B364" t="s">
-        <v>417</v>
+        <v>415</v>
       </c>
       <c r="E364" t="s">
         <v>64</v>
@@ -6583,47 +6547,47 @@
     </row>
     <row r="365" spans="2:5" x14ac:dyDescent="0.35">
       <c r="B365" t="s">
-        <v>418</v>
+        <v>416</v>
       </c>
       <c r="E365" t="s">
-        <v>91</v>
+        <v>82</v>
       </c>
     </row>
     <row r="366" spans="2:5" x14ac:dyDescent="0.35">
       <c r="B366" t="s">
-        <v>419</v>
+        <v>417</v>
       </c>
       <c r="E366" t="s">
-        <v>68</v>
+        <v>90</v>
       </c>
     </row>
     <row r="367" spans="2:5" x14ac:dyDescent="0.35">
       <c r="B367" t="s">
-        <v>420</v>
+        <v>418</v>
       </c>
       <c r="E367" t="s">
-        <v>86</v>
+        <v>74</v>
       </c>
     </row>
     <row r="368" spans="2:5" x14ac:dyDescent="0.35">
       <c r="B368" t="s">
-        <v>421</v>
+        <v>419</v>
       </c>
       <c r="E368" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
     </row>
     <row r="369" spans="2:5" x14ac:dyDescent="0.35">
       <c r="B369" t="s">
-        <v>422</v>
+        <v>420</v>
       </c>
       <c r="E369" t="s">
-        <v>78</v>
+        <v>95</v>
       </c>
     </row>
     <row r="370" spans="2:5" x14ac:dyDescent="0.35">
       <c r="B370" t="s">
-        <v>423</v>
+        <v>421</v>
       </c>
       <c r="E370" t="s">
         <v>97</v>
@@ -6631,7 +6595,7 @@
     </row>
     <row r="371" spans="2:5" x14ac:dyDescent="0.35">
       <c r="B371" t="s">
-        <v>424</v>
+        <v>422</v>
       </c>
       <c r="E371" t="s">
         <v>99</v>
@@ -6639,31 +6603,31 @@
     </row>
     <row r="372" spans="2:5" x14ac:dyDescent="0.35">
       <c r="B372" t="s">
-        <v>425</v>
+        <v>423</v>
       </c>
       <c r="E372" t="s">
-        <v>101</v>
+        <v>79</v>
       </c>
     </row>
     <row r="373" spans="2:5" x14ac:dyDescent="0.35">
       <c r="B373" t="s">
-        <v>426</v>
+        <v>424</v>
       </c>
       <c r="E373" t="s">
-        <v>103</v>
+        <v>102</v>
       </c>
     </row>
     <row r="374" spans="2:5" x14ac:dyDescent="0.35">
       <c r="B374" t="s">
-        <v>427</v>
+        <v>425</v>
       </c>
       <c r="E374" t="s">
-        <v>83</v>
+        <v>104</v>
       </c>
     </row>
     <row r="375" spans="2:5" x14ac:dyDescent="0.35">
       <c r="B375" t="s">
-        <v>428</v>
+        <v>426</v>
       </c>
       <c r="E375" t="s">
         <v>106</v>
@@ -6671,7 +6635,7 @@
     </row>
     <row r="376" spans="2:5" x14ac:dyDescent="0.35">
       <c r="B376" t="s">
-        <v>429</v>
+        <v>427</v>
       </c>
       <c r="E376" t="s">
         <v>108</v>
@@ -6679,55 +6643,55 @@
     </row>
     <row r="377" spans="2:5" x14ac:dyDescent="0.35">
       <c r="B377" t="s">
-        <v>430</v>
+        <v>428</v>
       </c>
       <c r="E377" t="s">
-        <v>110</v>
+        <v>45</v>
       </c>
     </row>
     <row r="378" spans="2:5" x14ac:dyDescent="0.35">
       <c r="B378" t="s">
-        <v>431</v>
+        <v>429</v>
       </c>
       <c r="E378" t="s">
-        <v>112</v>
+        <v>57</v>
       </c>
     </row>
     <row r="379" spans="2:5" x14ac:dyDescent="0.35">
       <c r="B379" t="s">
-        <v>432</v>
+        <v>430</v>
       </c>
       <c r="E379" t="s">
-        <v>49</v>
+        <v>55</v>
       </c>
     </row>
     <row r="380" spans="2:5" x14ac:dyDescent="0.35">
       <c r="B380" t="s">
-        <v>433</v>
+        <v>431</v>
       </c>
       <c r="E380" t="s">
-        <v>61</v>
+        <v>50</v>
       </c>
     </row>
     <row r="381" spans="2:5" x14ac:dyDescent="0.35">
       <c r="B381" t="s">
-        <v>434</v>
+        <v>432</v>
       </c>
       <c r="E381" t="s">
-        <v>59</v>
+        <v>60</v>
       </c>
     </row>
     <row r="382" spans="2:5" x14ac:dyDescent="0.35">
       <c r="B382" t="s">
-        <v>435</v>
+        <v>433</v>
       </c>
       <c r="E382" t="s">
-        <v>54</v>
+        <v>87</v>
       </c>
     </row>
     <row r="383" spans="2:5" x14ac:dyDescent="0.35">
       <c r="B383" t="s">
-        <v>436</v>
+        <v>434</v>
       </c>
       <c r="E383" t="s">
         <v>64</v>
@@ -6735,47 +6699,47 @@
     </row>
     <row r="384" spans="2:5" x14ac:dyDescent="0.35">
       <c r="B384" t="s">
-        <v>437</v>
+        <v>435</v>
       </c>
       <c r="E384" t="s">
-        <v>91</v>
+        <v>82</v>
       </c>
     </row>
     <row r="385" spans="2:5" x14ac:dyDescent="0.35">
       <c r="B385" t="s">
-        <v>438</v>
+        <v>436</v>
       </c>
       <c r="E385" t="s">
-        <v>68</v>
+        <v>90</v>
       </c>
     </row>
     <row r="386" spans="2:5" x14ac:dyDescent="0.35">
       <c r="B386" t="s">
-        <v>439</v>
+        <v>437</v>
       </c>
       <c r="E386" t="s">
-        <v>86</v>
+        <v>74</v>
       </c>
     </row>
     <row r="387" spans="2:5" x14ac:dyDescent="0.35">
       <c r="B387" t="s">
-        <v>440</v>
+        <v>438</v>
       </c>
       <c r="E387" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
     </row>
     <row r="388" spans="2:5" x14ac:dyDescent="0.35">
       <c r="B388" t="s">
-        <v>441</v>
+        <v>439</v>
       </c>
       <c r="E388" t="s">
-        <v>78</v>
+        <v>95</v>
       </c>
     </row>
     <row r="389" spans="2:5" x14ac:dyDescent="0.35">
       <c r="B389" t="s">
-        <v>442</v>
+        <v>440</v>
       </c>
       <c r="E389" t="s">
         <v>97</v>
@@ -6783,7 +6747,7 @@
     </row>
     <row r="390" spans="2:5" x14ac:dyDescent="0.35">
       <c r="B390" t="s">
-        <v>443</v>
+        <v>441</v>
       </c>
       <c r="E390" t="s">
         <v>99</v>
@@ -6791,31 +6755,31 @@
     </row>
     <row r="391" spans="2:5" x14ac:dyDescent="0.35">
       <c r="B391" t="s">
-        <v>444</v>
+        <v>442</v>
       </c>
       <c r="E391" t="s">
-        <v>101</v>
+        <v>79</v>
       </c>
     </row>
     <row r="392" spans="2:5" x14ac:dyDescent="0.35">
       <c r="B392" t="s">
-        <v>445</v>
+        <v>443</v>
       </c>
       <c r="E392" t="s">
-        <v>103</v>
+        <v>102</v>
       </c>
     </row>
     <row r="393" spans="2:5" x14ac:dyDescent="0.35">
       <c r="B393" t="s">
-        <v>446</v>
+        <v>444</v>
       </c>
       <c r="E393" t="s">
-        <v>83</v>
+        <v>104</v>
       </c>
     </row>
     <row r="394" spans="2:5" x14ac:dyDescent="0.35">
       <c r="B394" t="s">
-        <v>447</v>
+        <v>445</v>
       </c>
       <c r="E394" t="s">
         <v>106</v>
@@ -6823,7 +6787,7 @@
     </row>
     <row r="395" spans="2:5" x14ac:dyDescent="0.35">
       <c r="B395" t="s">
-        <v>448</v>
+        <v>446</v>
       </c>
       <c r="E395" t="s">
         <v>108</v>
@@ -6831,55 +6795,55 @@
     </row>
     <row r="396" spans="2:5" x14ac:dyDescent="0.35">
       <c r="B396" t="s">
-        <v>449</v>
+        <v>447</v>
       </c>
       <c r="E396" t="s">
-        <v>110</v>
+        <v>45</v>
       </c>
     </row>
     <row r="397" spans="2:5" x14ac:dyDescent="0.35">
       <c r="B397" t="s">
-        <v>450</v>
+        <v>448</v>
       </c>
       <c r="E397" t="s">
-        <v>112</v>
+        <v>57</v>
       </c>
     </row>
     <row r="398" spans="2:5" x14ac:dyDescent="0.35">
       <c r="B398" t="s">
-        <v>451</v>
+        <v>449</v>
       </c>
       <c r="E398" t="s">
-        <v>49</v>
+        <v>55</v>
       </c>
     </row>
     <row r="399" spans="2:5" x14ac:dyDescent="0.35">
       <c r="B399" t="s">
-        <v>452</v>
+        <v>450</v>
       </c>
       <c r="E399" t="s">
-        <v>61</v>
+        <v>50</v>
       </c>
     </row>
     <row r="400" spans="2:5" x14ac:dyDescent="0.35">
       <c r="B400" t="s">
-        <v>453</v>
+        <v>451</v>
       </c>
       <c r="E400" t="s">
-        <v>59</v>
+        <v>60</v>
       </c>
     </row>
     <row r="401" spans="2:5" x14ac:dyDescent="0.35">
       <c r="B401" t="s">
-        <v>454</v>
+        <v>452</v>
       </c>
       <c r="E401" t="s">
-        <v>54</v>
+        <v>87</v>
       </c>
     </row>
     <row r="402" spans="2:5" x14ac:dyDescent="0.35">
       <c r="B402" t="s">
-        <v>455</v>
+        <v>453</v>
       </c>
       <c r="E402" t="s">
         <v>64</v>
@@ -6887,47 +6851,47 @@
     </row>
     <row r="403" spans="2:5" x14ac:dyDescent="0.35">
       <c r="B403" t="s">
-        <v>456</v>
+        <v>454</v>
       </c>
       <c r="E403" t="s">
-        <v>91</v>
+        <v>82</v>
       </c>
     </row>
     <row r="404" spans="2:5" x14ac:dyDescent="0.35">
       <c r="B404" t="s">
-        <v>457</v>
+        <v>455</v>
       </c>
       <c r="E404" t="s">
-        <v>68</v>
+        <v>90</v>
       </c>
     </row>
     <row r="405" spans="2:5" x14ac:dyDescent="0.35">
       <c r="B405" t="s">
-        <v>458</v>
+        <v>456</v>
       </c>
       <c r="E405" t="s">
-        <v>86</v>
+        <v>74</v>
       </c>
     </row>
     <row r="406" spans="2:5" x14ac:dyDescent="0.35">
       <c r="B406" t="s">
-        <v>459</v>
+        <v>457</v>
       </c>
       <c r="E406" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
     </row>
     <row r="407" spans="2:5" x14ac:dyDescent="0.35">
       <c r="B407" t="s">
-        <v>460</v>
+        <v>458</v>
       </c>
       <c r="E407" t="s">
-        <v>78</v>
+        <v>95</v>
       </c>
     </row>
     <row r="408" spans="2:5" x14ac:dyDescent="0.35">
       <c r="B408" t="s">
-        <v>461</v>
+        <v>459</v>
       </c>
       <c r="E408" t="s">
         <v>97</v>
@@ -6935,7 +6899,7 @@
     </row>
     <row r="409" spans="2:5" x14ac:dyDescent="0.35">
       <c r="B409" t="s">
-        <v>462</v>
+        <v>460</v>
       </c>
       <c r="E409" t="s">
         <v>99</v>
@@ -6943,31 +6907,31 @@
     </row>
     <row r="410" spans="2:5" x14ac:dyDescent="0.35">
       <c r="B410" t="s">
-        <v>463</v>
+        <v>461</v>
       </c>
       <c r="E410" t="s">
-        <v>101</v>
+        <v>79</v>
       </c>
     </row>
     <row r="411" spans="2:5" x14ac:dyDescent="0.35">
       <c r="B411" t="s">
-        <v>464</v>
+        <v>462</v>
       </c>
       <c r="E411" t="s">
-        <v>103</v>
+        <v>102</v>
       </c>
     </row>
     <row r="412" spans="2:5" x14ac:dyDescent="0.35">
       <c r="B412" t="s">
-        <v>465</v>
+        <v>463</v>
       </c>
       <c r="E412" t="s">
-        <v>83</v>
+        <v>104</v>
       </c>
     </row>
     <row r="413" spans="2:5" x14ac:dyDescent="0.35">
       <c r="B413" t="s">
-        <v>466</v>
+        <v>464</v>
       </c>
       <c r="E413" t="s">
         <v>106</v>
@@ -6975,7 +6939,7 @@
     </row>
     <row r="414" spans="2:5" x14ac:dyDescent="0.35">
       <c r="B414" t="s">
-        <v>467</v>
+        <v>465</v>
       </c>
       <c r="E414" t="s">
         <v>108</v>
@@ -6983,55 +6947,55 @@
     </row>
     <row r="415" spans="2:5" x14ac:dyDescent="0.35">
       <c r="B415" t="s">
-        <v>468</v>
+        <v>466</v>
       </c>
       <c r="E415" t="s">
-        <v>110</v>
+        <v>45</v>
       </c>
     </row>
     <row r="416" spans="2:5" x14ac:dyDescent="0.35">
       <c r="B416" t="s">
-        <v>469</v>
+        <v>467</v>
       </c>
       <c r="E416" t="s">
-        <v>112</v>
+        <v>57</v>
       </c>
     </row>
     <row r="417" spans="2:5" x14ac:dyDescent="0.35">
       <c r="B417" t="s">
-        <v>470</v>
+        <v>468</v>
       </c>
       <c r="E417" t="s">
-        <v>49</v>
+        <v>55</v>
       </c>
     </row>
     <row r="418" spans="2:5" x14ac:dyDescent="0.35">
       <c r="B418" t="s">
-        <v>471</v>
+        <v>469</v>
       </c>
       <c r="E418" t="s">
-        <v>61</v>
+        <v>50</v>
       </c>
     </row>
     <row r="419" spans="2:5" x14ac:dyDescent="0.35">
       <c r="B419" t="s">
-        <v>472</v>
+        <v>470</v>
       </c>
       <c r="E419" t="s">
-        <v>59</v>
+        <v>60</v>
       </c>
     </row>
     <row r="420" spans="2:5" x14ac:dyDescent="0.35">
       <c r="B420" t="s">
-        <v>473</v>
+        <v>471</v>
       </c>
       <c r="E420" t="s">
-        <v>54</v>
+        <v>87</v>
       </c>
     </row>
     <row r="421" spans="2:5" x14ac:dyDescent="0.35">
       <c r="B421" t="s">
-        <v>474</v>
+        <v>472</v>
       </c>
       <c r="E421" t="s">
         <v>64</v>
@@ -7039,47 +7003,47 @@
     </row>
     <row r="422" spans="2:5" x14ac:dyDescent="0.35">
       <c r="B422" t="s">
-        <v>475</v>
+        <v>473</v>
       </c>
       <c r="E422" t="s">
-        <v>91</v>
+        <v>82</v>
       </c>
     </row>
     <row r="423" spans="2:5" x14ac:dyDescent="0.35">
       <c r="B423" t="s">
-        <v>476</v>
+        <v>474</v>
       </c>
       <c r="E423" t="s">
-        <v>68</v>
+        <v>90</v>
       </c>
     </row>
     <row r="424" spans="2:5" x14ac:dyDescent="0.35">
       <c r="B424" t="s">
-        <v>477</v>
+        <v>475</v>
       </c>
       <c r="E424" t="s">
-        <v>86</v>
+        <v>74</v>
       </c>
     </row>
     <row r="425" spans="2:5" x14ac:dyDescent="0.35">
       <c r="B425" t="s">
-        <v>478</v>
+        <v>476</v>
       </c>
       <c r="E425" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
     </row>
     <row r="426" spans="2:5" x14ac:dyDescent="0.35">
       <c r="B426" t="s">
-        <v>479</v>
+        <v>477</v>
       </c>
       <c r="E426" t="s">
-        <v>78</v>
+        <v>95</v>
       </c>
     </row>
     <row r="427" spans="2:5" x14ac:dyDescent="0.35">
       <c r="B427" t="s">
-        <v>480</v>
+        <v>478</v>
       </c>
       <c r="E427" t="s">
         <v>97</v>
@@ -7087,7 +7051,7 @@
     </row>
     <row r="428" spans="2:5" x14ac:dyDescent="0.35">
       <c r="B428" t="s">
-        <v>481</v>
+        <v>479</v>
       </c>
       <c r="E428" t="s">
         <v>99</v>
@@ -7095,31 +7059,31 @@
     </row>
     <row r="429" spans="2:5" x14ac:dyDescent="0.35">
       <c r="B429" t="s">
-        <v>482</v>
+        <v>480</v>
       </c>
       <c r="E429" t="s">
-        <v>101</v>
+        <v>79</v>
       </c>
     </row>
     <row r="430" spans="2:5" x14ac:dyDescent="0.35">
       <c r="B430" t="s">
-        <v>483</v>
+        <v>481</v>
       </c>
       <c r="E430" t="s">
-        <v>103</v>
+        <v>102</v>
       </c>
     </row>
     <row r="431" spans="2:5" x14ac:dyDescent="0.35">
       <c r="B431" t="s">
-        <v>484</v>
+        <v>482</v>
       </c>
       <c r="E431" t="s">
-        <v>83</v>
+        <v>104</v>
       </c>
     </row>
     <row r="432" spans="2:5" x14ac:dyDescent="0.35">
       <c r="B432" t="s">
-        <v>485</v>
+        <v>483</v>
       </c>
       <c r="E432" t="s">
         <v>106</v>
@@ -7127,7 +7091,7 @@
     </row>
     <row r="433" spans="2:5" x14ac:dyDescent="0.35">
       <c r="B433" t="s">
-        <v>486</v>
+        <v>484</v>
       </c>
       <c r="E433" t="s">
         <v>108</v>
@@ -7135,87 +7099,87 @@
     </row>
     <row r="434" spans="2:5" x14ac:dyDescent="0.35">
       <c r="B434" t="s">
-        <v>487</v>
+        <v>485</v>
       </c>
       <c r="E434" t="s">
-        <v>110</v>
+        <v>45</v>
       </c>
     </row>
     <row r="435" spans="2:5" x14ac:dyDescent="0.35">
       <c r="B435" t="s">
-        <v>488</v>
+        <v>486</v>
       </c>
       <c r="E435" t="s">
-        <v>112</v>
+        <v>57</v>
       </c>
     </row>
     <row r="436" spans="2:5" x14ac:dyDescent="0.35">
       <c r="B436" t="s">
-        <v>489</v>
+        <v>487</v>
       </c>
       <c r="E436" t="s">
-        <v>49</v>
+        <v>55</v>
       </c>
     </row>
     <row r="437" spans="2:5" x14ac:dyDescent="0.35">
       <c r="B437" t="s">
-        <v>490</v>
+        <v>488</v>
       </c>
       <c r="E437" t="s">
-        <v>61</v>
+        <v>50</v>
       </c>
     </row>
     <row r="438" spans="2:5" x14ac:dyDescent="0.35">
       <c r="B438" t="s">
-        <v>491</v>
+        <v>489</v>
       </c>
       <c r="E438" t="s">
-        <v>59</v>
+        <v>87</v>
       </c>
     </row>
     <row r="439" spans="2:5" x14ac:dyDescent="0.35">
       <c r="B439" t="s">
-        <v>492</v>
+        <v>490</v>
       </c>
       <c r="E439" t="s">
-        <v>54</v>
+        <v>82</v>
       </c>
     </row>
     <row r="440" spans="2:5" x14ac:dyDescent="0.35">
       <c r="B440" t="s">
-        <v>493</v>
+        <v>491</v>
       </c>
       <c r="E440" t="s">
-        <v>91</v>
+        <v>90</v>
       </c>
     </row>
     <row r="441" spans="2:5" x14ac:dyDescent="0.35">
       <c r="B441" t="s">
-        <v>494</v>
+        <v>492</v>
       </c>
       <c r="E441" t="s">
-        <v>86</v>
+        <v>74</v>
       </c>
     </row>
     <row r="442" spans="2:5" x14ac:dyDescent="0.35">
       <c r="B442" t="s">
-        <v>495</v>
+        <v>493</v>
       </c>
       <c r="E442" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
     </row>
     <row r="443" spans="2:5" x14ac:dyDescent="0.35">
       <c r="B443" t="s">
-        <v>496</v>
+        <v>494</v>
       </c>
       <c r="E443" t="s">
-        <v>78</v>
+        <v>95</v>
       </c>
     </row>
     <row r="444" spans="2:5" x14ac:dyDescent="0.35">
       <c r="B444" t="s">
-        <v>497</v>
+        <v>495</v>
       </c>
       <c r="E444" t="s">
         <v>97</v>
@@ -7223,7 +7187,7 @@
     </row>
     <row r="445" spans="2:5" x14ac:dyDescent="0.35">
       <c r="B445" t="s">
-        <v>498</v>
+        <v>496</v>
       </c>
       <c r="E445" t="s">
         <v>99</v>
@@ -7231,31 +7195,31 @@
     </row>
     <row r="446" spans="2:5" x14ac:dyDescent="0.35">
       <c r="B446" t="s">
-        <v>499</v>
+        <v>497</v>
       </c>
       <c r="E446" t="s">
-        <v>101</v>
+        <v>79</v>
       </c>
     </row>
     <row r="447" spans="2:5" x14ac:dyDescent="0.35">
       <c r="B447" t="s">
-        <v>500</v>
+        <v>498</v>
       </c>
       <c r="E447" t="s">
-        <v>103</v>
+        <v>102</v>
       </c>
     </row>
     <row r="448" spans="2:5" x14ac:dyDescent="0.35">
       <c r="B448" t="s">
-        <v>501</v>
+        <v>499</v>
       </c>
       <c r="E448" t="s">
-        <v>83</v>
+        <v>104</v>
       </c>
     </row>
     <row r="449" spans="2:5" x14ac:dyDescent="0.35">
       <c r="B449" t="s">
-        <v>502</v>
+        <v>500</v>
       </c>
       <c r="E449" t="s">
         <v>106</v>
@@ -7263,7 +7227,7 @@
     </row>
     <row r="450" spans="2:5" x14ac:dyDescent="0.35">
       <c r="B450" t="s">
-        <v>503</v>
+        <v>501</v>
       </c>
       <c r="E450" t="s">
         <v>108</v>
@@ -7271,55 +7235,55 @@
     </row>
     <row r="451" spans="2:5" x14ac:dyDescent="0.35">
       <c r="B451" t="s">
-        <v>504</v>
+        <v>502</v>
       </c>
       <c r="E451" t="s">
-        <v>110</v>
+        <v>45</v>
       </c>
     </row>
     <row r="452" spans="2:5" x14ac:dyDescent="0.35">
       <c r="B452" t="s">
-        <v>505</v>
+        <v>503</v>
       </c>
       <c r="E452" t="s">
-        <v>112</v>
+        <v>57</v>
       </c>
     </row>
     <row r="453" spans="2:5" x14ac:dyDescent="0.35">
       <c r="B453" t="s">
-        <v>506</v>
+        <v>504</v>
       </c>
       <c r="E453" t="s">
-        <v>49</v>
+        <v>55</v>
       </c>
     </row>
     <row r="454" spans="2:5" x14ac:dyDescent="0.35">
       <c r="B454" t="s">
-        <v>507</v>
+        <v>505</v>
       </c>
       <c r="E454" t="s">
-        <v>61</v>
+        <v>50</v>
       </c>
     </row>
     <row r="455" spans="2:5" x14ac:dyDescent="0.35">
       <c r="B455" t="s">
-        <v>508</v>
+        <v>506</v>
       </c>
       <c r="E455" t="s">
-        <v>59</v>
+        <v>60</v>
       </c>
     </row>
     <row r="456" spans="2:5" x14ac:dyDescent="0.35">
       <c r="B456" t="s">
-        <v>509</v>
+        <v>507</v>
       </c>
       <c r="E456" t="s">
-        <v>54</v>
+        <v>87</v>
       </c>
     </row>
     <row r="457" spans="2:5" x14ac:dyDescent="0.35">
       <c r="B457" t="s">
-        <v>510</v>
+        <v>508</v>
       </c>
       <c r="E457" t="s">
         <v>64</v>
@@ -7327,47 +7291,47 @@
     </row>
     <row r="458" spans="2:5" x14ac:dyDescent="0.35">
       <c r="B458" t="s">
-        <v>511</v>
+        <v>509</v>
       </c>
       <c r="E458" t="s">
-        <v>91</v>
+        <v>82</v>
       </c>
     </row>
     <row r="459" spans="2:5" x14ac:dyDescent="0.35">
       <c r="B459" t="s">
-        <v>512</v>
+        <v>510</v>
       </c>
       <c r="E459" t="s">
-        <v>68</v>
+        <v>90</v>
       </c>
     </row>
     <row r="460" spans="2:5" x14ac:dyDescent="0.35">
       <c r="B460" t="s">
-        <v>513</v>
+        <v>511</v>
       </c>
       <c r="E460" t="s">
-        <v>86</v>
+        <v>74</v>
       </c>
     </row>
     <row r="461" spans="2:5" x14ac:dyDescent="0.35">
       <c r="B461" t="s">
-        <v>514</v>
+        <v>512</v>
       </c>
       <c r="E461" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
     </row>
     <row r="462" spans="2:5" x14ac:dyDescent="0.35">
       <c r="B462" t="s">
-        <v>515</v>
+        <v>513</v>
       </c>
       <c r="E462" t="s">
-        <v>78</v>
+        <v>95</v>
       </c>
     </row>
     <row r="463" spans="2:5" x14ac:dyDescent="0.35">
       <c r="B463" t="s">
-        <v>516</v>
+        <v>514</v>
       </c>
       <c r="E463" t="s">
         <v>97</v>
@@ -7375,7 +7339,7 @@
     </row>
     <row r="464" spans="2:5" x14ac:dyDescent="0.35">
       <c r="B464" t="s">
-        <v>517</v>
+        <v>515</v>
       </c>
       <c r="E464" t="s">
         <v>99</v>
@@ -7383,31 +7347,31 @@
     </row>
     <row r="465" spans="2:5" x14ac:dyDescent="0.35">
       <c r="B465" t="s">
-        <v>518</v>
+        <v>516</v>
       </c>
       <c r="E465" t="s">
-        <v>101</v>
+        <v>79</v>
       </c>
     </row>
     <row r="466" spans="2:5" x14ac:dyDescent="0.35">
       <c r="B466" t="s">
-        <v>519</v>
+        <v>517</v>
       </c>
       <c r="E466" t="s">
-        <v>103</v>
+        <v>102</v>
       </c>
     </row>
     <row r="467" spans="2:5" x14ac:dyDescent="0.35">
       <c r="B467" t="s">
-        <v>520</v>
+        <v>518</v>
       </c>
       <c r="E467" t="s">
-        <v>83</v>
+        <v>104</v>
       </c>
     </row>
     <row r="468" spans="2:5" x14ac:dyDescent="0.35">
       <c r="B468" t="s">
-        <v>521</v>
+        <v>519</v>
       </c>
       <c r="E468" t="s">
         <v>106</v>
@@ -7415,7 +7379,7 @@
     </row>
     <row r="469" spans="2:5" x14ac:dyDescent="0.35">
       <c r="B469" t="s">
-        <v>522</v>
+        <v>520</v>
       </c>
       <c r="E469" t="s">
         <v>108</v>
@@ -7423,55 +7387,55 @@
     </row>
     <row r="470" spans="2:5" x14ac:dyDescent="0.35">
       <c r="B470" t="s">
-        <v>523</v>
+        <v>521</v>
       </c>
       <c r="E470" t="s">
-        <v>110</v>
+        <v>45</v>
       </c>
     </row>
     <row r="471" spans="2:5" x14ac:dyDescent="0.35">
       <c r="B471" t="s">
-        <v>524</v>
+        <v>522</v>
       </c>
       <c r="E471" t="s">
-        <v>112</v>
+        <v>57</v>
       </c>
     </row>
     <row r="472" spans="2:5" x14ac:dyDescent="0.35">
       <c r="B472" t="s">
-        <v>525</v>
+        <v>523</v>
       </c>
       <c r="E472" t="s">
-        <v>49</v>
+        <v>55</v>
       </c>
     </row>
     <row r="473" spans="2:5" x14ac:dyDescent="0.35">
       <c r="B473" t="s">
-        <v>526</v>
+        <v>524</v>
       </c>
       <c r="E473" t="s">
-        <v>61</v>
+        <v>50</v>
       </c>
     </row>
     <row r="474" spans="2:5" x14ac:dyDescent="0.35">
       <c r="B474" t="s">
-        <v>527</v>
+        <v>525</v>
       </c>
       <c r="E474" t="s">
-        <v>59</v>
+        <v>60</v>
       </c>
     </row>
     <row r="475" spans="2:5" x14ac:dyDescent="0.35">
       <c r="B475" t="s">
-        <v>528</v>
+        <v>526</v>
       </c>
       <c r="E475" t="s">
-        <v>54</v>
+        <v>87</v>
       </c>
     </row>
     <row r="476" spans="2:5" x14ac:dyDescent="0.35">
       <c r="B476" t="s">
-        <v>529</v>
+        <v>527</v>
       </c>
       <c r="E476" t="s">
         <v>64</v>
@@ -7479,47 +7443,47 @@
     </row>
     <row r="477" spans="2:5" x14ac:dyDescent="0.35">
       <c r="B477" t="s">
-        <v>530</v>
+        <v>528</v>
       </c>
       <c r="E477" t="s">
-        <v>91</v>
+        <v>82</v>
       </c>
     </row>
     <row r="478" spans="2:5" x14ac:dyDescent="0.35">
       <c r="B478" t="s">
-        <v>531</v>
+        <v>529</v>
       </c>
       <c r="E478" t="s">
-        <v>68</v>
+        <v>90</v>
       </c>
     </row>
     <row r="479" spans="2:5" x14ac:dyDescent="0.35">
       <c r="B479" t="s">
-        <v>532</v>
+        <v>530</v>
       </c>
       <c r="E479" t="s">
-        <v>86</v>
+        <v>74</v>
       </c>
     </row>
     <row r="480" spans="2:5" x14ac:dyDescent="0.35">
       <c r="B480" t="s">
-        <v>533</v>
+        <v>531</v>
       </c>
       <c r="E480" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
     </row>
     <row r="481" spans="2:5" x14ac:dyDescent="0.35">
       <c r="B481" t="s">
-        <v>534</v>
+        <v>532</v>
       </c>
       <c r="E481" t="s">
-        <v>78</v>
+        <v>95</v>
       </c>
     </row>
     <row r="482" spans="2:5" x14ac:dyDescent="0.35">
       <c r="B482" t="s">
-        <v>535</v>
+        <v>533</v>
       </c>
       <c r="E482" t="s">
         <v>97</v>
@@ -7527,7 +7491,7 @@
     </row>
     <row r="483" spans="2:5" x14ac:dyDescent="0.35">
       <c r="B483" t="s">
-        <v>536</v>
+        <v>534</v>
       </c>
       <c r="E483" t="s">
         <v>99</v>
@@ -7535,31 +7499,31 @@
     </row>
     <row r="484" spans="2:5" x14ac:dyDescent="0.35">
       <c r="B484" t="s">
-        <v>537</v>
+        <v>535</v>
       </c>
       <c r="E484" t="s">
-        <v>101</v>
+        <v>79</v>
       </c>
     </row>
     <row r="485" spans="2:5" x14ac:dyDescent="0.35">
       <c r="B485" t="s">
-        <v>538</v>
+        <v>536</v>
       </c>
       <c r="E485" t="s">
-        <v>103</v>
+        <v>102</v>
       </c>
     </row>
     <row r="486" spans="2:5" x14ac:dyDescent="0.35">
       <c r="B486" t="s">
-        <v>539</v>
+        <v>537</v>
       </c>
       <c r="E486" t="s">
-        <v>83</v>
+        <v>104</v>
       </c>
     </row>
     <row r="487" spans="2:5" x14ac:dyDescent="0.35">
       <c r="B487" t="s">
-        <v>540</v>
+        <v>538</v>
       </c>
       <c r="E487" t="s">
         <v>106</v>
@@ -7567,7 +7531,7 @@
     </row>
     <row r="488" spans="2:5" x14ac:dyDescent="0.35">
       <c r="B488" t="s">
-        <v>541</v>
+        <v>539</v>
       </c>
       <c r="E488" t="s">
         <v>108</v>
@@ -7575,55 +7539,55 @@
     </row>
     <row r="489" spans="2:5" x14ac:dyDescent="0.35">
       <c r="B489" t="s">
-        <v>542</v>
+        <v>540</v>
       </c>
       <c r="E489" t="s">
-        <v>110</v>
+        <v>45</v>
       </c>
     </row>
     <row r="490" spans="2:5" x14ac:dyDescent="0.35">
       <c r="B490" t="s">
-        <v>543</v>
+        <v>541</v>
       </c>
       <c r="E490" t="s">
-        <v>112</v>
+        <v>57</v>
       </c>
     </row>
     <row r="491" spans="2:5" x14ac:dyDescent="0.35">
       <c r="B491" t="s">
-        <v>544</v>
+        <v>542</v>
       </c>
       <c r="E491" t="s">
-        <v>49</v>
+        <v>55</v>
       </c>
     </row>
     <row r="492" spans="2:5" x14ac:dyDescent="0.35">
       <c r="B492" t="s">
-        <v>545</v>
+        <v>543</v>
       </c>
       <c r="E492" t="s">
-        <v>61</v>
+        <v>50</v>
       </c>
     </row>
     <row r="493" spans="2:5" x14ac:dyDescent="0.35">
       <c r="B493" t="s">
-        <v>546</v>
+        <v>544</v>
       </c>
       <c r="E493" t="s">
-        <v>59</v>
+        <v>60</v>
       </c>
     </row>
     <row r="494" spans="2:5" x14ac:dyDescent="0.35">
       <c r="B494" t="s">
-        <v>547</v>
+        <v>545</v>
       </c>
       <c r="E494" t="s">
-        <v>54</v>
+        <v>87</v>
       </c>
     </row>
     <row r="495" spans="2:5" x14ac:dyDescent="0.35">
       <c r="B495" t="s">
-        <v>548</v>
+        <v>546</v>
       </c>
       <c r="E495" t="s">
         <v>64</v>
@@ -7631,47 +7595,47 @@
     </row>
     <row r="496" spans="2:5" x14ac:dyDescent="0.35">
       <c r="B496" t="s">
-        <v>549</v>
+        <v>547</v>
       </c>
       <c r="E496" t="s">
-        <v>91</v>
+        <v>82</v>
       </c>
     </row>
     <row r="497" spans="2:5" x14ac:dyDescent="0.35">
       <c r="B497" t="s">
-        <v>550</v>
+        <v>548</v>
       </c>
       <c r="E497" t="s">
-        <v>68</v>
+        <v>90</v>
       </c>
     </row>
     <row r="498" spans="2:5" x14ac:dyDescent="0.35">
       <c r="B498" t="s">
-        <v>551</v>
+        <v>549</v>
       </c>
       <c r="E498" t="s">
-        <v>86</v>
+        <v>74</v>
       </c>
     </row>
     <row r="499" spans="2:5" x14ac:dyDescent="0.35">
       <c r="B499" t="s">
-        <v>552</v>
+        <v>550</v>
       </c>
       <c r="E499" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
     </row>
     <row r="500" spans="2:5" x14ac:dyDescent="0.35">
       <c r="B500" t="s">
-        <v>553</v>
+        <v>551</v>
       </c>
       <c r="E500" t="s">
-        <v>78</v>
+        <v>95</v>
       </c>
     </row>
     <row r="501" spans="2:5" x14ac:dyDescent="0.35">
       <c r="B501" t="s">
-        <v>554</v>
+        <v>552</v>
       </c>
       <c r="E501" t="s">
         <v>97</v>
@@ -7679,7 +7643,7 @@
     </row>
     <row r="502" spans="2:5" x14ac:dyDescent="0.35">
       <c r="B502" t="s">
-        <v>555</v>
+        <v>553</v>
       </c>
       <c r="E502" t="s">
         <v>99</v>
@@ -7687,31 +7651,31 @@
     </row>
     <row r="503" spans="2:5" x14ac:dyDescent="0.35">
       <c r="B503" t="s">
-        <v>556</v>
+        <v>554</v>
       </c>
       <c r="E503" t="s">
-        <v>101</v>
+        <v>79</v>
       </c>
     </row>
     <row r="504" spans="2:5" x14ac:dyDescent="0.35">
       <c r="B504" t="s">
-        <v>557</v>
+        <v>555</v>
       </c>
       <c r="E504" t="s">
-        <v>103</v>
+        <v>102</v>
       </c>
     </row>
     <row r="505" spans="2:5" x14ac:dyDescent="0.35">
       <c r="B505" t="s">
-        <v>558</v>
+        <v>556</v>
       </c>
       <c r="E505" t="s">
-        <v>83</v>
+        <v>104</v>
       </c>
     </row>
     <row r="506" spans="2:5" x14ac:dyDescent="0.35">
       <c r="B506" t="s">
-        <v>559</v>
+        <v>557</v>
       </c>
       <c r="E506" t="s">
         <v>106</v>
@@ -7719,7 +7683,7 @@
     </row>
     <row r="507" spans="2:5" x14ac:dyDescent="0.35">
       <c r="B507" t="s">
-        <v>560</v>
+        <v>558</v>
       </c>
       <c r="E507" t="s">
         <v>108</v>
@@ -7727,55 +7691,55 @@
     </row>
     <row r="508" spans="2:5" x14ac:dyDescent="0.35">
       <c r="B508" t="s">
-        <v>561</v>
+        <v>559</v>
       </c>
       <c r="E508" t="s">
-        <v>110</v>
+        <v>45</v>
       </c>
     </row>
     <row r="509" spans="2:5" x14ac:dyDescent="0.35">
       <c r="B509" t="s">
-        <v>562</v>
+        <v>560</v>
       </c>
       <c r="E509" t="s">
-        <v>112</v>
+        <v>57</v>
       </c>
     </row>
     <row r="510" spans="2:5" x14ac:dyDescent="0.35">
       <c r="B510" t="s">
-        <v>563</v>
+        <v>561</v>
       </c>
       <c r="E510" t="s">
-        <v>49</v>
+        <v>55</v>
       </c>
     </row>
     <row r="511" spans="2:5" x14ac:dyDescent="0.35">
       <c r="B511" t="s">
-        <v>564</v>
+        <v>562</v>
       </c>
       <c r="E511" t="s">
-        <v>61</v>
+        <v>50</v>
       </c>
     </row>
     <row r="512" spans="2:5" x14ac:dyDescent="0.35">
       <c r="B512" t="s">
-        <v>565</v>
+        <v>563</v>
       </c>
       <c r="E512" t="s">
-        <v>59</v>
+        <v>60</v>
       </c>
     </row>
     <row r="513" spans="2:5" x14ac:dyDescent="0.35">
       <c r="B513" t="s">
-        <v>566</v>
+        <v>564</v>
       </c>
       <c r="E513" t="s">
-        <v>54</v>
+        <v>87</v>
       </c>
     </row>
     <row r="514" spans="2:5" x14ac:dyDescent="0.35">
       <c r="B514" t="s">
-        <v>567</v>
+        <v>565</v>
       </c>
       <c r="E514" t="s">
         <v>64</v>
@@ -7783,47 +7747,47 @@
     </row>
     <row r="515" spans="2:5" x14ac:dyDescent="0.35">
       <c r="B515" t="s">
-        <v>568</v>
+        <v>566</v>
       </c>
       <c r="E515" t="s">
-        <v>91</v>
+        <v>82</v>
       </c>
     </row>
     <row r="516" spans="2:5" x14ac:dyDescent="0.35">
       <c r="B516" t="s">
-        <v>569</v>
+        <v>567</v>
       </c>
       <c r="E516" t="s">
-        <v>68</v>
+        <v>90</v>
       </c>
     </row>
     <row r="517" spans="2:5" x14ac:dyDescent="0.35">
       <c r="B517" t="s">
-        <v>570</v>
+        <v>568</v>
       </c>
       <c r="E517" t="s">
-        <v>86</v>
+        <v>74</v>
       </c>
     </row>
     <row r="518" spans="2:5" x14ac:dyDescent="0.35">
       <c r="B518" t="s">
-        <v>571</v>
+        <v>569</v>
       </c>
       <c r="E518" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
     </row>
     <row r="519" spans="2:5" x14ac:dyDescent="0.35">
       <c r="B519" t="s">
-        <v>572</v>
+        <v>570</v>
       </c>
       <c r="E519" t="s">
-        <v>78</v>
+        <v>95</v>
       </c>
     </row>
     <row r="520" spans="2:5" x14ac:dyDescent="0.35">
       <c r="B520" t="s">
-        <v>573</v>
+        <v>571</v>
       </c>
       <c r="E520" t="s">
         <v>97</v>
@@ -7831,7 +7795,7 @@
     </row>
     <row r="521" spans="2:5" x14ac:dyDescent="0.35">
       <c r="B521" t="s">
-        <v>574</v>
+        <v>572</v>
       </c>
       <c r="E521" t="s">
         <v>99</v>
@@ -7839,31 +7803,31 @@
     </row>
     <row r="522" spans="2:5" x14ac:dyDescent="0.35">
       <c r="B522" t="s">
-        <v>575</v>
+        <v>573</v>
       </c>
       <c r="E522" t="s">
-        <v>101</v>
+        <v>79</v>
       </c>
     </row>
     <row r="523" spans="2:5" x14ac:dyDescent="0.35">
       <c r="B523" t="s">
-        <v>576</v>
+        <v>574</v>
       </c>
       <c r="E523" t="s">
-        <v>103</v>
+        <v>102</v>
       </c>
     </row>
     <row r="524" spans="2:5" x14ac:dyDescent="0.35">
       <c r="B524" t="s">
-        <v>577</v>
+        <v>575</v>
       </c>
       <c r="E524" t="s">
-        <v>83</v>
+        <v>104</v>
       </c>
     </row>
     <row r="525" spans="2:5" x14ac:dyDescent="0.35">
       <c r="B525" t="s">
-        <v>578</v>
+        <v>576</v>
       </c>
       <c r="E525" t="s">
         <v>106</v>
@@ -7871,7 +7835,7 @@
     </row>
     <row r="526" spans="2:5" x14ac:dyDescent="0.35">
       <c r="B526" t="s">
-        <v>579</v>
+        <v>577</v>
       </c>
       <c r="E526" t="s">
         <v>108</v>
@@ -7879,55 +7843,55 @@
     </row>
     <row r="527" spans="2:5" x14ac:dyDescent="0.35">
       <c r="B527" t="s">
-        <v>580</v>
+        <v>578</v>
       </c>
       <c r="E527" t="s">
-        <v>110</v>
+        <v>45</v>
       </c>
     </row>
     <row r="528" spans="2:5" x14ac:dyDescent="0.35">
       <c r="B528" t="s">
-        <v>581</v>
+        <v>579</v>
       </c>
       <c r="E528" t="s">
-        <v>112</v>
+        <v>57</v>
       </c>
     </row>
     <row r="529" spans="2:5" x14ac:dyDescent="0.35">
       <c r="B529" t="s">
-        <v>582</v>
+        <v>580</v>
       </c>
       <c r="E529" t="s">
-        <v>49</v>
+        <v>55</v>
       </c>
     </row>
     <row r="530" spans="2:5" x14ac:dyDescent="0.35">
       <c r="B530" t="s">
-        <v>583</v>
+        <v>581</v>
       </c>
       <c r="E530" t="s">
-        <v>61</v>
+        <v>50</v>
       </c>
     </row>
     <row r="531" spans="2:5" x14ac:dyDescent="0.35">
       <c r="B531" t="s">
-        <v>584</v>
+        <v>582</v>
       </c>
       <c r="E531" t="s">
-        <v>59</v>
+        <v>60</v>
       </c>
     </row>
     <row r="532" spans="2:5" x14ac:dyDescent="0.35">
       <c r="B532" t="s">
-        <v>585</v>
+        <v>583</v>
       </c>
       <c r="E532" t="s">
-        <v>54</v>
+        <v>87</v>
       </c>
     </row>
     <row r="533" spans="2:5" x14ac:dyDescent="0.35">
       <c r="B533" t="s">
-        <v>586</v>
+        <v>584</v>
       </c>
       <c r="E533" t="s">
         <v>64</v>
@@ -7935,47 +7899,47 @@
     </row>
     <row r="534" spans="2:5" x14ac:dyDescent="0.35">
       <c r="B534" t="s">
-        <v>587</v>
+        <v>585</v>
       </c>
       <c r="E534" t="s">
-        <v>91</v>
+        <v>82</v>
       </c>
     </row>
     <row r="535" spans="2:5" x14ac:dyDescent="0.35">
       <c r="B535" t="s">
-        <v>588</v>
+        <v>586</v>
       </c>
       <c r="E535" t="s">
-        <v>68</v>
+        <v>90</v>
       </c>
     </row>
     <row r="536" spans="2:5" x14ac:dyDescent="0.35">
       <c r="B536" t="s">
-        <v>589</v>
+        <v>587</v>
       </c>
       <c r="E536" t="s">
-        <v>86</v>
+        <v>74</v>
       </c>
     </row>
     <row r="537" spans="2:5" x14ac:dyDescent="0.35">
       <c r="B537" t="s">
-        <v>590</v>
+        <v>588</v>
       </c>
       <c r="E537" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
     </row>
     <row r="538" spans="2:5" x14ac:dyDescent="0.35">
       <c r="B538" t="s">
-        <v>591</v>
+        <v>589</v>
       </c>
       <c r="E538" t="s">
-        <v>78</v>
+        <v>95</v>
       </c>
     </row>
     <row r="539" spans="2:5" x14ac:dyDescent="0.35">
       <c r="B539" t="s">
-        <v>592</v>
+        <v>590</v>
       </c>
       <c r="E539" t="s">
         <v>97</v>
@@ -7983,7 +7947,7 @@
     </row>
     <row r="540" spans="2:5" x14ac:dyDescent="0.35">
       <c r="B540" t="s">
-        <v>593</v>
+        <v>591</v>
       </c>
       <c r="E540" t="s">
         <v>99</v>
@@ -7991,31 +7955,31 @@
     </row>
     <row r="541" spans="2:5" x14ac:dyDescent="0.35">
       <c r="B541" t="s">
-        <v>594</v>
+        <v>592</v>
       </c>
       <c r="E541" t="s">
-        <v>101</v>
+        <v>79</v>
       </c>
     </row>
     <row r="542" spans="2:5" x14ac:dyDescent="0.35">
       <c r="B542" t="s">
-        <v>595</v>
+        <v>593</v>
       </c>
       <c r="E542" t="s">
-        <v>103</v>
+        <v>102</v>
       </c>
     </row>
     <row r="543" spans="2:5" x14ac:dyDescent="0.35">
       <c r="B543" t="s">
-        <v>596</v>
+        <v>594</v>
       </c>
       <c r="E543" t="s">
-        <v>83</v>
+        <v>104</v>
       </c>
     </row>
     <row r="544" spans="2:5" x14ac:dyDescent="0.35">
       <c r="B544" t="s">
-        <v>597</v>
+        <v>595</v>
       </c>
       <c r="E544" t="s">
         <v>106</v>
@@ -8023,7 +7987,7 @@
     </row>
     <row r="545" spans="2:5" x14ac:dyDescent="0.35">
       <c r="B545" t="s">
-        <v>598</v>
+        <v>596</v>
       </c>
       <c r="E545" t="s">
         <v>108</v>
@@ -8031,55 +7995,55 @@
     </row>
     <row r="546" spans="2:5" x14ac:dyDescent="0.35">
       <c r="B546" t="s">
-        <v>599</v>
+        <v>597</v>
       </c>
       <c r="E546" t="s">
-        <v>110</v>
+        <v>45</v>
       </c>
     </row>
     <row r="547" spans="2:5" x14ac:dyDescent="0.35">
       <c r="B547" t="s">
-        <v>600</v>
+        <v>598</v>
       </c>
       <c r="E547" t="s">
-        <v>112</v>
+        <v>57</v>
       </c>
     </row>
     <row r="548" spans="2:5" x14ac:dyDescent="0.35">
       <c r="B548" t="s">
-        <v>601</v>
+        <v>599</v>
       </c>
       <c r="E548" t="s">
-        <v>49</v>
+        <v>55</v>
       </c>
     </row>
     <row r="549" spans="2:5" x14ac:dyDescent="0.35">
       <c r="B549" t="s">
-        <v>602</v>
+        <v>600</v>
       </c>
       <c r="E549" t="s">
-        <v>61</v>
+        <v>50</v>
       </c>
     </row>
     <row r="550" spans="2:5" x14ac:dyDescent="0.35">
       <c r="B550" t="s">
-        <v>603</v>
+        <v>601</v>
       </c>
       <c r="E550" t="s">
-        <v>59</v>
+        <v>60</v>
       </c>
     </row>
     <row r="551" spans="2:5" x14ac:dyDescent="0.35">
       <c r="B551" t="s">
-        <v>604</v>
+        <v>602</v>
       </c>
       <c r="E551" t="s">
-        <v>54</v>
+        <v>87</v>
       </c>
     </row>
     <row r="552" spans="2:5" x14ac:dyDescent="0.35">
       <c r="B552" t="s">
-        <v>605</v>
+        <v>603</v>
       </c>
       <c r="E552" t="s">
         <v>64</v>
@@ -8087,47 +8051,47 @@
     </row>
     <row r="553" spans="2:5" x14ac:dyDescent="0.35">
       <c r="B553" t="s">
-        <v>606</v>
+        <v>604</v>
       </c>
       <c r="E553" t="s">
-        <v>91</v>
+        <v>82</v>
       </c>
     </row>
     <row r="554" spans="2:5" x14ac:dyDescent="0.35">
       <c r="B554" t="s">
-        <v>607</v>
+        <v>605</v>
       </c>
       <c r="E554" t="s">
-        <v>68</v>
+        <v>90</v>
       </c>
     </row>
     <row r="555" spans="2:5" x14ac:dyDescent="0.35">
       <c r="B555" t="s">
-        <v>608</v>
+        <v>606</v>
       </c>
       <c r="E555" t="s">
-        <v>86</v>
+        <v>74</v>
       </c>
     </row>
     <row r="556" spans="2:5" x14ac:dyDescent="0.35">
       <c r="B556" t="s">
-        <v>609</v>
+        <v>607</v>
       </c>
       <c r="E556" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
     </row>
     <row r="557" spans="2:5" x14ac:dyDescent="0.35">
       <c r="B557" t="s">
-        <v>610</v>
+        <v>608</v>
       </c>
       <c r="E557" t="s">
-        <v>78</v>
+        <v>95</v>
       </c>
     </row>
     <row r="558" spans="2:5" x14ac:dyDescent="0.35">
       <c r="B558" t="s">
-        <v>611</v>
+        <v>609</v>
       </c>
       <c r="E558" t="s">
         <v>97</v>
@@ -8135,7 +8099,7 @@
     </row>
     <row r="559" spans="2:5" x14ac:dyDescent="0.35">
       <c r="B559" t="s">
-        <v>612</v>
+        <v>610</v>
       </c>
       <c r="E559" t="s">
         <v>99</v>
@@ -8143,31 +8107,31 @@
     </row>
     <row r="560" spans="2:5" x14ac:dyDescent="0.35">
       <c r="B560" t="s">
-        <v>613</v>
+        <v>611</v>
       </c>
       <c r="E560" t="s">
-        <v>101</v>
+        <v>79</v>
       </c>
     </row>
     <row r="561" spans="2:5" x14ac:dyDescent="0.35">
       <c r="B561" t="s">
-        <v>614</v>
+        <v>612</v>
       </c>
       <c r="E561" t="s">
-        <v>103</v>
+        <v>102</v>
       </c>
     </row>
     <row r="562" spans="2:5" x14ac:dyDescent="0.35">
       <c r="B562" t="s">
-        <v>615</v>
+        <v>613</v>
       </c>
       <c r="E562" t="s">
-        <v>83</v>
+        <v>104</v>
       </c>
     </row>
     <row r="563" spans="2:5" x14ac:dyDescent="0.35">
       <c r="B563" t="s">
-        <v>616</v>
+        <v>614</v>
       </c>
       <c r="E563" t="s">
         <v>106</v>
@@ -8175,7 +8139,7 @@
     </row>
     <row r="564" spans="2:5" x14ac:dyDescent="0.35">
       <c r="B564" t="s">
-        <v>617</v>
+        <v>615</v>
       </c>
       <c r="E564" t="s">
         <v>108</v>
@@ -8183,55 +8147,55 @@
     </row>
     <row r="565" spans="2:5" x14ac:dyDescent="0.35">
       <c r="B565" t="s">
-        <v>618</v>
+        <v>616</v>
       </c>
       <c r="E565" t="s">
-        <v>110</v>
+        <v>45</v>
       </c>
     </row>
     <row r="566" spans="2:5" x14ac:dyDescent="0.35">
       <c r="B566" t="s">
-        <v>619</v>
+        <v>617</v>
       </c>
       <c r="E566" t="s">
-        <v>112</v>
+        <v>57</v>
       </c>
     </row>
     <row r="567" spans="2:5" x14ac:dyDescent="0.35">
       <c r="B567" t="s">
-        <v>620</v>
+        <v>618</v>
       </c>
       <c r="E567" t="s">
-        <v>49</v>
+        <v>55</v>
       </c>
     </row>
     <row r="568" spans="2:5" x14ac:dyDescent="0.35">
       <c r="B568" t="s">
-        <v>621</v>
+        <v>619</v>
       </c>
       <c r="E568" t="s">
-        <v>61</v>
+        <v>50</v>
       </c>
     </row>
     <row r="569" spans="2:5" x14ac:dyDescent="0.35">
       <c r="B569" t="s">
-        <v>622</v>
+        <v>620</v>
       </c>
       <c r="E569" t="s">
-        <v>59</v>
+        <v>60</v>
       </c>
     </row>
     <row r="570" spans="2:5" x14ac:dyDescent="0.35">
       <c r="B570" t="s">
-        <v>623</v>
+        <v>621</v>
       </c>
       <c r="E570" t="s">
-        <v>54</v>
+        <v>87</v>
       </c>
     </row>
     <row r="571" spans="2:5" x14ac:dyDescent="0.35">
       <c r="B571" t="s">
-        <v>624</v>
+        <v>622</v>
       </c>
       <c r="E571" t="s">
         <v>64</v>
@@ -8239,47 +8203,47 @@
     </row>
     <row r="572" spans="2:5" x14ac:dyDescent="0.35">
       <c r="B572" t="s">
-        <v>625</v>
+        <v>623</v>
       </c>
       <c r="E572" t="s">
-        <v>91</v>
+        <v>82</v>
       </c>
     </row>
     <row r="573" spans="2:5" x14ac:dyDescent="0.35">
       <c r="B573" t="s">
-        <v>626</v>
+        <v>624</v>
       </c>
       <c r="E573" t="s">
-        <v>68</v>
+        <v>90</v>
       </c>
     </row>
     <row r="574" spans="2:5" x14ac:dyDescent="0.35">
       <c r="B574" t="s">
-        <v>627</v>
+        <v>625</v>
       </c>
       <c r="E574" t="s">
-        <v>86</v>
+        <v>74</v>
       </c>
     </row>
     <row r="575" spans="2:5" x14ac:dyDescent="0.35">
       <c r="B575" t="s">
-        <v>628</v>
+        <v>626</v>
       </c>
       <c r="E575" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
     </row>
     <row r="576" spans="2:5" x14ac:dyDescent="0.35">
       <c r="B576" t="s">
-        <v>629</v>
+        <v>627</v>
       </c>
       <c r="E576" t="s">
-        <v>78</v>
+        <v>95</v>
       </c>
     </row>
     <row r="577" spans="2:5" x14ac:dyDescent="0.35">
       <c r="B577" t="s">
-        <v>630</v>
+        <v>628</v>
       </c>
       <c r="E577" t="s">
         <v>97</v>
@@ -8287,7 +8251,7 @@
     </row>
     <row r="578" spans="2:5" x14ac:dyDescent="0.35">
       <c r="B578" t="s">
-        <v>631</v>
+        <v>629</v>
       </c>
       <c r="E578" t="s">
         <v>99</v>
@@ -8295,31 +8259,31 @@
     </row>
     <row r="579" spans="2:5" x14ac:dyDescent="0.35">
       <c r="B579" t="s">
-        <v>632</v>
+        <v>630</v>
       </c>
       <c r="E579" t="s">
-        <v>101</v>
+        <v>79</v>
       </c>
     </row>
     <row r="580" spans="2:5" x14ac:dyDescent="0.35">
       <c r="B580" t="s">
-        <v>633</v>
+        <v>631</v>
       </c>
       <c r="E580" t="s">
-        <v>103</v>
+        <v>102</v>
       </c>
     </row>
     <row r="581" spans="2:5" x14ac:dyDescent="0.35">
       <c r="B581" t="s">
-        <v>634</v>
+        <v>632</v>
       </c>
       <c r="E581" t="s">
-        <v>83</v>
+        <v>104</v>
       </c>
     </row>
     <row r="582" spans="2:5" x14ac:dyDescent="0.35">
       <c r="B582" t="s">
-        <v>635</v>
+        <v>633</v>
       </c>
       <c r="E582" t="s">
         <v>106</v>
@@ -8327,7 +8291,7 @@
     </row>
     <row r="583" spans="2:5" x14ac:dyDescent="0.35">
       <c r="B583" t="s">
-        <v>636</v>
+        <v>634</v>
       </c>
       <c r="E583" t="s">
         <v>108</v>
@@ -8335,55 +8299,55 @@
     </row>
     <row r="584" spans="2:5" x14ac:dyDescent="0.35">
       <c r="B584" t="s">
-        <v>637</v>
+        <v>635</v>
       </c>
       <c r="E584" t="s">
-        <v>110</v>
+        <v>45</v>
       </c>
     </row>
     <row r="585" spans="2:5" x14ac:dyDescent="0.35">
       <c r="B585" t="s">
-        <v>638</v>
+        <v>636</v>
       </c>
       <c r="E585" t="s">
-        <v>112</v>
+        <v>57</v>
       </c>
     </row>
     <row r="586" spans="2:5" x14ac:dyDescent="0.35">
       <c r="B586" t="s">
-        <v>639</v>
+        <v>637</v>
       </c>
       <c r="E586" t="s">
-        <v>49</v>
+        <v>55</v>
       </c>
     </row>
     <row r="587" spans="2:5" x14ac:dyDescent="0.35">
       <c r="B587" t="s">
-        <v>640</v>
+        <v>638</v>
       </c>
       <c r="E587" t="s">
-        <v>61</v>
+        <v>50</v>
       </c>
     </row>
     <row r="588" spans="2:5" x14ac:dyDescent="0.35">
       <c r="B588" t="s">
-        <v>641</v>
+        <v>639</v>
       </c>
       <c r="E588" t="s">
-        <v>59</v>
+        <v>60</v>
       </c>
     </row>
     <row r="589" spans="2:5" x14ac:dyDescent="0.35">
       <c r="B589" t="s">
-        <v>642</v>
+        <v>640</v>
       </c>
       <c r="E589" t="s">
-        <v>54</v>
+        <v>87</v>
       </c>
     </row>
     <row r="590" spans="2:5" x14ac:dyDescent="0.35">
       <c r="B590" t="s">
-        <v>643</v>
+        <v>641</v>
       </c>
       <c r="E590" t="s">
         <v>64</v>
@@ -8391,47 +8355,47 @@
     </row>
     <row r="591" spans="2:5" x14ac:dyDescent="0.35">
       <c r="B591" t="s">
-        <v>644</v>
+        <v>642</v>
       </c>
       <c r="E591" t="s">
-        <v>91</v>
+        <v>82</v>
       </c>
     </row>
     <row r="592" spans="2:5" x14ac:dyDescent="0.35">
       <c r="B592" t="s">
-        <v>645</v>
+        <v>643</v>
       </c>
       <c r="E592" t="s">
-        <v>68</v>
+        <v>90</v>
       </c>
     </row>
     <row r="593" spans="2:5" x14ac:dyDescent="0.35">
       <c r="B593" t="s">
-        <v>646</v>
+        <v>644</v>
       </c>
       <c r="E593" t="s">
-        <v>86</v>
+        <v>74</v>
       </c>
     </row>
     <row r="594" spans="2:5" x14ac:dyDescent="0.35">
       <c r="B594" t="s">
-        <v>647</v>
+        <v>645</v>
       </c>
       <c r="E594" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
     </row>
     <row r="595" spans="2:5" x14ac:dyDescent="0.35">
       <c r="B595" t="s">
-        <v>648</v>
+        <v>646</v>
       </c>
       <c r="E595" t="s">
-        <v>78</v>
+        <v>95</v>
       </c>
     </row>
     <row r="596" spans="2:5" x14ac:dyDescent="0.35">
       <c r="B596" t="s">
-        <v>649</v>
+        <v>647</v>
       </c>
       <c r="E596" t="s">
         <v>97</v>
@@ -8439,7 +8403,7 @@
     </row>
     <row r="597" spans="2:5" x14ac:dyDescent="0.35">
       <c r="B597" t="s">
-        <v>650</v>
+        <v>648</v>
       </c>
       <c r="E597" t="s">
         <v>99</v>
@@ -8447,31 +8411,31 @@
     </row>
     <row r="598" spans="2:5" x14ac:dyDescent="0.35">
       <c r="B598" t="s">
-        <v>651</v>
+        <v>649</v>
       </c>
       <c r="E598" t="s">
-        <v>101</v>
+        <v>79</v>
       </c>
     </row>
     <row r="599" spans="2:5" x14ac:dyDescent="0.35">
       <c r="B599" t="s">
-        <v>652</v>
+        <v>650</v>
       </c>
       <c r="E599" t="s">
-        <v>103</v>
+        <v>102</v>
       </c>
     </row>
     <row r="600" spans="2:5" x14ac:dyDescent="0.35">
       <c r="B600" t="s">
-        <v>653</v>
+        <v>651</v>
       </c>
       <c r="E600" t="s">
-        <v>83</v>
+        <v>104</v>
       </c>
     </row>
     <row r="601" spans="2:5" x14ac:dyDescent="0.35">
       <c r="B601" t="s">
-        <v>654</v>
+        <v>652</v>
       </c>
       <c r="E601" t="s">
         <v>106</v>
@@ -8479,7 +8443,7 @@
     </row>
     <row r="602" spans="2:5" x14ac:dyDescent="0.35">
       <c r="B602" t="s">
-        <v>655</v>
+        <v>653</v>
       </c>
       <c r="E602" t="s">
         <v>108</v>
@@ -8487,18 +8451,18 @@
     </row>
     <row r="603" spans="2:5" x14ac:dyDescent="0.35">
       <c r="B603" t="s">
-        <v>656</v>
+        <v>654</v>
       </c>
       <c r="E603" t="s">
-        <v>110</v>
+        <v>655</v>
       </c>
     </row>
     <row r="604" spans="2:5" x14ac:dyDescent="0.35">
       <c r="B604" t="s">
+        <v>656</v>
+      </c>
+      <c r="E604" t="s">
         <v>657</v>
-      </c>
-      <c r="E604" t="s">
-        <v>112</v>
       </c>
     </row>
     <row r="605" spans="2:5" x14ac:dyDescent="0.35">
@@ -8562,55 +8526,55 @@
         <v>672</v>
       </c>
       <c r="E612" t="s">
-        <v>673</v>
+        <v>76</v>
       </c>
     </row>
     <row r="613" spans="2:5" x14ac:dyDescent="0.35">
       <c r="B613" t="s">
+        <v>673</v>
+      </c>
+      <c r="E613" t="s">
         <v>674</v>
-      </c>
-      <c r="E613" t="s">
-        <v>675</v>
       </c>
     </row>
     <row r="614" spans="2:5" x14ac:dyDescent="0.35">
       <c r="B614" t="s">
-        <v>676</v>
+        <v>675</v>
       </c>
       <c r="E614" t="s">
-        <v>80</v>
+        <v>47</v>
       </c>
     </row>
     <row r="615" spans="2:5" x14ac:dyDescent="0.35">
       <c r="B615" t="s">
+        <v>676</v>
+      </c>
+      <c r="E615" t="s">
         <v>677</v>
-      </c>
-      <c r="E615" t="s">
-        <v>678</v>
       </c>
     </row>
     <row r="616" spans="2:5" x14ac:dyDescent="0.35">
       <c r="B616" t="s">
-        <v>679</v>
+        <v>678</v>
       </c>
       <c r="E616" t="s">
-        <v>51</v>
+        <v>52</v>
       </c>
     </row>
     <row r="617" spans="2:5" x14ac:dyDescent="0.35">
       <c r="B617" t="s">
+        <v>679</v>
+      </c>
+      <c r="E617" t="s">
         <v>680</v>
-      </c>
-      <c r="E617" t="s">
-        <v>681</v>
       </c>
     </row>
     <row r="618" spans="2:5" x14ac:dyDescent="0.35">
       <c r="B618" t="s">
+        <v>681</v>
+      </c>
+      <c r="E618" t="s">
         <v>682</v>
-      </c>
-      <c r="E618" t="s">
-        <v>56</v>
       </c>
     </row>
     <row r="619" spans="2:5" x14ac:dyDescent="0.35">
@@ -8626,52 +8590,52 @@
         <v>685</v>
       </c>
       <c r="E620" t="s">
-        <v>686</v>
+        <v>45</v>
       </c>
     </row>
     <row r="621" spans="2:5" x14ac:dyDescent="0.35">
       <c r="B621" t="s">
-        <v>687</v>
+        <v>686</v>
       </c>
       <c r="E621" t="s">
-        <v>688</v>
+        <v>57</v>
       </c>
     </row>
     <row r="622" spans="2:5" x14ac:dyDescent="0.35">
       <c r="B622" t="s">
-        <v>689</v>
+        <v>687</v>
       </c>
       <c r="E622" t="s">
-        <v>49</v>
+        <v>55</v>
       </c>
     </row>
     <row r="623" spans="2:5" x14ac:dyDescent="0.35">
       <c r="B623" t="s">
-        <v>690</v>
+        <v>688</v>
       </c>
       <c r="E623" t="s">
-        <v>61</v>
+        <v>50</v>
       </c>
     </row>
     <row r="624" spans="2:5" x14ac:dyDescent="0.35">
       <c r="B624" t="s">
-        <v>691</v>
+        <v>689</v>
       </c>
       <c r="E624" t="s">
-        <v>59</v>
+        <v>60</v>
       </c>
     </row>
     <row r="625" spans="2:5" x14ac:dyDescent="0.35">
       <c r="B625" t="s">
-        <v>692</v>
+        <v>690</v>
       </c>
       <c r="E625" t="s">
-        <v>54</v>
+        <v>87</v>
       </c>
     </row>
     <row r="626" spans="2:5" x14ac:dyDescent="0.35">
       <c r="B626" t="s">
-        <v>693</v>
+        <v>691</v>
       </c>
       <c r="E626" t="s">
         <v>64</v>
@@ -8679,143 +8643,143 @@
     </row>
     <row r="627" spans="2:5" x14ac:dyDescent="0.35">
       <c r="B627" t="s">
-        <v>694</v>
+        <v>692</v>
       </c>
       <c r="E627" t="s">
-        <v>91</v>
+        <v>90</v>
       </c>
     </row>
     <row r="628" spans="2:5" x14ac:dyDescent="0.35">
       <c r="B628" t="s">
-        <v>695</v>
+        <v>693</v>
       </c>
       <c r="E628" t="s">
-        <v>68</v>
+        <v>65</v>
       </c>
     </row>
     <row r="629" spans="2:5" x14ac:dyDescent="0.35">
       <c r="B629" t="s">
-        <v>696</v>
+        <v>694</v>
       </c>
       <c r="E629" t="s">
-        <v>94</v>
+        <v>76</v>
       </c>
     </row>
     <row r="630" spans="2:5" x14ac:dyDescent="0.35">
       <c r="B630" t="s">
-        <v>697</v>
+        <v>695</v>
       </c>
       <c r="E630" t="s">
-        <v>69</v>
+        <v>674</v>
       </c>
     </row>
     <row r="631" spans="2:5" x14ac:dyDescent="0.35">
       <c r="B631" t="s">
-        <v>698</v>
+        <v>696</v>
       </c>
       <c r="E631" t="s">
-        <v>80</v>
+        <v>47</v>
       </c>
     </row>
     <row r="632" spans="2:5" x14ac:dyDescent="0.35">
       <c r="B632" t="s">
-        <v>699</v>
+        <v>697</v>
       </c>
       <c r="E632" t="s">
-        <v>678</v>
+        <v>677</v>
       </c>
     </row>
     <row r="633" spans="2:5" x14ac:dyDescent="0.35">
       <c r="B633" t="s">
-        <v>700</v>
+        <v>698</v>
       </c>
       <c r="E633" t="s">
-        <v>51</v>
+        <v>52</v>
       </c>
     </row>
     <row r="634" spans="2:5" x14ac:dyDescent="0.35">
       <c r="B634" t="s">
-        <v>701</v>
+        <v>699</v>
       </c>
       <c r="E634" t="s">
-        <v>681</v>
+        <v>680</v>
       </c>
     </row>
     <row r="635" spans="2:5" x14ac:dyDescent="0.35">
       <c r="B635" t="s">
-        <v>702</v>
+        <v>700</v>
       </c>
       <c r="E635" t="s">
-        <v>56</v>
+        <v>61</v>
       </c>
     </row>
     <row r="636" spans="2:5" x14ac:dyDescent="0.35">
       <c r="B636" t="s">
-        <v>703</v>
+        <v>701</v>
       </c>
       <c r="E636" t="s">
-        <v>684</v>
+        <v>682</v>
       </c>
     </row>
     <row r="637" spans="2:5" x14ac:dyDescent="0.35">
       <c r="B637" t="s">
-        <v>704</v>
+        <v>702</v>
       </c>
       <c r="E637" t="s">
-        <v>65</v>
+        <v>684</v>
       </c>
     </row>
     <row r="638" spans="2:5" x14ac:dyDescent="0.35">
       <c r="B638" t="s">
-        <v>705</v>
+        <v>703</v>
       </c>
       <c r="E638" t="s">
-        <v>686</v>
+        <v>45</v>
       </c>
     </row>
     <row r="639" spans="2:5" x14ac:dyDescent="0.35">
       <c r="B639" t="s">
-        <v>706</v>
+        <v>704</v>
       </c>
       <c r="E639" t="s">
-        <v>688</v>
+        <v>57</v>
       </c>
     </row>
     <row r="640" spans="2:5" x14ac:dyDescent="0.35">
       <c r="B640" t="s">
-        <v>707</v>
+        <v>705</v>
       </c>
       <c r="E640" t="s">
-        <v>49</v>
+        <v>55</v>
       </c>
     </row>
     <row r="641" spans="2:5" x14ac:dyDescent="0.35">
       <c r="B641" t="s">
-        <v>708</v>
+        <v>706</v>
       </c>
       <c r="E641" t="s">
-        <v>61</v>
+        <v>50</v>
       </c>
     </row>
     <row r="642" spans="2:5" x14ac:dyDescent="0.35">
       <c r="B642" t="s">
-        <v>709</v>
+        <v>707</v>
       </c>
       <c r="E642" t="s">
-        <v>59</v>
+        <v>60</v>
       </c>
     </row>
     <row r="643" spans="2:5" x14ac:dyDescent="0.35">
       <c r="B643" t="s">
-        <v>710</v>
+        <v>708</v>
       </c>
       <c r="E643" t="s">
-        <v>54</v>
+        <v>87</v>
       </c>
     </row>
     <row r="644" spans="2:5" x14ac:dyDescent="0.35">
       <c r="B644" t="s">
-        <v>711</v>
+        <v>709</v>
       </c>
       <c r="E644" t="s">
         <v>64</v>
@@ -8823,63 +8787,63 @@
     </row>
     <row r="645" spans="2:5" x14ac:dyDescent="0.35">
       <c r="B645" t="s">
-        <v>712</v>
+        <v>710</v>
       </c>
       <c r="E645" t="s">
-        <v>91</v>
+        <v>82</v>
       </c>
     </row>
     <row r="646" spans="2:5" x14ac:dyDescent="0.35">
       <c r="B646" t="s">
-        <v>713</v>
+        <v>711</v>
       </c>
       <c r="E646" t="s">
-        <v>68</v>
+        <v>90</v>
       </c>
     </row>
     <row r="647" spans="2:5" x14ac:dyDescent="0.35">
       <c r="B647" t="s">
-        <v>714</v>
+        <v>712</v>
       </c>
       <c r="E647" t="s">
-        <v>86</v>
+        <v>65</v>
       </c>
     </row>
     <row r="648" spans="2:5" x14ac:dyDescent="0.35">
       <c r="B648" t="s">
-        <v>715</v>
+        <v>713</v>
       </c>
       <c r="E648" t="s">
-        <v>94</v>
+        <v>674</v>
       </c>
     </row>
     <row r="649" spans="2:5" x14ac:dyDescent="0.35">
       <c r="B649" t="s">
-        <v>716</v>
+        <v>714</v>
       </c>
       <c r="E649" t="s">
-        <v>69</v>
+        <v>677</v>
       </c>
     </row>
     <row r="650" spans="2:5" x14ac:dyDescent="0.35">
       <c r="B650" t="s">
-        <v>717</v>
+        <v>715</v>
       </c>
       <c r="E650" t="s">
-        <v>678</v>
+        <v>680</v>
       </c>
     </row>
     <row r="651" spans="2:5" x14ac:dyDescent="0.35">
       <c r="B651" t="s">
-        <v>718</v>
+        <v>716</v>
       </c>
       <c r="E651" t="s">
-        <v>681</v>
+        <v>682</v>
       </c>
     </row>
     <row r="652" spans="2:5" x14ac:dyDescent="0.35">
       <c r="B652" t="s">
-        <v>719</v>
+        <v>717</v>
       </c>
       <c r="E652" t="s">
         <v>684</v>
@@ -8887,55 +8851,55 @@
     </row>
     <row r="653" spans="2:5" x14ac:dyDescent="0.35">
       <c r="B653" t="s">
-        <v>720</v>
+        <v>718</v>
       </c>
       <c r="E653" t="s">
-        <v>686</v>
+        <v>45</v>
       </c>
     </row>
     <row r="654" spans="2:5" x14ac:dyDescent="0.35">
       <c r="B654" t="s">
-        <v>721</v>
+        <v>719</v>
       </c>
       <c r="E654" t="s">
-        <v>688</v>
+        <v>57</v>
       </c>
     </row>
     <row r="655" spans="2:5" x14ac:dyDescent="0.35">
       <c r="B655" t="s">
-        <v>722</v>
+        <v>720</v>
       </c>
       <c r="E655" t="s">
-        <v>49</v>
+        <v>55</v>
       </c>
     </row>
     <row r="656" spans="2:5" x14ac:dyDescent="0.35">
       <c r="B656" t="s">
-        <v>723</v>
+        <v>721</v>
       </c>
       <c r="E656" t="s">
-        <v>61</v>
+        <v>50</v>
       </c>
     </row>
     <row r="657" spans="2:5" x14ac:dyDescent="0.35">
       <c r="B657" t="s">
-        <v>724</v>
+        <v>722</v>
       </c>
       <c r="E657" t="s">
-        <v>59</v>
+        <v>60</v>
       </c>
     </row>
     <row r="658" spans="2:5" x14ac:dyDescent="0.35">
       <c r="B658" t="s">
-        <v>725</v>
+        <v>723</v>
       </c>
       <c r="E658" t="s">
-        <v>54</v>
+        <v>87</v>
       </c>
     </row>
     <row r="659" spans="2:5" x14ac:dyDescent="0.35">
       <c r="B659" t="s">
-        <v>726</v>
+        <v>724</v>
       </c>
       <c r="E659" t="s">
         <v>64</v>
@@ -8943,151 +8907,151 @@
     </row>
     <row r="660" spans="2:5" x14ac:dyDescent="0.35">
       <c r="B660" t="s">
-        <v>727</v>
+        <v>725</v>
       </c>
       <c r="E660" t="s">
-        <v>91</v>
+        <v>82</v>
       </c>
     </row>
     <row r="661" spans="2:5" x14ac:dyDescent="0.35">
       <c r="B661" t="s">
-        <v>728</v>
+        <v>726</v>
       </c>
       <c r="E661" t="s">
-        <v>68</v>
+        <v>90</v>
       </c>
     </row>
     <row r="662" spans="2:5" x14ac:dyDescent="0.35">
       <c r="B662" t="s">
-        <v>729</v>
+        <v>727</v>
       </c>
       <c r="E662" t="s">
-        <v>86</v>
+        <v>65</v>
       </c>
     </row>
     <row r="663" spans="2:5" x14ac:dyDescent="0.35">
       <c r="B663" t="s">
-        <v>730</v>
+        <v>728</v>
       </c>
       <c r="E663" t="s">
-        <v>94</v>
+        <v>76</v>
       </c>
     </row>
     <row r="664" spans="2:5" x14ac:dyDescent="0.35">
       <c r="B664" t="s">
-        <v>731</v>
+        <v>729</v>
       </c>
       <c r="E664" t="s">
-        <v>69</v>
+        <v>674</v>
       </c>
     </row>
     <row r="665" spans="2:5" x14ac:dyDescent="0.35">
       <c r="B665" t="s">
-        <v>732</v>
+        <v>730</v>
       </c>
       <c r="E665" t="s">
-        <v>80</v>
+        <v>47</v>
       </c>
     </row>
     <row r="666" spans="2:5" x14ac:dyDescent="0.35">
       <c r="B666" t="s">
-        <v>733</v>
+        <v>731</v>
       </c>
       <c r="E666" t="s">
-        <v>678</v>
+        <v>677</v>
       </c>
     </row>
     <row r="667" spans="2:5" x14ac:dyDescent="0.35">
       <c r="B667" t="s">
-        <v>734</v>
+        <v>732</v>
       </c>
       <c r="E667" t="s">
-        <v>51</v>
+        <v>52</v>
       </c>
     </row>
     <row r="668" spans="2:5" x14ac:dyDescent="0.35">
       <c r="B668" t="s">
-        <v>735</v>
+        <v>733</v>
       </c>
       <c r="E668" t="s">
-        <v>681</v>
+        <v>680</v>
       </c>
     </row>
     <row r="669" spans="2:5" x14ac:dyDescent="0.35">
       <c r="B669" t="s">
-        <v>736</v>
+        <v>734</v>
       </c>
       <c r="E669" t="s">
-        <v>56</v>
+        <v>61</v>
       </c>
     </row>
     <row r="670" spans="2:5" x14ac:dyDescent="0.35">
       <c r="B670" t="s">
-        <v>737</v>
+        <v>735</v>
       </c>
       <c r="E670" t="s">
-        <v>684</v>
+        <v>682</v>
       </c>
     </row>
     <row r="671" spans="2:5" x14ac:dyDescent="0.35">
       <c r="B671" t="s">
-        <v>738</v>
+        <v>736</v>
       </c>
       <c r="E671" t="s">
-        <v>65</v>
+        <v>684</v>
       </c>
     </row>
     <row r="672" spans="2:5" x14ac:dyDescent="0.35">
       <c r="B672" t="s">
-        <v>739</v>
+        <v>737</v>
       </c>
       <c r="E672" t="s">
-        <v>686</v>
+        <v>45</v>
       </c>
     </row>
     <row r="673" spans="2:5" x14ac:dyDescent="0.35">
       <c r="B673" t="s">
-        <v>740</v>
+        <v>738</v>
       </c>
       <c r="E673" t="s">
-        <v>688</v>
+        <v>57</v>
       </c>
     </row>
     <row r="674" spans="2:5" x14ac:dyDescent="0.35">
       <c r="B674" t="s">
-        <v>741</v>
+        <v>739</v>
       </c>
       <c r="E674" t="s">
-        <v>49</v>
+        <v>55</v>
       </c>
     </row>
     <row r="675" spans="2:5" x14ac:dyDescent="0.35">
       <c r="B675" t="s">
-        <v>742</v>
+        <v>740</v>
       </c>
       <c r="E675" t="s">
-        <v>61</v>
+        <v>50</v>
       </c>
     </row>
     <row r="676" spans="2:5" x14ac:dyDescent="0.35">
       <c r="B676" t="s">
-        <v>743</v>
+        <v>741</v>
       </c>
       <c r="E676" t="s">
-        <v>59</v>
+        <v>60</v>
       </c>
     </row>
     <row r="677" spans="2:5" x14ac:dyDescent="0.35">
       <c r="B677" t="s">
-        <v>744</v>
+        <v>742</v>
       </c>
       <c r="E677" t="s">
-        <v>54</v>
+        <v>87</v>
       </c>
     </row>
     <row r="678" spans="2:5" x14ac:dyDescent="0.35">
       <c r="B678" t="s">
-        <v>745</v>
+        <v>743</v>
       </c>
       <c r="E678" t="s">
         <v>64</v>
@@ -9095,151 +9059,151 @@
     </row>
     <row r="679" spans="2:5" x14ac:dyDescent="0.35">
       <c r="B679" t="s">
-        <v>746</v>
+        <v>744</v>
       </c>
       <c r="E679" t="s">
-        <v>91</v>
+        <v>82</v>
       </c>
     </row>
     <row r="680" spans="2:5" x14ac:dyDescent="0.35">
       <c r="B680" t="s">
-        <v>747</v>
+        <v>745</v>
       </c>
       <c r="E680" t="s">
-        <v>68</v>
+        <v>90</v>
       </c>
     </row>
     <row r="681" spans="2:5" x14ac:dyDescent="0.35">
       <c r="B681" t="s">
-        <v>748</v>
+        <v>746</v>
       </c>
       <c r="E681" t="s">
-        <v>86</v>
+        <v>65</v>
       </c>
     </row>
     <row r="682" spans="2:5" x14ac:dyDescent="0.35">
       <c r="B682" t="s">
-        <v>749</v>
+        <v>747</v>
       </c>
       <c r="E682" t="s">
-        <v>94</v>
+        <v>76</v>
       </c>
     </row>
     <row r="683" spans="2:5" x14ac:dyDescent="0.35">
       <c r="B683" t="s">
-        <v>750</v>
+        <v>748</v>
       </c>
       <c r="E683" t="s">
-        <v>69</v>
+        <v>674</v>
       </c>
     </row>
     <row r="684" spans="2:5" x14ac:dyDescent="0.35">
       <c r="B684" t="s">
-        <v>751</v>
+        <v>749</v>
       </c>
       <c r="E684" t="s">
-        <v>80</v>
+        <v>47</v>
       </c>
     </row>
     <row r="685" spans="2:5" x14ac:dyDescent="0.35">
       <c r="B685" t="s">
-        <v>752</v>
+        <v>750</v>
       </c>
       <c r="E685" t="s">
-        <v>678</v>
+        <v>677</v>
       </c>
     </row>
     <row r="686" spans="2:5" x14ac:dyDescent="0.35">
       <c r="B686" t="s">
-        <v>753</v>
+        <v>751</v>
       </c>
       <c r="E686" t="s">
-        <v>51</v>
+        <v>52</v>
       </c>
     </row>
     <row r="687" spans="2:5" x14ac:dyDescent="0.35">
       <c r="B687" t="s">
-        <v>754</v>
+        <v>752</v>
       </c>
       <c r="E687" t="s">
-        <v>681</v>
+        <v>680</v>
       </c>
     </row>
     <row r="688" spans="2:5" x14ac:dyDescent="0.35">
       <c r="B688" t="s">
-        <v>755</v>
+        <v>753</v>
       </c>
       <c r="E688" t="s">
-        <v>56</v>
+        <v>61</v>
       </c>
     </row>
     <row r="689" spans="2:5" x14ac:dyDescent="0.35">
       <c r="B689" t="s">
-        <v>756</v>
+        <v>754</v>
       </c>
       <c r="E689" t="s">
-        <v>684</v>
+        <v>682</v>
       </c>
     </row>
     <row r="690" spans="2:5" x14ac:dyDescent="0.35">
       <c r="B690" t="s">
-        <v>757</v>
+        <v>755</v>
       </c>
       <c r="E690" t="s">
-        <v>65</v>
+        <v>684</v>
       </c>
     </row>
     <row r="691" spans="2:5" x14ac:dyDescent="0.35">
       <c r="B691" t="s">
-        <v>758</v>
+        <v>756</v>
       </c>
       <c r="E691" t="s">
-        <v>686</v>
+        <v>45</v>
       </c>
     </row>
     <row r="692" spans="2:5" x14ac:dyDescent="0.35">
       <c r="B692" t="s">
-        <v>759</v>
+        <v>757</v>
       </c>
       <c r="E692" t="s">
-        <v>688</v>
+        <v>57</v>
       </c>
     </row>
     <row r="693" spans="2:5" x14ac:dyDescent="0.35">
       <c r="B693" t="s">
-        <v>760</v>
+        <v>758</v>
       </c>
       <c r="E693" t="s">
-        <v>49</v>
+        <v>55</v>
       </c>
     </row>
     <row r="694" spans="2:5" x14ac:dyDescent="0.35">
       <c r="B694" t="s">
-        <v>761</v>
+        <v>759</v>
       </c>
       <c r="E694" t="s">
-        <v>61</v>
+        <v>50</v>
       </c>
     </row>
     <row r="695" spans="2:5" x14ac:dyDescent="0.35">
       <c r="B695" t="s">
-        <v>762</v>
+        <v>760</v>
       </c>
       <c r="E695" t="s">
-        <v>59</v>
+        <v>60</v>
       </c>
     </row>
     <row r="696" spans="2:5" x14ac:dyDescent="0.35">
       <c r="B696" t="s">
-        <v>763</v>
+        <v>761</v>
       </c>
       <c r="E696" t="s">
-        <v>54</v>
+        <v>87</v>
       </c>
     </row>
     <row r="697" spans="2:5" x14ac:dyDescent="0.35">
       <c r="B697" t="s">
-        <v>764</v>
+        <v>762</v>
       </c>
       <c r="E697" t="s">
         <v>64</v>
@@ -9247,151 +9211,151 @@
     </row>
     <row r="698" spans="2:5" x14ac:dyDescent="0.35">
       <c r="B698" t="s">
-        <v>765</v>
+        <v>763</v>
       </c>
       <c r="E698" t="s">
-        <v>91</v>
+        <v>82</v>
       </c>
     </row>
     <row r="699" spans="2:5" x14ac:dyDescent="0.35">
       <c r="B699" t="s">
-        <v>766</v>
+        <v>764</v>
       </c>
       <c r="E699" t="s">
-        <v>68</v>
+        <v>90</v>
       </c>
     </row>
     <row r="700" spans="2:5" x14ac:dyDescent="0.35">
       <c r="B700" t="s">
-        <v>767</v>
+        <v>765</v>
       </c>
       <c r="E700" t="s">
-        <v>86</v>
+        <v>65</v>
       </c>
     </row>
     <row r="701" spans="2:5" x14ac:dyDescent="0.35">
       <c r="B701" t="s">
-        <v>768</v>
+        <v>766</v>
       </c>
       <c r="E701" t="s">
-        <v>94</v>
+        <v>76</v>
       </c>
     </row>
     <row r="702" spans="2:5" x14ac:dyDescent="0.35">
       <c r="B702" t="s">
-        <v>769</v>
+        <v>767</v>
       </c>
       <c r="E702" t="s">
-        <v>69</v>
+        <v>674</v>
       </c>
     </row>
     <row r="703" spans="2:5" x14ac:dyDescent="0.35">
       <c r="B703" t="s">
-        <v>770</v>
+        <v>768</v>
       </c>
       <c r="E703" t="s">
-        <v>80</v>
+        <v>47</v>
       </c>
     </row>
     <row r="704" spans="2:5" x14ac:dyDescent="0.35">
       <c r="B704" t="s">
-        <v>771</v>
+        <v>769</v>
       </c>
       <c r="E704" t="s">
-        <v>678</v>
+        <v>677</v>
       </c>
     </row>
     <row r="705" spans="2:5" x14ac:dyDescent="0.35">
       <c r="B705" t="s">
-        <v>772</v>
+        <v>770</v>
       </c>
       <c r="E705" t="s">
-        <v>51</v>
+        <v>52</v>
       </c>
     </row>
     <row r="706" spans="2:5" x14ac:dyDescent="0.35">
       <c r="B706" t="s">
-        <v>773</v>
+        <v>771</v>
       </c>
       <c r="E706" t="s">
-        <v>681</v>
+        <v>680</v>
       </c>
     </row>
     <row r="707" spans="2:5" x14ac:dyDescent="0.35">
       <c r="B707" t="s">
-        <v>774</v>
+        <v>772</v>
       </c>
       <c r="E707" t="s">
-        <v>56</v>
+        <v>61</v>
       </c>
     </row>
     <row r="708" spans="2:5" x14ac:dyDescent="0.35">
       <c r="B708" t="s">
-        <v>775</v>
+        <v>773</v>
       </c>
       <c r="E708" t="s">
-        <v>684</v>
+        <v>682</v>
       </c>
     </row>
     <row r="709" spans="2:5" x14ac:dyDescent="0.35">
       <c r="B709" t="s">
-        <v>776</v>
+        <v>774</v>
       </c>
       <c r="E709" t="s">
-        <v>65</v>
+        <v>684</v>
       </c>
     </row>
     <row r="710" spans="2:5" x14ac:dyDescent="0.35">
       <c r="B710" t="s">
-        <v>777</v>
+        <v>775</v>
       </c>
       <c r="E710" t="s">
-        <v>686</v>
+        <v>45</v>
       </c>
     </row>
     <row r="711" spans="2:5" x14ac:dyDescent="0.35">
       <c r="B711" t="s">
-        <v>778</v>
+        <v>776</v>
       </c>
       <c r="E711" t="s">
-        <v>688</v>
+        <v>57</v>
       </c>
     </row>
     <row r="712" spans="2:5" x14ac:dyDescent="0.35">
       <c r="B712" t="s">
-        <v>779</v>
+        <v>777</v>
       </c>
       <c r="E712" t="s">
-        <v>49</v>
+        <v>55</v>
       </c>
     </row>
     <row r="713" spans="2:5" x14ac:dyDescent="0.35">
       <c r="B713" t="s">
-        <v>780</v>
+        <v>778</v>
       </c>
       <c r="E713" t="s">
-        <v>61</v>
+        <v>50</v>
       </c>
     </row>
     <row r="714" spans="2:5" x14ac:dyDescent="0.35">
       <c r="B714" t="s">
-        <v>781</v>
+        <v>779</v>
       </c>
       <c r="E714" t="s">
-        <v>59</v>
+        <v>60</v>
       </c>
     </row>
     <row r="715" spans="2:5" x14ac:dyDescent="0.35">
       <c r="B715" t="s">
-        <v>782</v>
+        <v>780</v>
       </c>
       <c r="E715" t="s">
-        <v>54</v>
+        <v>87</v>
       </c>
     </row>
     <row r="716" spans="2:5" x14ac:dyDescent="0.35">
       <c r="B716" t="s">
-        <v>783</v>
+        <v>781</v>
       </c>
       <c r="E716" t="s">
         <v>64</v>
@@ -9399,151 +9363,151 @@
     </row>
     <row r="717" spans="2:5" x14ac:dyDescent="0.35">
       <c r="B717" t="s">
-        <v>784</v>
+        <v>782</v>
       </c>
       <c r="E717" t="s">
-        <v>91</v>
+        <v>82</v>
       </c>
     </row>
     <row r="718" spans="2:5" x14ac:dyDescent="0.35">
       <c r="B718" t="s">
-        <v>785</v>
+        <v>783</v>
       </c>
       <c r="E718" t="s">
-        <v>68</v>
+        <v>90</v>
       </c>
     </row>
     <row r="719" spans="2:5" x14ac:dyDescent="0.35">
       <c r="B719" t="s">
-        <v>786</v>
+        <v>784</v>
       </c>
       <c r="E719" t="s">
-        <v>86</v>
+        <v>65</v>
       </c>
     </row>
     <row r="720" spans="2:5" x14ac:dyDescent="0.35">
       <c r="B720" t="s">
-        <v>787</v>
+        <v>785</v>
       </c>
       <c r="E720" t="s">
-        <v>94</v>
+        <v>76</v>
       </c>
     </row>
     <row r="721" spans="2:5" x14ac:dyDescent="0.35">
       <c r="B721" t="s">
-        <v>788</v>
+        <v>786</v>
       </c>
       <c r="E721" t="s">
-        <v>69</v>
+        <v>674</v>
       </c>
     </row>
     <row r="722" spans="2:5" x14ac:dyDescent="0.35">
       <c r="B722" t="s">
-        <v>789</v>
+        <v>787</v>
       </c>
       <c r="E722" t="s">
-        <v>80</v>
+        <v>47</v>
       </c>
     </row>
     <row r="723" spans="2:5" x14ac:dyDescent="0.35">
       <c r="B723" t="s">
-        <v>790</v>
+        <v>788</v>
       </c>
       <c r="E723" t="s">
-        <v>678</v>
+        <v>677</v>
       </c>
     </row>
     <row r="724" spans="2:5" x14ac:dyDescent="0.35">
       <c r="B724" t="s">
-        <v>791</v>
+        <v>789</v>
       </c>
       <c r="E724" t="s">
-        <v>51</v>
+        <v>52</v>
       </c>
     </row>
     <row r="725" spans="2:5" x14ac:dyDescent="0.35">
       <c r="B725" t="s">
-        <v>792</v>
+        <v>790</v>
       </c>
       <c r="E725" t="s">
-        <v>681</v>
+        <v>680</v>
       </c>
     </row>
     <row r="726" spans="2:5" x14ac:dyDescent="0.35">
       <c r="B726" t="s">
-        <v>793</v>
+        <v>791</v>
       </c>
       <c r="E726" t="s">
-        <v>56</v>
+        <v>61</v>
       </c>
     </row>
     <row r="727" spans="2:5" x14ac:dyDescent="0.35">
       <c r="B727" t="s">
-        <v>794</v>
+        <v>792</v>
       </c>
       <c r="E727" t="s">
-        <v>684</v>
+        <v>682</v>
       </c>
     </row>
     <row r="728" spans="2:5" x14ac:dyDescent="0.35">
       <c r="B728" t="s">
-        <v>795</v>
+        <v>793</v>
       </c>
       <c r="E728" t="s">
-        <v>65</v>
+        <v>684</v>
       </c>
     </row>
     <row r="729" spans="2:5" x14ac:dyDescent="0.35">
       <c r="B729" t="s">
-        <v>796</v>
+        <v>794</v>
       </c>
       <c r="E729" t="s">
-        <v>686</v>
+        <v>45</v>
       </c>
     </row>
     <row r="730" spans="2:5" x14ac:dyDescent="0.35">
       <c r="B730" t="s">
-        <v>797</v>
+        <v>795</v>
       </c>
       <c r="E730" t="s">
-        <v>688</v>
+        <v>57</v>
       </c>
     </row>
     <row r="731" spans="2:5" x14ac:dyDescent="0.35">
       <c r="B731" t="s">
-        <v>798</v>
+        <v>796</v>
       </c>
       <c r="E731" t="s">
-        <v>49</v>
+        <v>55</v>
       </c>
     </row>
     <row r="732" spans="2:5" x14ac:dyDescent="0.35">
       <c r="B732" t="s">
-        <v>799</v>
+        <v>797</v>
       </c>
       <c r="E732" t="s">
-        <v>61</v>
+        <v>50</v>
       </c>
     </row>
     <row r="733" spans="2:5" x14ac:dyDescent="0.35">
       <c r="B733" t="s">
-        <v>800</v>
+        <v>798</v>
       </c>
       <c r="E733" t="s">
-        <v>59</v>
+        <v>60</v>
       </c>
     </row>
     <row r="734" spans="2:5" x14ac:dyDescent="0.35">
       <c r="B734" t="s">
-        <v>801</v>
+        <v>799</v>
       </c>
       <c r="E734" t="s">
-        <v>54</v>
+        <v>87</v>
       </c>
     </row>
     <row r="735" spans="2:5" x14ac:dyDescent="0.35">
       <c r="B735" t="s">
-        <v>802</v>
+        <v>800</v>
       </c>
       <c r="E735" t="s">
         <v>64</v>
@@ -9551,151 +9515,151 @@
     </row>
     <row r="736" spans="2:5" x14ac:dyDescent="0.35">
       <c r="B736" t="s">
-        <v>803</v>
+        <v>801</v>
       </c>
       <c r="E736" t="s">
-        <v>91</v>
+        <v>82</v>
       </c>
     </row>
     <row r="737" spans="2:5" x14ac:dyDescent="0.35">
       <c r="B737" t="s">
-        <v>804</v>
+        <v>802</v>
       </c>
       <c r="E737" t="s">
-        <v>68</v>
+        <v>90</v>
       </c>
     </row>
     <row r="738" spans="2:5" x14ac:dyDescent="0.35">
       <c r="B738" t="s">
-        <v>805</v>
+        <v>803</v>
       </c>
       <c r="E738" t="s">
-        <v>86</v>
+        <v>65</v>
       </c>
     </row>
     <row r="739" spans="2:5" x14ac:dyDescent="0.35">
       <c r="B739" t="s">
-        <v>806</v>
+        <v>804</v>
       </c>
       <c r="E739" t="s">
-        <v>94</v>
+        <v>76</v>
       </c>
     </row>
     <row r="740" spans="2:5" x14ac:dyDescent="0.35">
       <c r="B740" t="s">
-        <v>807</v>
+        <v>805</v>
       </c>
       <c r="E740" t="s">
-        <v>69</v>
+        <v>674</v>
       </c>
     </row>
     <row r="741" spans="2:5" x14ac:dyDescent="0.35">
       <c r="B741" t="s">
-        <v>808</v>
+        <v>806</v>
       </c>
       <c r="E741" t="s">
-        <v>80</v>
+        <v>47</v>
       </c>
     </row>
     <row r="742" spans="2:5" x14ac:dyDescent="0.35">
       <c r="B742" t="s">
-        <v>809</v>
+        <v>807</v>
       </c>
       <c r="E742" t="s">
-        <v>678</v>
+        <v>677</v>
       </c>
     </row>
     <row r="743" spans="2:5" x14ac:dyDescent="0.35">
       <c r="B743" t="s">
-        <v>810</v>
+        <v>808</v>
       </c>
       <c r="E743" t="s">
-        <v>51</v>
+        <v>52</v>
       </c>
     </row>
     <row r="744" spans="2:5" x14ac:dyDescent="0.35">
       <c r="B744" t="s">
-        <v>811</v>
+        <v>809</v>
       </c>
       <c r="E744" t="s">
-        <v>681</v>
+        <v>680</v>
       </c>
     </row>
     <row r="745" spans="2:5" x14ac:dyDescent="0.35">
       <c r="B745" t="s">
-        <v>812</v>
+        <v>810</v>
       </c>
       <c r="E745" t="s">
-        <v>56</v>
+        <v>61</v>
       </c>
     </row>
     <row r="746" spans="2:5" x14ac:dyDescent="0.35">
       <c r="B746" t="s">
-        <v>813</v>
+        <v>811</v>
       </c>
       <c r="E746" t="s">
-        <v>684</v>
+        <v>682</v>
       </c>
     </row>
     <row r="747" spans="2:5" x14ac:dyDescent="0.35">
       <c r="B747" t="s">
-        <v>814</v>
+        <v>812</v>
       </c>
       <c r="E747" t="s">
-        <v>65</v>
+        <v>684</v>
       </c>
     </row>
     <row r="748" spans="2:5" x14ac:dyDescent="0.35">
       <c r="B748" t="s">
-        <v>815</v>
+        <v>813</v>
       </c>
       <c r="E748" t="s">
-        <v>686</v>
+        <v>45</v>
       </c>
     </row>
     <row r="749" spans="2:5" x14ac:dyDescent="0.35">
       <c r="B749" t="s">
-        <v>816</v>
+        <v>814</v>
       </c>
       <c r="E749" t="s">
-        <v>688</v>
+        <v>57</v>
       </c>
     </row>
     <row r="750" spans="2:5" x14ac:dyDescent="0.35">
       <c r="B750" t="s">
-        <v>817</v>
+        <v>815</v>
       </c>
       <c r="E750" t="s">
-        <v>49</v>
+        <v>55</v>
       </c>
     </row>
     <row r="751" spans="2:5" x14ac:dyDescent="0.35">
       <c r="B751" t="s">
-        <v>818</v>
+        <v>816</v>
       </c>
       <c r="E751" t="s">
-        <v>61</v>
+        <v>50</v>
       </c>
     </row>
     <row r="752" spans="2:5" x14ac:dyDescent="0.35">
       <c r="B752" t="s">
-        <v>819</v>
+        <v>817</v>
       </c>
       <c r="E752" t="s">
-        <v>59</v>
+        <v>60</v>
       </c>
     </row>
     <row r="753" spans="2:5" x14ac:dyDescent="0.35">
       <c r="B753" t="s">
-        <v>820</v>
+        <v>818</v>
       </c>
       <c r="E753" t="s">
-        <v>54</v>
+        <v>87</v>
       </c>
     </row>
     <row r="754" spans="2:5" x14ac:dyDescent="0.35">
       <c r="B754" t="s">
-        <v>821</v>
+        <v>819</v>
       </c>
       <c r="E754" t="s">
         <v>64</v>
@@ -9703,151 +9667,151 @@
     </row>
     <row r="755" spans="2:5" x14ac:dyDescent="0.35">
       <c r="B755" t="s">
-        <v>822</v>
+        <v>820</v>
       </c>
       <c r="E755" t="s">
-        <v>91</v>
+        <v>82</v>
       </c>
     </row>
     <row r="756" spans="2:5" x14ac:dyDescent="0.35">
       <c r="B756" t="s">
-        <v>823</v>
+        <v>821</v>
       </c>
       <c r="E756" t="s">
-        <v>68</v>
+        <v>90</v>
       </c>
     </row>
     <row r="757" spans="2:5" x14ac:dyDescent="0.35">
       <c r="B757" t="s">
-        <v>824</v>
+        <v>822</v>
       </c>
       <c r="E757" t="s">
-        <v>86</v>
+        <v>65</v>
       </c>
     </row>
     <row r="758" spans="2:5" x14ac:dyDescent="0.35">
       <c r="B758" t="s">
-        <v>825</v>
+        <v>823</v>
       </c>
       <c r="E758" t="s">
-        <v>94</v>
+        <v>76</v>
       </c>
     </row>
     <row r="759" spans="2:5" x14ac:dyDescent="0.35">
       <c r="B759" t="s">
-        <v>826</v>
+        <v>824</v>
       </c>
       <c r="E759" t="s">
-        <v>69</v>
+        <v>674</v>
       </c>
     </row>
     <row r="760" spans="2:5" x14ac:dyDescent="0.35">
       <c r="B760" t="s">
-        <v>827</v>
+        <v>825</v>
       </c>
       <c r="E760" t="s">
-        <v>80</v>
+        <v>47</v>
       </c>
     </row>
     <row r="761" spans="2:5" x14ac:dyDescent="0.35">
       <c r="B761" t="s">
-        <v>828</v>
+        <v>826</v>
       </c>
       <c r="E761" t="s">
-        <v>678</v>
+        <v>677</v>
       </c>
     </row>
     <row r="762" spans="2:5" x14ac:dyDescent="0.35">
       <c r="B762" t="s">
-        <v>829</v>
+        <v>827</v>
       </c>
       <c r="E762" t="s">
-        <v>51</v>
+        <v>52</v>
       </c>
     </row>
     <row r="763" spans="2:5" x14ac:dyDescent="0.35">
       <c r="B763" t="s">
-        <v>830</v>
+        <v>828</v>
       </c>
       <c r="E763" t="s">
-        <v>681</v>
+        <v>680</v>
       </c>
     </row>
     <row r="764" spans="2:5" x14ac:dyDescent="0.35">
       <c r="B764" t="s">
-        <v>831</v>
+        <v>829</v>
       </c>
       <c r="E764" t="s">
-        <v>56</v>
+        <v>61</v>
       </c>
     </row>
     <row r="765" spans="2:5" x14ac:dyDescent="0.35">
       <c r="B765" t="s">
-        <v>832</v>
+        <v>830</v>
       </c>
       <c r="E765" t="s">
-        <v>684</v>
+        <v>682</v>
       </c>
     </row>
     <row r="766" spans="2:5" x14ac:dyDescent="0.35">
       <c r="B766" t="s">
-        <v>833</v>
+        <v>831</v>
       </c>
       <c r="E766" t="s">
-        <v>65</v>
+        <v>684</v>
       </c>
     </row>
     <row r="767" spans="2:5" x14ac:dyDescent="0.35">
       <c r="B767" t="s">
-        <v>834</v>
+        <v>832</v>
       </c>
       <c r="E767" t="s">
-        <v>686</v>
+        <v>45</v>
       </c>
     </row>
     <row r="768" spans="2:5" x14ac:dyDescent="0.35">
       <c r="B768" t="s">
-        <v>835</v>
+        <v>833</v>
       </c>
       <c r="E768" t="s">
-        <v>688</v>
+        <v>57</v>
       </c>
     </row>
     <row r="769" spans="2:5" x14ac:dyDescent="0.35">
       <c r="B769" t="s">
-        <v>836</v>
+        <v>834</v>
       </c>
       <c r="E769" t="s">
-        <v>49</v>
+        <v>55</v>
       </c>
     </row>
     <row r="770" spans="2:5" x14ac:dyDescent="0.35">
       <c r="B770" t="s">
-        <v>837</v>
+        <v>835</v>
       </c>
       <c r="E770" t="s">
-        <v>61</v>
+        <v>50</v>
       </c>
     </row>
     <row r="771" spans="2:5" x14ac:dyDescent="0.35">
       <c r="B771" t="s">
-        <v>838</v>
+        <v>836</v>
       </c>
       <c r="E771" t="s">
-        <v>59</v>
+        <v>60</v>
       </c>
     </row>
     <row r="772" spans="2:5" x14ac:dyDescent="0.35">
       <c r="B772" t="s">
-        <v>839</v>
+        <v>837</v>
       </c>
       <c r="E772" t="s">
-        <v>54</v>
+        <v>87</v>
       </c>
     </row>
     <row r="773" spans="2:5" x14ac:dyDescent="0.35">
       <c r="B773" t="s">
-        <v>840</v>
+        <v>838</v>
       </c>
       <c r="E773" t="s">
         <v>64</v>
@@ -9855,151 +9819,151 @@
     </row>
     <row r="774" spans="2:5" x14ac:dyDescent="0.35">
       <c r="B774" t="s">
-        <v>841</v>
+        <v>839</v>
       </c>
       <c r="E774" t="s">
-        <v>91</v>
+        <v>82</v>
       </c>
     </row>
     <row r="775" spans="2:5" x14ac:dyDescent="0.35">
       <c r="B775" t="s">
-        <v>842</v>
+        <v>840</v>
       </c>
       <c r="E775" t="s">
-        <v>68</v>
+        <v>90</v>
       </c>
     </row>
     <row r="776" spans="2:5" x14ac:dyDescent="0.35">
       <c r="B776" t="s">
-        <v>843</v>
+        <v>841</v>
       </c>
       <c r="E776" t="s">
-        <v>86</v>
+        <v>65</v>
       </c>
     </row>
     <row r="777" spans="2:5" x14ac:dyDescent="0.35">
       <c r="B777" t="s">
-        <v>844</v>
+        <v>842</v>
       </c>
       <c r="E777" t="s">
-        <v>94</v>
+        <v>76</v>
       </c>
     </row>
     <row r="778" spans="2:5" x14ac:dyDescent="0.35">
       <c r="B778" t="s">
-        <v>845</v>
+        <v>843</v>
       </c>
       <c r="E778" t="s">
-        <v>69</v>
+        <v>674</v>
       </c>
     </row>
     <row r="779" spans="2:5" x14ac:dyDescent="0.35">
       <c r="B779" t="s">
-        <v>846</v>
+        <v>844</v>
       </c>
       <c r="E779" t="s">
-        <v>80</v>
+        <v>47</v>
       </c>
     </row>
     <row r="780" spans="2:5" x14ac:dyDescent="0.35">
       <c r="B780" t="s">
-        <v>847</v>
+        <v>845</v>
       </c>
       <c r="E780" t="s">
-        <v>678</v>
+        <v>677</v>
       </c>
     </row>
     <row r="781" spans="2:5" x14ac:dyDescent="0.35">
       <c r="B781" t="s">
-        <v>848</v>
+        <v>846</v>
       </c>
       <c r="E781" t="s">
-        <v>51</v>
+        <v>52</v>
       </c>
     </row>
     <row r="782" spans="2:5" x14ac:dyDescent="0.35">
       <c r="B782" t="s">
-        <v>849</v>
+        <v>847</v>
       </c>
       <c r="E782" t="s">
-        <v>681</v>
+        <v>680</v>
       </c>
     </row>
     <row r="783" spans="2:5" x14ac:dyDescent="0.35">
       <c r="B783" t="s">
-        <v>850</v>
+        <v>848</v>
       </c>
       <c r="E783" t="s">
-        <v>56</v>
+        <v>61</v>
       </c>
     </row>
     <row r="784" spans="2:5" x14ac:dyDescent="0.35">
       <c r="B784" t="s">
-        <v>851</v>
+        <v>849</v>
       </c>
       <c r="E784" t="s">
-        <v>684</v>
+        <v>682</v>
       </c>
     </row>
     <row r="785" spans="2:5" x14ac:dyDescent="0.35">
       <c r="B785" t="s">
-        <v>852</v>
+        <v>850</v>
       </c>
       <c r="E785" t="s">
-        <v>65</v>
+        <v>684</v>
       </c>
     </row>
     <row r="786" spans="2:5" x14ac:dyDescent="0.35">
       <c r="B786" t="s">
-        <v>853</v>
+        <v>851</v>
       </c>
       <c r="E786" t="s">
-        <v>686</v>
+        <v>45</v>
       </c>
     </row>
     <row r="787" spans="2:5" x14ac:dyDescent="0.35">
       <c r="B787" t="s">
-        <v>854</v>
+        <v>852</v>
       </c>
       <c r="E787" t="s">
-        <v>688</v>
+        <v>57</v>
       </c>
     </row>
     <row r="788" spans="2:5" x14ac:dyDescent="0.35">
       <c r="B788" t="s">
-        <v>855</v>
+        <v>853</v>
       </c>
       <c r="E788" t="s">
-        <v>49</v>
+        <v>55</v>
       </c>
     </row>
     <row r="789" spans="2:5" x14ac:dyDescent="0.35">
       <c r="B789" t="s">
-        <v>856</v>
+        <v>854</v>
       </c>
       <c r="E789" t="s">
-        <v>61</v>
+        <v>50</v>
       </c>
     </row>
     <row r="790" spans="2:5" x14ac:dyDescent="0.35">
       <c r="B790" t="s">
-        <v>857</v>
+        <v>855</v>
       </c>
       <c r="E790" t="s">
-        <v>59</v>
+        <v>60</v>
       </c>
     </row>
     <row r="791" spans="2:5" x14ac:dyDescent="0.35">
       <c r="B791" t="s">
-        <v>858</v>
+        <v>856</v>
       </c>
       <c r="E791" t="s">
-        <v>54</v>
+        <v>87</v>
       </c>
     </row>
     <row r="792" spans="2:5" x14ac:dyDescent="0.35">
       <c r="B792" t="s">
-        <v>859</v>
+        <v>857</v>
       </c>
       <c r="E792" t="s">
         <v>64</v>
@@ -10007,151 +9971,151 @@
     </row>
     <row r="793" spans="2:5" x14ac:dyDescent="0.35">
       <c r="B793" t="s">
-        <v>860</v>
+        <v>858</v>
       </c>
       <c r="E793" t="s">
-        <v>91</v>
+        <v>82</v>
       </c>
     </row>
     <row r="794" spans="2:5" x14ac:dyDescent="0.35">
       <c r="B794" t="s">
-        <v>861</v>
+        <v>859</v>
       </c>
       <c r="E794" t="s">
-        <v>68</v>
+        <v>90</v>
       </c>
     </row>
     <row r="795" spans="2:5" x14ac:dyDescent="0.35">
       <c r="B795" t="s">
-        <v>862</v>
+        <v>860</v>
       </c>
       <c r="E795" t="s">
-        <v>86</v>
+        <v>65</v>
       </c>
     </row>
     <row r="796" spans="2:5" x14ac:dyDescent="0.35">
       <c r="B796" t="s">
-        <v>863</v>
+        <v>861</v>
       </c>
       <c r="E796" t="s">
-        <v>94</v>
+        <v>76</v>
       </c>
     </row>
     <row r="797" spans="2:5" x14ac:dyDescent="0.35">
       <c r="B797" t="s">
-        <v>864</v>
+        <v>862</v>
       </c>
       <c r="E797" t="s">
-        <v>69</v>
+        <v>674</v>
       </c>
     </row>
     <row r="798" spans="2:5" x14ac:dyDescent="0.35">
       <c r="B798" t="s">
-        <v>865</v>
+        <v>863</v>
       </c>
       <c r="E798" t="s">
-        <v>80</v>
+        <v>47</v>
       </c>
     </row>
     <row r="799" spans="2:5" x14ac:dyDescent="0.35">
       <c r="B799" t="s">
-        <v>866</v>
+        <v>864</v>
       </c>
       <c r="E799" t="s">
-        <v>678</v>
+        <v>677</v>
       </c>
     </row>
     <row r="800" spans="2:5" x14ac:dyDescent="0.35">
       <c r="B800" t="s">
-        <v>867</v>
+        <v>865</v>
       </c>
       <c r="E800" t="s">
-        <v>51</v>
+        <v>52</v>
       </c>
     </row>
     <row r="801" spans="2:5" x14ac:dyDescent="0.35">
       <c r="B801" t="s">
-        <v>868</v>
+        <v>866</v>
       </c>
       <c r="E801" t="s">
-        <v>681</v>
+        <v>680</v>
       </c>
     </row>
     <row r="802" spans="2:5" x14ac:dyDescent="0.35">
       <c r="B802" t="s">
-        <v>869</v>
+        <v>867</v>
       </c>
       <c r="E802" t="s">
-        <v>56</v>
+        <v>61</v>
       </c>
     </row>
     <row r="803" spans="2:5" x14ac:dyDescent="0.35">
       <c r="B803" t="s">
-        <v>870</v>
+        <v>868</v>
       </c>
       <c r="E803" t="s">
-        <v>684</v>
+        <v>682</v>
       </c>
     </row>
     <row r="804" spans="2:5" x14ac:dyDescent="0.35">
       <c r="B804" t="s">
-        <v>871</v>
+        <v>869</v>
       </c>
       <c r="E804" t="s">
-        <v>65</v>
+        <v>684</v>
       </c>
     </row>
     <row r="805" spans="2:5" x14ac:dyDescent="0.35">
       <c r="B805" t="s">
-        <v>872</v>
+        <v>870</v>
       </c>
       <c r="E805" t="s">
-        <v>686</v>
+        <v>45</v>
       </c>
     </row>
     <row r="806" spans="2:5" x14ac:dyDescent="0.35">
       <c r="B806" t="s">
-        <v>873</v>
+        <v>871</v>
       </c>
       <c r="E806" t="s">
-        <v>688</v>
+        <v>57</v>
       </c>
     </row>
     <row r="807" spans="2:5" x14ac:dyDescent="0.35">
       <c r="B807" t="s">
-        <v>874</v>
+        <v>872</v>
       </c>
       <c r="E807" t="s">
-        <v>49</v>
+        <v>55</v>
       </c>
     </row>
     <row r="808" spans="2:5" x14ac:dyDescent="0.35">
       <c r="B808" t="s">
-        <v>875</v>
+        <v>873</v>
       </c>
       <c r="E808" t="s">
-        <v>61</v>
+        <v>50</v>
       </c>
     </row>
     <row r="809" spans="2:5" x14ac:dyDescent="0.35">
       <c r="B809" t="s">
-        <v>876</v>
+        <v>874</v>
       </c>
       <c r="E809" t="s">
-        <v>59</v>
+        <v>60</v>
       </c>
     </row>
     <row r="810" spans="2:5" x14ac:dyDescent="0.35">
       <c r="B810" t="s">
-        <v>877</v>
+        <v>875</v>
       </c>
       <c r="E810" t="s">
-        <v>54</v>
+        <v>87</v>
       </c>
     </row>
     <row r="811" spans="2:5" x14ac:dyDescent="0.35">
       <c r="B811" t="s">
-        <v>878</v>
+        <v>876</v>
       </c>
       <c r="E811" t="s">
         <v>64</v>
@@ -10159,151 +10123,151 @@
     </row>
     <row r="812" spans="2:5" x14ac:dyDescent="0.35">
       <c r="B812" t="s">
-        <v>879</v>
+        <v>877</v>
       </c>
       <c r="E812" t="s">
-        <v>91</v>
+        <v>82</v>
       </c>
     </row>
     <row r="813" spans="2:5" x14ac:dyDescent="0.35">
       <c r="B813" t="s">
-        <v>880</v>
+        <v>878</v>
       </c>
       <c r="E813" t="s">
-        <v>68</v>
+        <v>90</v>
       </c>
     </row>
     <row r="814" spans="2:5" x14ac:dyDescent="0.35">
       <c r="B814" t="s">
-        <v>881</v>
+        <v>879</v>
       </c>
       <c r="E814" t="s">
-        <v>86</v>
+        <v>65</v>
       </c>
     </row>
     <row r="815" spans="2:5" x14ac:dyDescent="0.35">
       <c r="B815" t="s">
-        <v>882</v>
+        <v>880</v>
       </c>
       <c r="E815" t="s">
-        <v>94</v>
+        <v>76</v>
       </c>
     </row>
     <row r="816" spans="2:5" x14ac:dyDescent="0.35">
       <c r="B816" t="s">
-        <v>883</v>
+        <v>881</v>
       </c>
       <c r="E816" t="s">
-        <v>69</v>
+        <v>674</v>
       </c>
     </row>
     <row r="817" spans="2:5" x14ac:dyDescent="0.35">
       <c r="B817" t="s">
-        <v>884</v>
+        <v>882</v>
       </c>
       <c r="E817" t="s">
-        <v>80</v>
+        <v>47</v>
       </c>
     </row>
     <row r="818" spans="2:5" x14ac:dyDescent="0.35">
       <c r="B818" t="s">
-        <v>885</v>
+        <v>883</v>
       </c>
       <c r="E818" t="s">
-        <v>678</v>
+        <v>677</v>
       </c>
     </row>
     <row r="819" spans="2:5" x14ac:dyDescent="0.35">
       <c r="B819" t="s">
-        <v>886</v>
+        <v>884</v>
       </c>
       <c r="E819" t="s">
-        <v>51</v>
+        <v>52</v>
       </c>
     </row>
     <row r="820" spans="2:5" x14ac:dyDescent="0.35">
       <c r="B820" t="s">
-        <v>887</v>
+        <v>885</v>
       </c>
       <c r="E820" t="s">
-        <v>681</v>
+        <v>680</v>
       </c>
     </row>
     <row r="821" spans="2:5" x14ac:dyDescent="0.35">
       <c r="B821" t="s">
-        <v>888</v>
+        <v>886</v>
       </c>
       <c r="E821" t="s">
-        <v>56</v>
+        <v>61</v>
       </c>
     </row>
     <row r="822" spans="2:5" x14ac:dyDescent="0.35">
       <c r="B822" t="s">
-        <v>889</v>
+        <v>887</v>
       </c>
       <c r="E822" t="s">
-        <v>684</v>
+        <v>682</v>
       </c>
     </row>
     <row r="823" spans="2:5" x14ac:dyDescent="0.35">
       <c r="B823" t="s">
-        <v>890</v>
+        <v>888</v>
       </c>
       <c r="E823" t="s">
-        <v>65</v>
+        <v>684</v>
       </c>
     </row>
     <row r="824" spans="2:5" x14ac:dyDescent="0.35">
       <c r="B824" t="s">
-        <v>891</v>
+        <v>889</v>
       </c>
       <c r="E824" t="s">
-        <v>686</v>
+        <v>45</v>
       </c>
     </row>
     <row r="825" spans="2:5" x14ac:dyDescent="0.35">
       <c r="B825" t="s">
-        <v>892</v>
+        <v>890</v>
       </c>
       <c r="E825" t="s">
-        <v>688</v>
+        <v>57</v>
       </c>
     </row>
     <row r="826" spans="2:5" x14ac:dyDescent="0.35">
       <c r="B826" t="s">
-        <v>893</v>
+        <v>891</v>
       </c>
       <c r="E826" t="s">
-        <v>49</v>
+        <v>55</v>
       </c>
     </row>
     <row r="827" spans="2:5" x14ac:dyDescent="0.35">
       <c r="B827" t="s">
-        <v>894</v>
+        <v>892</v>
       </c>
       <c r="E827" t="s">
-        <v>61</v>
+        <v>50</v>
       </c>
     </row>
     <row r="828" spans="2:5" x14ac:dyDescent="0.35">
       <c r="B828" t="s">
-        <v>895</v>
+        <v>893</v>
       </c>
       <c r="E828" t="s">
-        <v>59</v>
+        <v>60</v>
       </c>
     </row>
     <row r="829" spans="2:5" x14ac:dyDescent="0.35">
       <c r="B829" t="s">
-        <v>896</v>
+        <v>894</v>
       </c>
       <c r="E829" t="s">
-        <v>54</v>
+        <v>87</v>
       </c>
     </row>
     <row r="830" spans="2:5" x14ac:dyDescent="0.35">
       <c r="B830" t="s">
-        <v>897</v>
+        <v>895</v>
       </c>
       <c r="E830" t="s">
         <v>64</v>
@@ -10311,151 +10275,151 @@
     </row>
     <row r="831" spans="2:5" x14ac:dyDescent="0.35">
       <c r="B831" t="s">
-        <v>898</v>
+        <v>896</v>
       </c>
       <c r="E831" t="s">
-        <v>91</v>
+        <v>82</v>
       </c>
     </row>
     <row r="832" spans="2:5" x14ac:dyDescent="0.35">
       <c r="B832" t="s">
-        <v>899</v>
+        <v>897</v>
       </c>
       <c r="E832" t="s">
-        <v>68</v>
+        <v>90</v>
       </c>
     </row>
     <row r="833" spans="2:5" x14ac:dyDescent="0.35">
       <c r="B833" t="s">
-        <v>900</v>
+        <v>898</v>
       </c>
       <c r="E833" t="s">
-        <v>86</v>
+        <v>65</v>
       </c>
     </row>
     <row r="834" spans="2:5" x14ac:dyDescent="0.35">
       <c r="B834" t="s">
-        <v>901</v>
+        <v>899</v>
       </c>
       <c r="E834" t="s">
-        <v>94</v>
+        <v>76</v>
       </c>
     </row>
     <row r="835" spans="2:5" x14ac:dyDescent="0.35">
       <c r="B835" t="s">
-        <v>902</v>
+        <v>900</v>
       </c>
       <c r="E835" t="s">
-        <v>69</v>
+        <v>674</v>
       </c>
     </row>
     <row r="836" spans="2:5" x14ac:dyDescent="0.35">
       <c r="B836" t="s">
-        <v>903</v>
+        <v>901</v>
       </c>
       <c r="E836" t="s">
-        <v>80</v>
+        <v>47</v>
       </c>
     </row>
     <row r="837" spans="2:5" x14ac:dyDescent="0.35">
       <c r="B837" t="s">
-        <v>904</v>
+        <v>902</v>
       </c>
       <c r="E837" t="s">
-        <v>678</v>
+        <v>677</v>
       </c>
     </row>
     <row r="838" spans="2:5" x14ac:dyDescent="0.35">
       <c r="B838" t="s">
-        <v>905</v>
+        <v>903</v>
       </c>
       <c r="E838" t="s">
-        <v>51</v>
+        <v>52</v>
       </c>
     </row>
     <row r="839" spans="2:5" x14ac:dyDescent="0.35">
       <c r="B839" t="s">
-        <v>906</v>
+        <v>904</v>
       </c>
       <c r="E839" t="s">
-        <v>681</v>
+        <v>680</v>
       </c>
     </row>
     <row r="840" spans="2:5" x14ac:dyDescent="0.35">
       <c r="B840" t="s">
-        <v>907</v>
+        <v>905</v>
       </c>
       <c r="E840" t="s">
-        <v>56</v>
+        <v>61</v>
       </c>
     </row>
     <row r="841" spans="2:5" x14ac:dyDescent="0.35">
       <c r="B841" t="s">
-        <v>908</v>
+        <v>906</v>
       </c>
       <c r="E841" t="s">
-        <v>684</v>
+        <v>682</v>
       </c>
     </row>
     <row r="842" spans="2:5" x14ac:dyDescent="0.35">
       <c r="B842" t="s">
-        <v>909</v>
+        <v>907</v>
       </c>
       <c r="E842" t="s">
-        <v>65</v>
+        <v>684</v>
       </c>
     </row>
     <row r="843" spans="2:5" x14ac:dyDescent="0.35">
       <c r="B843" t="s">
-        <v>910</v>
+        <v>908</v>
       </c>
       <c r="E843" t="s">
-        <v>686</v>
+        <v>45</v>
       </c>
     </row>
     <row r="844" spans="2:5" x14ac:dyDescent="0.35">
       <c r="B844" t="s">
-        <v>911</v>
+        <v>909</v>
       </c>
       <c r="E844" t="s">
-        <v>688</v>
+        <v>57</v>
       </c>
     </row>
     <row r="845" spans="2:5" x14ac:dyDescent="0.35">
       <c r="B845" t="s">
-        <v>912</v>
+        <v>910</v>
       </c>
       <c r="E845" t="s">
-        <v>49</v>
+        <v>55</v>
       </c>
     </row>
     <row r="846" spans="2:5" x14ac:dyDescent="0.35">
       <c r="B846" t="s">
-        <v>913</v>
+        <v>911</v>
       </c>
       <c r="E846" t="s">
-        <v>61</v>
+        <v>50</v>
       </c>
     </row>
     <row r="847" spans="2:5" x14ac:dyDescent="0.35">
       <c r="B847" t="s">
-        <v>914</v>
+        <v>912</v>
       </c>
       <c r="E847" t="s">
-        <v>59</v>
+        <v>60</v>
       </c>
     </row>
     <row r="848" spans="2:5" x14ac:dyDescent="0.35">
       <c r="B848" t="s">
-        <v>915</v>
+        <v>913</v>
       </c>
       <c r="E848" t="s">
-        <v>54</v>
+        <v>87</v>
       </c>
     </row>
     <row r="849" spans="2:5" x14ac:dyDescent="0.35">
       <c r="B849" t="s">
-        <v>916</v>
+        <v>914</v>
       </c>
       <c r="E849" t="s">
         <v>64</v>
@@ -10463,42 +10427,26 @@
     </row>
     <row r="850" spans="2:5" x14ac:dyDescent="0.35">
       <c r="B850" t="s">
-        <v>917</v>
+        <v>915</v>
       </c>
       <c r="E850" t="s">
-        <v>91</v>
+        <v>82</v>
       </c>
     </row>
     <row r="851" spans="2:5" x14ac:dyDescent="0.35">
       <c r="B851" t="s">
-        <v>918</v>
+        <v>916</v>
       </c>
       <c r="E851" t="s">
-        <v>68</v>
+        <v>90</v>
       </c>
     </row>
     <row r="852" spans="2:5" x14ac:dyDescent="0.35">
       <c r="B852" t="s">
-        <v>919</v>
+        <v>917</v>
       </c>
       <c r="E852" t="s">
-        <v>86</v>
-      </c>
-    </row>
-    <row r="853" spans="2:5" x14ac:dyDescent="0.35">
-      <c r="B853" t="s">
-        <v>920</v>
-      </c>
-      <c r="E853" t="s">
-        <v>94</v>
-      </c>
-    </row>
-    <row r="854" spans="2:5" x14ac:dyDescent="0.35">
-      <c r="B854" t="s">
-        <v>921</v>
-      </c>
-      <c r="E854" t="s">
-        <v>88</v>
+        <v>84</v>
       </c>
     </row>
   </sheetData>

--- a/Test Data/Regression/4689052/UK_ImportMapping.xlsx
+++ b/Test Data/Regression/4689052/UK_ImportMapping.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Playwright_self\playwright-OCT-Automation2\Test Data\Regression\4689052\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C619C4F5-9977-41C0-AB70-498B22580BFA}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{03BAB3AA-45BC-4A19-A054-F332BE08F0F6}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="11500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
